--- a/Gantt Zeitplan Josiah Spilker.xlsx
+++ b/Gantt Zeitplan Josiah Spilker.xlsx
@@ -3,39 +3,47 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6656C02C-33BA-4372-BF8F-D4D624F4706A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DA0B313-9E82-4B7E-BCAF-0F02F07A6644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project plan" sheetId="11" r:id="rId1"/>
-    <sheet name="Project plan Should Is" sheetId="17" r:id="rId2"/>
-    <sheet name="Small" sheetId="16" r:id="rId3"/>
-    <sheet name="Mini" sheetId="15" r:id="rId4"/>
-    <sheet name="Info" sheetId="12" r:id="rId5"/>
+    <sheet name="Temp Soll" sheetId="18" r:id="rId2"/>
+    <sheet name="Project plan Should Is" sheetId="17" r:id="rId3"/>
+    <sheet name="Small" sheetId="16" r:id="rId4"/>
+    <sheet name="Mini" sheetId="15" r:id="rId5"/>
+    <sheet name="Info" sheetId="12" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="Anzeigewoche" localSheetId="1">'Project plan Should Is'!#REF!</definedName>
-    <definedName name="Anzeigewoche" localSheetId="2">Small!#REF!</definedName>
+    <definedName name="Anzeigewoche" localSheetId="2">'Project plan Should Is'!#REF!</definedName>
+    <definedName name="Anzeigewoche" localSheetId="3">Small!#REF!</definedName>
+    <definedName name="Anzeigewoche" localSheetId="1">'Temp Soll'!#REF!</definedName>
     <definedName name="Anzeigewoche">'Project plan'!#REF!</definedName>
     <definedName name="Heute" localSheetId="0">TODAY()</definedName>
+    <definedName name="Heute" localSheetId="2">TODAY()</definedName>
+    <definedName name="Heute" localSheetId="3">TODAY()</definedName>
     <definedName name="Heute" localSheetId="1">TODAY()</definedName>
-    <definedName name="Heute" localSheetId="2">TODAY()</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Project plan'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Project plan Should Is'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">Small!$4:$5</definedName>
-    <definedName name="Projektanfang" localSheetId="1">'Project plan Should Is'!#REF!</definedName>
-    <definedName name="Projektanfang" localSheetId="2">Small!#REF!</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Project plan Should Is'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">Small!$4:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Temp Soll'!$4:$4</definedName>
+    <definedName name="Projektanfang" localSheetId="2">'Project plan Should Is'!#REF!</definedName>
+    <definedName name="Projektanfang" localSheetId="3">Small!#REF!</definedName>
+    <definedName name="Projektanfang" localSheetId="1">'Temp Soll'!#REF!</definedName>
     <definedName name="Projektanfang">'Project plan'!#REF!</definedName>
     <definedName name="task_end" localSheetId="0">'Project plan'!#REF!</definedName>
-    <definedName name="task_end" localSheetId="1">'Project plan Should Is'!#REF!</definedName>
-    <definedName name="task_end" localSheetId="2">Small!#REF!</definedName>
+    <definedName name="task_end" localSheetId="2">'Project plan Should Is'!#REF!</definedName>
+    <definedName name="task_end" localSheetId="3">Small!#REF!</definedName>
+    <definedName name="task_end" localSheetId="1">'Temp Soll'!#REF!</definedName>
     <definedName name="task_progress" localSheetId="0">'Project plan'!#REF!</definedName>
-    <definedName name="task_progress" localSheetId="1">'Project plan Should Is'!#REF!</definedName>
-    <definedName name="task_progress" localSheetId="2">Small!#REF!</definedName>
+    <definedName name="task_progress" localSheetId="2">'Project plan Should Is'!#REF!</definedName>
+    <definedName name="task_progress" localSheetId="3">Small!#REF!</definedName>
+    <definedName name="task_progress" localSheetId="1">'Temp Soll'!#REF!</definedName>
     <definedName name="task_start" localSheetId="0">'Project plan'!#REF!</definedName>
-    <definedName name="task_start" localSheetId="1">'Project plan Should Is'!#REF!</definedName>
-    <definedName name="task_start" localSheetId="2">Small!#REF!</definedName>
+    <definedName name="task_start" localSheetId="2">'Project plan Should Is'!#REF!</definedName>
+    <definedName name="task_start" localSheetId="3">Small!#REF!</definedName>
+    <definedName name="task_start" localSheetId="1">'Temp Soll'!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -58,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="167">
   <si>
     <t>EINFACHES GANTT-DIAGRAMM von Vertex42.com</t>
   </si>
@@ -507,6 +515,63 @@
   </si>
   <si>
     <t>18h</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> = Task was worked on during this 2 hour increment</t>
+  </si>
+  <si>
+    <t>Documentation + Administration is meant as an overarching task that is worked on simultaneously with other tasks.</t>
+  </si>
+  <si>
+    <t>T4.7 : Implement Merge Logic</t>
+  </si>
+  <si>
+    <t>T3.3: Dataverse Entity Design</t>
+  </si>
+  <si>
+    <t>T2.6 : Define Project Roles</t>
+  </si>
+  <si>
+    <t>T3.1 : Architecture Decisions</t>
+  </si>
+  <si>
+    <t>T3.4: Merge/Deactivation Logic</t>
+  </si>
+  <si>
+    <t>T5.1 : Execute Test Cases</t>
+  </si>
+  <si>
+    <t>T5.2 : Robustness/Negative Testing</t>
+  </si>
+  <si>
+    <t>Wed.</t>
+  </si>
+  <si>
+    <t>T3 : Decide                                              5h</t>
+  </si>
+  <si>
+    <t>T5 : Control                                              6h</t>
+  </si>
+  <si>
+    <t>T1 : Inform                                               3h</t>
+  </si>
+  <si>
+    <t>T2 : Plan                                                 14h</t>
+  </si>
+  <si>
+    <t>27.04.2026                                   / = &lt;1h</t>
+  </si>
+  <si>
+    <t>T0 : Documentation/Administration  16h</t>
+  </si>
+  <si>
+    <t>T4 : Realise                                            18h</t>
+  </si>
+  <si>
+    <t>T6 : Evaluate                                          8h</t>
+  </si>
+  <si>
+    <t>T7 : Buffer                                             8h</t>
   </si>
 </sst>
 </file>
@@ -523,7 +588,7 @@
     <numFmt numFmtId="168" formatCode="d/m/yy;@"/>
     <numFmt numFmtId="169" formatCode="ddd\,\ d/m/yyyy"/>
   </numFmts>
-  <fonts count="35" x14ac:knownFonts="1">
+  <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -771,6 +836,21 @@
     <font>
       <b/>
       <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1090,7 +1170,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="74">
+  <borders count="73">
     <border>
       <left/>
       <right/>
@@ -1958,21 +2038,6 @@
         <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </top>
-      <bottom style="medium">
-        <color theme="0" tint="-0.14996795556505021"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="medium">
@@ -2087,7 +2152,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="3" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="3" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="215">
+  <cellXfs count="262">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2540,10 +2605,7 @@
     <xf numFmtId="0" fontId="0" fillId="51" borderId="39" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="51" borderId="71" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="51" borderId="70" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2555,7 +2617,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="73" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="72" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="51" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2588,8 +2650,130 @@
     <xf numFmtId="0" fontId="4" fillId="47" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="35" fillId="0" borderId="0" xfId="7" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="49" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="7" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="45" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="47" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="51" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="41" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="41" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="69" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="68" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="61" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="61" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="44" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="44" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2597,10 +2781,31 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="69" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="68" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="61" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="46" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2615,53 +2820,14 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="41" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="69" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="68" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="61" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="44" borderId="36" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2722,6 +2888,42 @@
     </xf>
     <xf numFmtId="0" fontId="32" fillId="52" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="53" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="48" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="48" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -3321,188 +3523,231 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="41" width="2.7109375" customWidth="1"/>
+    <col min="2" max="13" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="14" max="41" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="194"/>
-      <c r="Z1" s="194"/>
-      <c r="AA1" s="194"/>
-      <c r="AB1" s="194"/>
-      <c r="AC1" s="194"/>
-      <c r="AD1" s="194"/>
-      <c r="AE1" s="194"/>
-      <c r="AF1" s="194"/>
-      <c r="AG1" s="194"/>
-      <c r="AH1" s="194"/>
-      <c r="AI1" s="194"/>
-      <c r="AJ1" s="194"/>
-      <c r="AK1" s="194"/>
-      <c r="AL1" s="194"/>
-      <c r="AM1" s="194"/>
-      <c r="AN1" s="194"/>
-      <c r="AO1" s="194"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="203"/>
+      <c r="O1" s="203"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="203"/>
+      <c r="Y1" s="203"/>
+      <c r="Z1" s="203"/>
+      <c r="AA1" s="203"/>
+      <c r="AB1" s="203"/>
+      <c r="AC1" s="203"/>
+      <c r="AD1" s="203"/>
+      <c r="AE1" s="203"/>
+      <c r="AF1" s="203"/>
+      <c r="AG1" s="203"/>
+      <c r="AH1" s="203"/>
+      <c r="AI1" s="203"/>
+      <c r="AJ1" s="203"/>
+      <c r="AK1" s="203"/>
+      <c r="AL1" s="203"/>
+      <c r="AM1" s="203"/>
+      <c r="AN1" s="203"/>
+      <c r="AO1" s="203"/>
     </row>
     <row r="2" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
+      <c r="B2" s="172"/>
+      <c r="C2" s="211" t="s">
+        <v>148</v>
+      </c>
+      <c r="D2" s="211"/>
+      <c r="E2" s="211"/>
+      <c r="F2" s="211"/>
+      <c r="G2" s="211"/>
+      <c r="H2" s="211"/>
+      <c r="I2" s="211"/>
+      <c r="J2" s="211"/>
+      <c r="K2" s="211"/>
+      <c r="L2" s="211"/>
+      <c r="M2" s="211"/>
+      <c r="N2" s="211"/>
+      <c r="O2" s="211"/>
+      <c r="P2" s="211"/>
+      <c r="Q2" s="211"/>
+      <c r="R2" s="211"/>
+      <c r="S2" s="211"/>
+      <c r="T2" s="211"/>
+      <c r="U2" s="211"/>
+      <c r="V2" s="211"/>
+      <c r="W2" s="211"/>
+      <c r="X2" s="211"/>
+      <c r="Y2" s="211"/>
+      <c r="Z2" s="211"/>
+      <c r="AA2" s="211"/>
+      <c r="AB2" s="211"/>
+      <c r="AC2" s="211"/>
+      <c r="AD2" s="211"/>
+      <c r="AE2" s="211"/>
+      <c r="AF2" s="211"/>
+      <c r="AG2" s="211"/>
+      <c r="AH2" s="211"/>
+      <c r="AI2" s="211"/>
+      <c r="AJ2" s="211"/>
+      <c r="AK2" s="211"/>
+      <c r="AL2" s="211"/>
+      <c r="AM2" s="211"/>
+      <c r="AN2" s="211"/>
+      <c r="AO2" s="211"/>
     </row>
     <row r="3" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="191" t="s">
+      <c r="B3" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="191" t="s">
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="210"/>
+      <c r="F3" s="208" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="191" t="s">
+      <c r="G3" s="209"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="210"/>
+      <c r="J3" s="208" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="192"/>
-      <c r="L3" s="192"/>
-      <c r="M3" s="193"/>
-      <c r="N3" s="191" t="s">
+      <c r="K3" s="209"/>
+      <c r="L3" s="209"/>
+      <c r="M3" s="210"/>
+      <c r="N3" s="208" t="s">
         <v>97</v>
       </c>
-      <c r="O3" s="192"/>
-      <c r="P3" s="192"/>
-      <c r="Q3" s="193"/>
-      <c r="R3" s="191" t="s">
+      <c r="O3" s="209"/>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="210"/>
+      <c r="R3" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="S3" s="192"/>
-      <c r="T3" s="192"/>
-      <c r="U3" s="193"/>
-      <c r="V3" s="191" t="s">
+      <c r="S3" s="209"/>
+      <c r="T3" s="209"/>
+      <c r="U3" s="210"/>
+      <c r="V3" s="208" t="s">
         <v>95</v>
       </c>
-      <c r="W3" s="192"/>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="193"/>
-      <c r="Z3" s="191" t="s">
+      <c r="W3" s="209"/>
+      <c r="X3" s="209"/>
+      <c r="Y3" s="210"/>
+      <c r="Z3" s="208" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="192"/>
-      <c r="AB3" s="192"/>
-      <c r="AC3" s="193"/>
-      <c r="AD3" s="191" t="s">
+      <c r="AA3" s="209"/>
+      <c r="AB3" s="209"/>
+      <c r="AC3" s="210"/>
+      <c r="AD3" s="208" t="s">
         <v>97</v>
       </c>
-      <c r="AE3" s="192"/>
-      <c r="AF3" s="192"/>
-      <c r="AG3" s="193"/>
-      <c r="AH3" s="191" t="s">
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="209"/>
+      <c r="AG3" s="210"/>
+      <c r="AH3" s="208" t="s">
         <v>98</v>
       </c>
-      <c r="AI3" s="192"/>
-      <c r="AJ3" s="192"/>
-      <c r="AK3" s="193"/>
-      <c r="AL3" s="191" t="s">
+      <c r="AI3" s="209"/>
+      <c r="AJ3" s="209"/>
+      <c r="AK3" s="210"/>
+      <c r="AL3" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="AM3" s="192"/>
-      <c r="AN3" s="192"/>
-      <c r="AO3" s="193"/>
+      <c r="AM3" s="209"/>
+      <c r="AN3" s="209"/>
+      <c r="AO3" s="210"/>
     </row>
     <row r="4" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>46139</v>
       </c>
-      <c r="B4" s="185" t="s">
+      <c r="B4" s="205" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="185" t="s">
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="205" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="185" t="s">
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="205" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="185" t="s">
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="205" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="186"/>
-      <c r="P4" s="186"/>
-      <c r="Q4" s="187"/>
-      <c r="R4" s="185" t="s">
+      <c r="O4" s="206"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="205" t="s">
         <v>103</v>
       </c>
-      <c r="S4" s="186"/>
-      <c r="T4" s="186"/>
-      <c r="U4" s="187"/>
-      <c r="V4" s="185" t="s">
+      <c r="S4" s="206"/>
+      <c r="T4" s="206"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="205" t="s">
         <v>104</v>
       </c>
-      <c r="W4" s="186"/>
-      <c r="X4" s="186"/>
-      <c r="Y4" s="187"/>
-      <c r="Z4" s="185" t="s">
+      <c r="W4" s="206"/>
+      <c r="X4" s="206"/>
+      <c r="Y4" s="207"/>
+      <c r="Z4" s="205" t="s">
         <v>105</v>
       </c>
-      <c r="AA4" s="186"/>
-      <c r="AB4" s="186"/>
-      <c r="AC4" s="187"/>
-      <c r="AD4" s="185" t="s">
+      <c r="AA4" s="206"/>
+      <c r="AB4" s="206"/>
+      <c r="AC4" s="207"/>
+      <c r="AD4" s="205" t="s">
         <v>106</v>
       </c>
-      <c r="AE4" s="186"/>
-      <c r="AF4" s="186"/>
-      <c r="AG4" s="187"/>
-      <c r="AH4" s="185" t="s">
+      <c r="AE4" s="206"/>
+      <c r="AF4" s="206"/>
+      <c r="AG4" s="207"/>
+      <c r="AH4" s="205" t="s">
         <v>107</v>
       </c>
-      <c r="AI4" s="186"/>
-      <c r="AJ4" s="186"/>
-      <c r="AK4" s="187"/>
-      <c r="AL4" s="185" t="s">
+      <c r="AI4" s="206"/>
+      <c r="AJ4" s="206"/>
+      <c r="AK4" s="207"/>
+      <c r="AL4" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="AM4" s="186"/>
-      <c r="AN4" s="186"/>
-      <c r="AO4" s="187"/>
+      <c r="AM4" s="206"/>
+      <c r="AN4" s="206"/>
+      <c r="AO4" s="207"/>
     </row>
     <row r="5" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="126" t="s">
@@ -3734,7 +3979,7 @@
         <v>29</v>
       </c>
       <c r="B10" s="100"/>
-      <c r="C10" s="111"/>
+      <c r="C10" s="169"/>
       <c r="D10" s="111"/>
       <c r="E10" s="112"/>
       <c r="F10" s="111"/>
@@ -3779,15 +4024,15 @@
         <v>30</v>
       </c>
       <c r="B11" s="94"/>
-      <c r="C11" s="42"/>
+      <c r="C11" s="90"/>
       <c r="D11" s="42"/>
       <c r="E11" s="30"/>
-      <c r="F11" s="28"/>
-      <c r="G11" s="29"/>
+      <c r="F11" s="170"/>
+      <c r="G11" s="42"/>
       <c r="H11" s="2"/>
       <c r="I11" s="30"/>
       <c r="J11" s="28"/>
-      <c r="K11" s="29"/>
+      <c r="K11" s="42"/>
       <c r="L11" s="29"/>
       <c r="M11" s="30"/>
       <c r="N11" s="28"/>
@@ -3879,8 +4124,8 @@
       </c>
       <c r="B13" s="70"/>
       <c r="C13" s="25"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="26"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="161"/>
       <c r="F13" s="27"/>
       <c r="G13" s="25"/>
       <c r="H13" s="25"/>
@@ -3989,7 +4234,7 @@
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
       <c r="E15" s="26"/>
-      <c r="F15" s="27"/>
+      <c r="F15" s="171"/>
       <c r="G15" s="25"/>
       <c r="H15" s="25"/>
       <c r="I15" s="26"/>
@@ -4035,7 +4280,7 @@
       <c r="D16" s="25"/>
       <c r="E16" s="26"/>
       <c r="F16" s="27"/>
-      <c r="G16" s="25"/>
+      <c r="G16" s="41"/>
       <c r="H16" s="25"/>
       <c r="I16" s="26"/>
       <c r="J16" s="27"/>
@@ -4081,7 +4326,7 @@
       <c r="E17" s="24"/>
       <c r="F17" s="27"/>
       <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
+      <c r="H17" s="21"/>
       <c r="I17" s="24"/>
       <c r="J17" s="27"/>
       <c r="K17" s="22"/>
@@ -4127,8 +4372,8 @@
       <c r="F18" s="27"/>
       <c r="G18" s="25"/>
       <c r="H18" s="25"/>
-      <c r="I18" s="26"/>
-      <c r="J18" s="27"/>
+      <c r="I18" s="161"/>
+      <c r="J18" s="171"/>
       <c r="K18" s="25"/>
       <c r="L18" s="25"/>
       <c r="M18" s="26"/>
@@ -4218,7 +4463,7 @@
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
       <c r="I20" s="39"/>
-      <c r="J20" s="28"/>
+      <c r="J20" s="170"/>
       <c r="K20" s="29"/>
       <c r="L20" s="29"/>
       <c r="M20" s="39"/>
@@ -4264,7 +4509,7 @@
       <c r="H21" s="25"/>
       <c r="I21" s="26"/>
       <c r="J21" s="27"/>
-      <c r="K21" s="25"/>
+      <c r="K21" s="41"/>
       <c r="L21" s="25"/>
       <c r="M21" s="26"/>
       <c r="N21" s="27"/>
@@ -4310,7 +4555,7 @@
       <c r="I22" s="26"/>
       <c r="J22" s="27"/>
       <c r="K22" s="25"/>
-      <c r="L22" s="25"/>
+      <c r="L22" s="41"/>
       <c r="M22" s="26"/>
       <c r="N22" s="27"/>
       <c r="O22" s="25"/>
@@ -4356,7 +4601,7 @@
       <c r="J23" s="23"/>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
-      <c r="M23" s="24"/>
+      <c r="M23" s="135"/>
       <c r="N23" s="23"/>
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
@@ -4401,8 +4646,8 @@
       <c r="J24" s="27"/>
       <c r="K24" s="25"/>
       <c r="L24" s="25"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="27"/>
+      <c r="M24" s="161"/>
+      <c r="N24" s="171"/>
       <c r="O24" s="25"/>
       <c r="P24" s="25"/>
       <c r="Q24" s="26"/>
@@ -4492,7 +4737,7 @@
       <c r="K26" s="29"/>
       <c r="L26" s="28"/>
       <c r="M26" s="30"/>
-      <c r="N26" s="28"/>
+      <c r="N26" s="170"/>
       <c r="O26" s="29"/>
       <c r="P26" s="28"/>
       <c r="Q26" s="30"/>
@@ -4538,7 +4783,7 @@
       <c r="L27" s="23"/>
       <c r="M27" s="24"/>
       <c r="N27" s="23"/>
-      <c r="O27" s="22"/>
+      <c r="O27" s="21"/>
       <c r="P27" s="23"/>
       <c r="Q27" s="24"/>
       <c r="R27" s="23"/>
@@ -4583,8 +4828,8 @@
       <c r="L28" s="22"/>
       <c r="M28" s="24"/>
       <c r="N28" s="23"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
       <c r="Q28" s="24"/>
       <c r="R28" s="23"/>
       <c r="S28" s="22"/>
@@ -4630,7 +4875,7 @@
       <c r="N29" s="23"/>
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
-      <c r="Q29" s="24"/>
+      <c r="Q29" s="21"/>
       <c r="R29" s="23"/>
       <c r="S29" s="22"/>
       <c r="T29" s="23"/>
@@ -5386,7 +5631,7 @@
       <c r="AO45" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="22">
     <mergeCell ref="A1:AO1"/>
     <mergeCell ref="AL3:AO3"/>
     <mergeCell ref="AH3:AK3"/>
@@ -5394,6 +5639,7 @@
     <mergeCell ref="V3:Y3"/>
     <mergeCell ref="Z3:AC3"/>
     <mergeCell ref="AD3:AG3"/>
+    <mergeCell ref="C2:AO2"/>
     <mergeCell ref="AL4:AO4"/>
     <mergeCell ref="V4:Y4"/>
     <mergeCell ref="Z4:AC4"/>
@@ -5420,213 +5666,247 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E93050-BE04-4DD6-80BE-C2638DEE928D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFE0FE38-922F-4F3A-AE7F-D4CF81484CE2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BH79"/>
+  <dimension ref="A1:BH80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="2" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="52.7109375" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" hidden="1" customWidth="1"/>
     <col min="3" max="42" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="194"/>
-      <c r="Z1" s="194"/>
-      <c r="AA1" s="194"/>
-      <c r="AB1" s="194"/>
-      <c r="AC1" s="194"/>
-      <c r="AD1" s="194"/>
-      <c r="AE1" s="194"/>
-      <c r="AF1" s="194"/>
-      <c r="AG1" s="194"/>
-      <c r="AH1" s="194"/>
-      <c r="AI1" s="194"/>
-      <c r="AJ1" s="194"/>
-      <c r="AK1" s="194"/>
-      <c r="AL1" s="194"/>
-      <c r="AM1" s="194"/>
-      <c r="AN1" s="194"/>
-      <c r="AO1" s="194"/>
-      <c r="AP1" s="194"/>
-    </row>
-    <row r="2" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="203"/>
+      <c r="O1" s="203"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="203"/>
+      <c r="Y1" s="203"/>
+      <c r="Z1" s="203"/>
+      <c r="AA1" s="203"/>
+      <c r="AB1" s="203"/>
+      <c r="AC1" s="203"/>
+      <c r="AD1" s="203"/>
+      <c r="AE1" s="203"/>
+      <c r="AF1" s="203"/>
+      <c r="AG1" s="203"/>
+      <c r="AH1" s="203"/>
+      <c r="AI1" s="203"/>
+      <c r="AJ1" s="203"/>
+      <c r="AK1" s="203"/>
+      <c r="AL1" s="203"/>
+      <c r="AM1" s="203"/>
+      <c r="AN1" s="203"/>
+      <c r="AO1" s="203"/>
+      <c r="AP1" s="203"/>
+    </row>
+    <row r="2" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="173" t="s">
         <v>109</v>
       </c>
       <c r="B2" s="14"/>
-      <c r="C2" s="170" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="170"/>
-      <c r="E2" s="170"/>
-      <c r="F2" s="170"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
+      <c r="I2" s="204"/>
+      <c r="J2" s="204"/>
+      <c r="K2" s="204"/>
+      <c r="L2" s="204"/>
+      <c r="M2" s="204"/>
+      <c r="N2" s="204"/>
+      <c r="O2" s="204"/>
+      <c r="P2" s="204"/>
+      <c r="Q2" s="204"/>
+      <c r="R2" s="204"/>
+      <c r="S2" s="204"/>
+      <c r="T2" s="204"/>
+      <c r="U2" s="204"/>
+      <c r="V2" s="204"/>
+      <c r="W2" s="204"/>
+      <c r="X2" s="204"/>
+      <c r="Y2" s="204"/>
+      <c r="Z2" s="204"/>
+      <c r="AA2" s="204"/>
+      <c r="AB2" s="204"/>
+      <c r="AC2" s="204"/>
+      <c r="AD2" s="204"/>
+      <c r="AE2" s="204"/>
+      <c r="AF2" s="204"/>
+      <c r="AG2" s="204"/>
+      <c r="AH2" s="204"/>
+      <c r="AI2" s="204"/>
+      <c r="AJ2" s="204"/>
+      <c r="AK2" s="204"/>
+      <c r="AL2" s="204"/>
+      <c r="AM2" s="204"/>
+      <c r="AN2" s="204"/>
+      <c r="AO2" s="204"/>
+      <c r="AP2" s="204"/>
     </row>
     <row r="3" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="174" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="15"/>
-      <c r="C3" s="191" t="s">
+      <c r="C3" s="202" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="193"/>
-      <c r="G3" s="191" t="s">
+      <c r="D3" s="202"/>
+      <c r="E3" s="202"/>
+      <c r="F3" s="202"/>
+      <c r="G3" s="202" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="192"/>
-      <c r="I3" s="192"/>
-      <c r="J3" s="193"/>
-      <c r="K3" s="191" t="s">
-        <v>96</v>
-      </c>
-      <c r="L3" s="192"/>
-      <c r="M3" s="192"/>
-      <c r="N3" s="193"/>
-      <c r="O3" s="191" t="s">
+      <c r="H3" s="202"/>
+      <c r="I3" s="202"/>
+      <c r="J3" s="202"/>
+      <c r="K3" s="202" t="s">
+        <v>157</v>
+      </c>
+      <c r="L3" s="202"/>
+      <c r="M3" s="202"/>
+      <c r="N3" s="202"/>
+      <c r="O3" s="202" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="192"/>
-      <c r="Q3" s="192"/>
-      <c r="R3" s="193"/>
-      <c r="S3" s="191" t="s">
+      <c r="P3" s="202"/>
+      <c r="Q3" s="202"/>
+      <c r="R3" s="202"/>
+      <c r="S3" s="202" t="s">
         <v>94</v>
       </c>
-      <c r="T3" s="192"/>
-      <c r="U3" s="192"/>
-      <c r="V3" s="193"/>
-      <c r="W3" s="191" t="s">
+      <c r="T3" s="202"/>
+      <c r="U3" s="202"/>
+      <c r="V3" s="202"/>
+      <c r="W3" s="202" t="s">
         <v>95</v>
       </c>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="192"/>
-      <c r="Z3" s="193"/>
-      <c r="AA3" s="191" t="s">
-        <v>96</v>
-      </c>
-      <c r="AB3" s="192"/>
-      <c r="AC3" s="192"/>
-      <c r="AD3" s="193"/>
-      <c r="AE3" s="191" t="s">
+      <c r="X3" s="202"/>
+      <c r="Y3" s="202"/>
+      <c r="Z3" s="202"/>
+      <c r="AA3" s="202" t="s">
+        <v>157</v>
+      </c>
+      <c r="AB3" s="202"/>
+      <c r="AC3" s="202"/>
+      <c r="AD3" s="202"/>
+      <c r="AE3" s="202" t="s">
         <v>97</v>
       </c>
-      <c r="AF3" s="192"/>
-      <c r="AG3" s="192"/>
-      <c r="AH3" s="193"/>
-      <c r="AI3" s="191" t="s">
+      <c r="AF3" s="202"/>
+      <c r="AG3" s="202"/>
+      <c r="AH3" s="202"/>
+      <c r="AI3" s="202" t="s">
         <v>98</v>
       </c>
-      <c r="AJ3" s="192"/>
-      <c r="AK3" s="192"/>
-      <c r="AL3" s="193"/>
-      <c r="AM3" s="191" t="s">
+      <c r="AJ3" s="202"/>
+      <c r="AK3" s="202"/>
+      <c r="AL3" s="202"/>
+      <c r="AM3" s="202" t="s">
         <v>94</v>
       </c>
-      <c r="AN3" s="192"/>
-      <c r="AO3" s="192"/>
-      <c r="AP3" s="193"/>
+      <c r="AN3" s="202"/>
+      <c r="AO3" s="202"/>
+      <c r="AP3" s="202"/>
     </row>
     <row r="4" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
-        <v>46139</v>
+      <c r="A4" s="175" t="s">
+        <v>162</v>
       </c>
       <c r="B4" s="20"/>
-      <c r="C4" s="185" t="s">
+      <c r="C4" s="196" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="187"/>
-      <c r="G4" s="185" t="s">
+      <c r="D4" s="197"/>
+      <c r="E4" s="197"/>
+      <c r="F4" s="198"/>
+      <c r="G4" s="196" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="187"/>
-      <c r="K4" s="185" t="s">
+      <c r="H4" s="197"/>
+      <c r="I4" s="197"/>
+      <c r="J4" s="198"/>
+      <c r="K4" s="196" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="186"/>
-      <c r="M4" s="186"/>
-      <c r="N4" s="187"/>
-      <c r="O4" s="185" t="s">
+      <c r="L4" s="197"/>
+      <c r="M4" s="197"/>
+      <c r="N4" s="198"/>
+      <c r="O4" s="196" t="s">
         <v>102</v>
       </c>
-      <c r="P4" s="186"/>
-      <c r="Q4" s="186"/>
-      <c r="R4" s="187"/>
-      <c r="S4" s="185" t="s">
+      <c r="P4" s="197"/>
+      <c r="Q4" s="197"/>
+      <c r="R4" s="198"/>
+      <c r="S4" s="196" t="s">
         <v>103</v>
       </c>
-      <c r="T4" s="186"/>
-      <c r="U4" s="186"/>
-      <c r="V4" s="187"/>
-      <c r="W4" s="185" t="s">
+      <c r="T4" s="197"/>
+      <c r="U4" s="197"/>
+      <c r="V4" s="198"/>
+      <c r="W4" s="196" t="s">
         <v>104</v>
       </c>
-      <c r="X4" s="186"/>
-      <c r="Y4" s="186"/>
-      <c r="Z4" s="187"/>
-      <c r="AA4" s="185" t="s">
+      <c r="X4" s="197"/>
+      <c r="Y4" s="197"/>
+      <c r="Z4" s="198"/>
+      <c r="AA4" s="196" t="s">
         <v>105</v>
       </c>
-      <c r="AB4" s="186"/>
-      <c r="AC4" s="186"/>
-      <c r="AD4" s="187"/>
-      <c r="AE4" s="185" t="s">
+      <c r="AB4" s="197"/>
+      <c r="AC4" s="197"/>
+      <c r="AD4" s="198"/>
+      <c r="AE4" s="196" t="s">
         <v>106</v>
       </c>
-      <c r="AF4" s="186"/>
-      <c r="AG4" s="186"/>
-      <c r="AH4" s="187"/>
-      <c r="AI4" s="185" t="s">
+      <c r="AF4" s="197"/>
+      <c r="AG4" s="197"/>
+      <c r="AH4" s="198"/>
+      <c r="AI4" s="196" t="s">
         <v>107</v>
       </c>
-      <c r="AJ4" s="186"/>
-      <c r="AK4" s="186"/>
-      <c r="AL4" s="187"/>
-      <c r="AM4" s="185" t="s">
+      <c r="AJ4" s="197"/>
+      <c r="AK4" s="197"/>
+      <c r="AL4" s="198"/>
+      <c r="AM4" s="196" t="s">
         <v>108</v>
       </c>
-      <c r="AN4" s="186"/>
-      <c r="AO4" s="186"/>
-      <c r="AP4" s="187"/>
+      <c r="AN4" s="197"/>
+      <c r="AO4" s="197"/>
+      <c r="AP4" s="198"/>
     </row>
     <row r="5" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="126" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" s="163" t="s">
+      <c r="A5" s="176" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="162" t="s">
         <v>141</v>
       </c>
       <c r="C5" s="127"/>
@@ -5671,10 +5951,10 @@
       <c r="AP5" s="129"/>
     </row>
     <row r="6" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="125" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="164" t="s">
+      <c r="A6" s="177" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="163" t="s">
         <v>142</v>
       </c>
       <c r="C6" s="103"/>
@@ -5718,8 +5998,8 @@
       <c r="AO6" s="34"/>
       <c r="AP6" s="39"/>
     </row>
-    <row r="7" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="179" t="s">
+    <row r="7" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="199" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="141" t="s">
@@ -5766,12 +6046,12 @@
       <c r="AO7" s="22"/>
       <c r="AP7" s="24"/>
     </row>
-    <row r="8" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="180"/>
+    <row r="8" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="200"/>
       <c r="B8" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="C8" s="21"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="22"/>
       <c r="E8" s="22"/>
       <c r="F8" s="24"/>
@@ -5812,8 +6092,8 @@
       <c r="AO8" s="22"/>
       <c r="AP8" s="24"/>
     </row>
-    <row r="9" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="179" t="s">
+    <row r="9" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="199" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="141" t="s">
@@ -5862,15 +6142,13 @@
       <c r="AO9" s="22"/>
       <c r="AP9" s="24"/>
     </row>
-    <row r="10" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="180"/>
+    <row r="10" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="200"/>
       <c r="B10" s="142" t="s">
         <v>133</v>
       </c>
       <c r="C10" s="23"/>
-      <c r="D10" s="21" t="s">
-        <v>139</v>
-      </c>
+      <c r="D10" s="22"/>
       <c r="E10" s="22"/>
       <c r="F10" s="24"/>
       <c r="G10" s="23"/>
@@ -5910,8 +6188,8 @@
       <c r="AO10" s="22"/>
       <c r="AP10" s="24"/>
     </row>
-    <row r="11" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="179" t="s">
+    <row r="11" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="199" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="141" t="s">
@@ -5959,17 +6237,15 @@
       <c r="AO11" s="31"/>
       <c r="AP11" s="32"/>
     </row>
-    <row r="12" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="190"/>
+    <row r="12" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="201"/>
       <c r="B12" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="27"/>
-      <c r="D12" s="140" t="s">
-        <v>139</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="24"/>
       <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
@@ -6007,11 +6283,11 @@
       <c r="AO12" s="25"/>
       <c r="AP12" s="26"/>
     </row>
-    <row r="13" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="73" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="165" t="s">
+    <row r="13" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="178" t="s">
+        <v>161</v>
+      </c>
+      <c r="B13" s="164" t="s">
         <v>147</v>
       </c>
       <c r="C13" s="96"/>
@@ -6055,8 +6331,8 @@
       <c r="AO13" s="98"/>
       <c r="AP13" s="113"/>
     </row>
-    <row r="14" spans="1:51" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="188" t="s">
+    <row r="14" spans="1:51" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="192" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="141" t="s">
@@ -6112,17 +6388,15 @@
       <c r="AX14" s="2"/>
       <c r="AY14" s="2"/>
     </row>
-    <row r="15" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="189"/>
+    <row r="15" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="193"/>
       <c r="B15" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="28"/>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="F15" s="30"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="24"/>
       <c r="G15" s="28"/>
       <c r="H15" s="29"/>
       <c r="I15" s="29"/>
@@ -6160,8 +6434,8 @@
       <c r="AO15" s="29"/>
       <c r="AP15" s="30"/>
     </row>
-    <row r="16" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="188" t="s">
+    <row r="16" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="192" t="s">
         <v>116</v>
       </c>
       <c r="B16" s="141" t="s">
@@ -6208,17 +6482,15 @@
       <c r="AO16" s="139"/>
       <c r="AP16" s="137"/>
     </row>
-    <row r="17" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="189"/>
+    <row r="17" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="193"/>
       <c r="B17" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="C17" s="27"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="F17" s="26"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="24"/>
       <c r="G17" s="27"/>
       <c r="H17" s="25"/>
       <c r="I17" s="25"/>
@@ -6256,8 +6528,8 @@
       <c r="AO17" s="25"/>
       <c r="AP17" s="26"/>
     </row>
-    <row r="18" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="188" t="s">
+    <row r="18" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="192" t="s">
         <v>92</v>
       </c>
       <c r="B18" s="141" t="s">
@@ -6304,17 +6576,15 @@
       <c r="AO18" s="25"/>
       <c r="AP18" s="26"/>
     </row>
-    <row r="19" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="189"/>
+    <row r="19" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="193"/>
       <c r="B19" s="142" t="s">
         <v>133</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="25"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="22"/>
       <c r="E19" s="22"/>
-      <c r="F19" s="162" t="s">
-        <v>139</v>
-      </c>
+      <c r="F19" s="24"/>
       <c r="G19" s="27"/>
       <c r="H19" s="25"/>
       <c r="I19" s="25"/>
@@ -6352,8 +6622,8 @@
       <c r="AO19" s="25"/>
       <c r="AP19" s="26"/>
     </row>
-    <row r="20" spans="1:60" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="188" t="s">
+    <row r="20" spans="1:60" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="192" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="141" t="s">
@@ -6418,17 +6688,15 @@
       <c r="BG20" s="2"/>
       <c r="BH20" s="2"/>
     </row>
-    <row r="21" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="189"/>
+    <row r="21" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="193"/>
       <c r="B21" s="142" t="s">
         <v>133</v>
       </c>
       <c r="C21" s="23"/>
       <c r="D21" s="22"/>
       <c r="E21" s="22"/>
-      <c r="F21" s="135" t="s">
-        <v>139</v>
-      </c>
+      <c r="F21" s="24"/>
       <c r="G21" s="23"/>
       <c r="H21" s="22"/>
       <c r="I21" s="22"/>
@@ -6466,8 +6734,8 @@
       <c r="AO21" s="22"/>
       <c r="AP21" s="24"/>
     </row>
-    <row r="22" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="188" t="s">
+    <row r="22" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="192" t="s">
         <v>118</v>
       </c>
       <c r="B22" s="141" t="s">
@@ -6514,8 +6782,8 @@
       <c r="AO22" s="31"/>
       <c r="AP22" s="32"/>
     </row>
-    <row r="23" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="189"/>
+    <row r="23" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="193"/>
       <c r="B23" s="142" t="s">
         <v>133</v>
       </c>
@@ -6560,9 +6828,9 @@
       <c r="AO23" s="31"/>
       <c r="AP23" s="26"/>
     </row>
-    <row r="24" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="188" t="s">
-        <v>117</v>
+    <row r="24" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="192" t="s">
+        <v>152</v>
       </c>
       <c r="B24" s="141" t="s">
         <v>132</v>
@@ -6610,8 +6878,8 @@
       <c r="AO24" s="31"/>
       <c r="AP24" s="26"/>
     </row>
-    <row r="25" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="189"/>
+    <row r="25" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="193"/>
       <c r="B25" s="142" t="s">
         <v>133</v>
       </c>
@@ -6656,8 +6924,8 @@
       <c r="AO25" s="25"/>
       <c r="AP25" s="26"/>
     </row>
-    <row r="26" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="188" t="s">
+    <row r="26" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="192" t="s">
         <v>121</v>
       </c>
       <c r="B26" s="141" t="s">
@@ -6706,8 +6974,8 @@
       <c r="AO26" s="31"/>
       <c r="AP26" s="32"/>
     </row>
-    <row r="27" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="189"/>
+    <row r="27" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="193"/>
       <c r="B27" s="142" t="s">
         <v>133</v>
       </c>
@@ -6752,8 +7020,8 @@
       <c r="AO27" s="22"/>
       <c r="AP27" s="24"/>
     </row>
-    <row r="28" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="188" t="s">
+    <row r="28" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="192" t="s">
         <v>122</v>
       </c>
       <c r="B28" s="141" t="s">
@@ -6800,8 +7068,8 @@
       <c r="AO28" s="31"/>
       <c r="AP28" s="32"/>
     </row>
-    <row r="29" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="189"/>
+    <row r="29" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="193"/>
       <c r="B29" s="142" t="s">
         <v>133</v>
       </c>
@@ -6846,11 +7114,11 @@
       <c r="AO29" s="25"/>
       <c r="AP29" s="26"/>
     </row>
-    <row r="30" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="76" t="s">
-        <v>31</v>
-      </c>
-      <c r="B30" s="166" t="s">
+    <row r="30" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="179" t="s">
+        <v>158</v>
+      </c>
+      <c r="B30" s="165" t="s">
         <v>144</v>
       </c>
       <c r="C30" s="96"/>
@@ -6894,9 +7162,9 @@
       <c r="AO30" s="98"/>
       <c r="AP30" s="113"/>
     </row>
-    <row r="31" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="184" t="s">
-        <v>32</v>
+    <row r="31" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="194" t="s">
+        <v>153</v>
       </c>
       <c r="B31" s="141" t="s">
         <v>132</v>
@@ -6942,8 +7210,8 @@
       <c r="AO31" s="29"/>
       <c r="AP31" s="39"/>
     </row>
-    <row r="32" spans="1:60" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="182"/>
+    <row r="32" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="191"/>
       <c r="B32" s="142" t="s">
         <v>133</v>
       </c>
@@ -6988,8 +7256,8 @@
       <c r="AO32" s="139"/>
       <c r="AP32" s="137"/>
     </row>
-    <row r="33" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="181" t="s">
+    <row r="33" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="190" t="s">
         <v>110</v>
       </c>
       <c r="B33" s="141" t="s">
@@ -7038,8 +7306,8 @@
       <c r="AO33" s="25"/>
       <c r="AP33" s="26"/>
     </row>
-    <row r="34" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="182"/>
+    <row r="34" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="191"/>
       <c r="B34" s="142" t="s">
         <v>133</v>
       </c>
@@ -7084,9 +7352,9 @@
       <c r="AO34" s="25"/>
       <c r="AP34" s="26"/>
     </row>
-    <row r="35" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="181" t="s">
-        <v>111</v>
+    <row r="35" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="190" t="s">
+        <v>151</v>
       </c>
       <c r="B35" s="141" t="s">
         <v>132</v>
@@ -7134,8 +7402,8 @@
       <c r="AO35" s="25"/>
       <c r="AP35" s="26"/>
     </row>
-    <row r="36" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="183"/>
+    <row r="36" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="195"/>
       <c r="B36" s="142" t="s">
         <v>133</v>
       </c>
@@ -7180,9 +7448,9 @@
       <c r="AO36" s="31"/>
       <c r="AP36" s="32"/>
     </row>
-    <row r="37" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="181" t="s">
-        <v>112</v>
+    <row r="37" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="190" t="s">
+        <v>154</v>
       </c>
       <c r="B37" s="141" t="s">
         <v>132</v>
@@ -7230,8 +7498,8 @@
       <c r="AO37" s="22"/>
       <c r="AP37" s="24"/>
     </row>
-    <row r="38" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="182"/>
+    <row r="38" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="191"/>
       <c r="B38" s="142" t="s">
         <v>133</v>
       </c>
@@ -7276,8 +7544,8 @@
       <c r="AO38" s="31"/>
       <c r="AP38" s="32"/>
     </row>
-    <row r="39" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="181" t="s">
+    <row r="39" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="190" t="s">
         <v>113</v>
       </c>
       <c r="B39" s="141" t="s">
@@ -7296,7 +7564,7 @@
       <c r="M39" s="31"/>
       <c r="N39" s="32"/>
       <c r="O39" s="31"/>
-      <c r="P39" s="148" t="s">
+      <c r="P39" s="183" t="s">
         <v>139</v>
       </c>
       <c r="Q39" s="31"/>
@@ -7326,8 +7594,8 @@
       <c r="AO39" s="31"/>
       <c r="AP39" s="32"/>
     </row>
-    <row r="40" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="182"/>
+    <row r="40" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="191"/>
       <c r="B40" s="142" t="s">
         <v>133</v>
       </c>
@@ -7344,7 +7612,7 @@
       <c r="M40" s="31"/>
       <c r="N40" s="32"/>
       <c r="O40" s="31"/>
-      <c r="P40" s="31"/>
+      <c r="P40" s="139"/>
       <c r="Q40" s="31"/>
       <c r="R40" s="32"/>
       <c r="S40" s="31"/>
@@ -7372,11 +7640,11 @@
       <c r="AO40" s="31"/>
       <c r="AP40" s="32"/>
     </row>
-    <row r="41" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="147" t="s">
-        <v>33</v>
-      </c>
-      <c r="B41" s="167" t="s">
+    <row r="41" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="180" t="s">
+        <v>164</v>
+      </c>
+      <c r="B41" s="166" t="s">
         <v>145</v>
       </c>
       <c r="C41" s="96"/>
@@ -7395,7 +7663,7 @@
       <c r="P41" s="98"/>
       <c r="Q41" s="118"/>
       <c r="R41" s="119"/>
-      <c r="S41" s="158"/>
+      <c r="S41" s="157"/>
       <c r="T41" s="118"/>
       <c r="U41" s="118"/>
       <c r="V41" s="119"/>
@@ -7420,8 +7688,8 @@
       <c r="AO41" s="98"/>
       <c r="AP41" s="113"/>
     </row>
-    <row r="42" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="171" t="s">
+    <row r="42" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="187" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="141" t="s">
@@ -7441,9 +7709,9 @@
       <c r="N42" s="30"/>
       <c r="O42" s="94"/>
       <c r="P42" s="29"/>
-      <c r="Q42" s="157"/>
+      <c r="Q42" s="156"/>
       <c r="R42" s="30"/>
-      <c r="S42" s="159"/>
+      <c r="S42" s="158"/>
       <c r="T42" s="29"/>
       <c r="U42" s="29"/>
       <c r="V42" s="30"/>
@@ -7468,8 +7736,8 @@
       <c r="AO42" s="29"/>
       <c r="AP42" s="30"/>
     </row>
-    <row r="43" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="172"/>
+    <row r="43" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="188"/>
       <c r="B43" s="142" t="s">
         <v>133</v>
       </c>
@@ -7514,8 +7782,8 @@
       <c r="AO43" s="29"/>
       <c r="AP43" s="30"/>
     </row>
-    <row r="44" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="171" t="s">
+    <row r="44" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="187" t="s">
         <v>115</v>
       </c>
       <c r="B44" s="141" t="s">
@@ -7562,8 +7830,8 @@
       <c r="AO44" s="22"/>
       <c r="AP44" s="24"/>
     </row>
-    <row r="45" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="172"/>
+    <row r="45" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="188"/>
       <c r="B45" s="142" t="s">
         <v>133</v>
       </c>
@@ -7608,8 +7876,8 @@
       <c r="AO45" s="22"/>
       <c r="AP45" s="24"/>
     </row>
-    <row r="46" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="171" t="s">
+    <row r="46" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="187" t="s">
         <v>123</v>
       </c>
       <c r="B46" s="141" t="s">
@@ -7632,7 +7900,7 @@
       <c r="Q46" s="22"/>
       <c r="R46" s="24"/>
       <c r="S46" s="153"/>
-      <c r="T46" s="160"/>
+      <c r="T46" s="159"/>
       <c r="U46" s="23"/>
       <c r="V46" s="23"/>
       <c r="W46" s="93"/>
@@ -7656,8 +7924,8 @@
       <c r="AO46" s="22"/>
       <c r="AP46" s="24"/>
     </row>
-    <row r="47" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="172"/>
+    <row r="47" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="188"/>
       <c r="B47" s="142" t="s">
         <v>133</v>
       </c>
@@ -7702,8 +7970,8 @@
       <c r="AO47" s="22"/>
       <c r="AP47" s="24"/>
     </row>
-    <row r="48" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="171" t="s">
+    <row r="48" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="187" t="s">
         <v>124</v>
       </c>
       <c r="B48" s="141" t="s">
@@ -7727,7 +7995,7 @@
       <c r="R48" s="24"/>
       <c r="S48" s="93"/>
       <c r="T48" s="22"/>
-      <c r="U48" s="160"/>
+      <c r="U48" s="159"/>
       <c r="V48" s="151"/>
       <c r="W48" s="23"/>
       <c r="X48" s="23"/>
@@ -7750,8 +8018,8 @@
       <c r="AO48" s="22"/>
       <c r="AP48" s="24"/>
     </row>
-    <row r="49" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="172"/>
+    <row r="49" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="188"/>
       <c r="B49" s="142" t="s">
         <v>133</v>
       </c>
@@ -7796,8 +8064,8 @@
       <c r="AO49" s="31"/>
       <c r="AP49" s="32"/>
     </row>
-    <row r="50" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="171" t="s">
+    <row r="50" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="187" t="s">
         <v>119</v>
       </c>
       <c r="B50" s="141" t="s">
@@ -7823,7 +8091,7 @@
       <c r="T50" s="25"/>
       <c r="U50" s="25"/>
       <c r="V50" s="26"/>
-      <c r="W50" s="161"/>
+      <c r="W50" s="160"/>
       <c r="X50" s="25"/>
       <c r="Y50" s="23"/>
       <c r="Z50" s="26"/>
@@ -7844,8 +8112,8 @@
       <c r="AO50" s="25"/>
       <c r="AP50" s="26"/>
     </row>
-    <row r="51" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="172"/>
+    <row r="51" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="188"/>
       <c r="B51" s="142" t="s">
         <v>133</v>
       </c>
@@ -7890,8 +8158,8 @@
       <c r="AO51" s="31"/>
       <c r="AP51" s="32"/>
     </row>
-    <row r="52" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="171" t="s">
+    <row r="52" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="187" t="s">
         <v>125</v>
       </c>
       <c r="B52" s="141" t="s">
@@ -7918,7 +8186,7 @@
       <c r="U52" s="22"/>
       <c r="V52" s="24"/>
       <c r="W52" s="93"/>
-      <c r="X52" s="160"/>
+      <c r="X52" s="159"/>
       <c r="Y52" s="22"/>
       <c r="Z52" s="23"/>
       <c r="AA52" s="93"/>
@@ -7938,8 +8206,8 @@
       <c r="AO52" s="22"/>
       <c r="AP52" s="24"/>
     </row>
-    <row r="53" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="172"/>
+    <row r="53" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="188"/>
       <c r="B53" s="142" t="s">
         <v>133</v>
       </c>
@@ -7984,9 +8252,9 @@
       <c r="AO53" s="22"/>
       <c r="AP53" s="24"/>
     </row>
-    <row r="54" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="171" t="s">
-        <v>126</v>
+    <row r="54" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="187" t="s">
+        <v>150</v>
       </c>
       <c r="B54" s="141" t="s">
         <v>132</v>
@@ -8013,7 +8281,7 @@
       <c r="V54" s="24"/>
       <c r="W54" s="93"/>
       <c r="X54" s="22"/>
-      <c r="Y54" s="160"/>
+      <c r="Y54" s="159"/>
       <c r="Z54" s="151"/>
       <c r="AA54" s="148"/>
       <c r="AB54" s="22"/>
@@ -8032,8 +8300,8 @@
       <c r="AO54" s="22"/>
       <c r="AP54" s="24"/>
     </row>
-    <row r="55" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="172"/>
+    <row r="55" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="188"/>
       <c r="B55" s="142" t="s">
         <v>133</v>
       </c>
@@ -8078,8 +8346,8 @@
       <c r="AO55" s="31"/>
       <c r="AP55" s="32"/>
     </row>
-    <row r="56" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="171" t="s">
+    <row r="56" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="187" t="s">
         <v>129</v>
       </c>
       <c r="B56" s="141" t="s">
@@ -8126,8 +8394,8 @@
       <c r="AO56" s="31"/>
       <c r="AP56" s="32"/>
     </row>
-    <row r="57" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="172"/>
+    <row r="57" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="188"/>
       <c r="B57" s="142" t="s">
         <v>133</v>
       </c>
@@ -8172,8 +8440,8 @@
       <c r="AO57" s="31"/>
       <c r="AP57" s="32"/>
     </row>
-    <row r="58" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="171" t="s">
+    <row r="58" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="187" t="s">
         <v>127</v>
       </c>
       <c r="B58" s="141" t="s">
@@ -8220,8 +8488,8 @@
       <c r="AO58" s="25"/>
       <c r="AP58" s="26"/>
     </row>
-    <row r="59" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="172"/>
+    <row r="59" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="188"/>
       <c r="B59" s="142" t="s">
         <v>133</v>
       </c>
@@ -8266,8 +8534,8 @@
       <c r="AO59" s="31"/>
       <c r="AP59" s="32"/>
     </row>
-    <row r="60" spans="1:51" s="40" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="171" t="s">
+    <row r="60" spans="1:51" s="40" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="187" t="s">
         <v>128</v>
       </c>
       <c r="B60" s="141" t="s">
@@ -8323,8 +8591,8 @@
       <c r="AX60" s="2"/>
       <c r="AY60" s="2"/>
     </row>
-    <row r="61" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="178"/>
+    <row r="61" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="189"/>
       <c r="B61" s="142" t="s">
         <v>133</v>
       </c>
@@ -8369,11 +8637,11 @@
       <c r="AO61" s="25"/>
       <c r="AP61" s="26"/>
     </row>
-    <row r="62" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="82" t="s">
-        <v>40</v>
-      </c>
-      <c r="B62" s="168" t="s">
+    <row r="62" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="181" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" s="167" t="s">
         <v>146</v>
       </c>
       <c r="C62" s="96"/>
@@ -8417,9 +8685,9 @@
       <c r="AO62" s="98"/>
       <c r="AP62" s="113"/>
     </row>
-    <row r="63" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="175" t="s">
-        <v>45</v>
+    <row r="63" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="184" t="s">
+        <v>155</v>
       </c>
       <c r="B63" s="141" t="s">
         <v>132</v>
@@ -8465,8 +8733,8 @@
       <c r="AO63" s="29"/>
       <c r="AP63" s="30"/>
     </row>
-    <row r="64" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="177"/>
+    <row r="64" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="185"/>
       <c r="B64" s="142" t="s">
         <v>133</v>
       </c>
@@ -8511,9 +8779,9 @@
       <c r="AO64" s="29"/>
       <c r="AP64" s="30"/>
     </row>
-    <row r="65" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="175" t="s">
-        <v>46</v>
+    <row r="65" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="184" t="s">
+        <v>156</v>
       </c>
       <c r="B65" s="141" t="s">
         <v>132</v>
@@ -8559,8 +8827,8 @@
       <c r="AO65" s="22"/>
       <c r="AP65" s="24"/>
     </row>
-    <row r="66" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="177"/>
+    <row r="66" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="185"/>
       <c r="B66" s="142" t="s">
         <v>133</v>
       </c>
@@ -8605,8 +8873,8 @@
       <c r="AO66" s="31"/>
       <c r="AP66" s="32"/>
     </row>
-    <row r="67" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="175" t="s">
+    <row r="67" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="184" t="s">
         <v>120</v>
       </c>
       <c r="B67" s="141" t="s">
@@ -8653,8 +8921,8 @@
       <c r="AO67" s="22"/>
       <c r="AP67" s="24"/>
     </row>
-    <row r="68" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="176"/>
+    <row r="68" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="186"/>
       <c r="B68" s="142" t="s">
         <v>133</v>
       </c>
@@ -8699,11 +8967,11 @@
       <c r="AO68" s="139"/>
       <c r="AP68" s="143"/>
     </row>
-    <row r="69" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="85" t="s">
-        <v>42</v>
-      </c>
-      <c r="B69" s="169" t="s">
+    <row r="69" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="182" t="s">
+        <v>165</v>
+      </c>
+      <c r="B69" s="168" t="s">
         <v>143</v>
       </c>
       <c r="C69" s="96"/>
@@ -8747,8 +9015,8 @@
       <c r="AO69" s="102"/>
       <c r="AP69" s="102"/>
     </row>
-    <row r="70" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="173" t="s">
+    <row r="70" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="260" t="s">
         <v>130</v>
       </c>
       <c r="B70" s="141" t="s">
@@ -8795,8 +9063,8 @@
       <c r="AO70" s="29"/>
       <c r="AP70" s="91"/>
     </row>
-    <row r="71" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="174"/>
+    <row r="71" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="261"/>
       <c r="B71" s="142" t="s">
         <v>133</v>
       </c>
@@ -8841,8 +9109,8 @@
       <c r="AO71" s="29"/>
       <c r="AP71" s="91"/>
     </row>
-    <row r="72" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="173" t="s">
+    <row r="72" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="260" t="s">
         <v>131</v>
       </c>
       <c r="B72" s="141" t="s">
@@ -8889,8 +9157,8 @@
       <c r="AO72" s="22"/>
       <c r="AP72" s="18"/>
     </row>
-    <row r="73" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="174"/>
+    <row r="73" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="261"/>
       <c r="B73" s="142" t="s">
         <v>133</v>
       </c>
@@ -8935,8 +9203,8 @@
       <c r="AO73" s="22"/>
       <c r="AP73" s="18"/>
     </row>
-    <row r="74" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="173" t="s">
+    <row r="74" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="260" t="s">
         <v>135</v>
       </c>
       <c r="B74" s="141" t="s">
@@ -8976,15 +9244,17 @@
       <c r="AH74" s="18"/>
       <c r="AI74" s="146"/>
       <c r="AJ74" s="154"/>
-      <c r="AK74" s="155"/>
-      <c r="AL74" s="156"/>
-      <c r="AM74" s="148"/>
+      <c r="AK74" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL74" s="18"/>
+      <c r="AM74" s="23"/>
       <c r="AN74" s="3"/>
       <c r="AO74" s="22"/>
       <c r="AP74" s="18"/>
     </row>
-    <row r="75" spans="1:42" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="174"/>
+    <row r="75" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="261"/>
       <c r="B75" s="142" t="s">
         <v>133</v>
       </c>
@@ -9029,8 +9299,8 @@
       <c r="AO75" s="22"/>
       <c r="AP75" s="18"/>
     </row>
-    <row r="76" spans="1:42" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="173" t="s">
+    <row r="76" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="260" t="s">
         <v>136</v>
       </c>
       <c r="B76" s="141" t="s">
@@ -9070,15 +9340,19 @@
       <c r="AH76" s="18"/>
       <c r="AI76" s="23"/>
       <c r="AJ76" s="3"/>
-      <c r="AK76" s="22"/>
-      <c r="AL76" s="18"/>
+      <c r="AK76" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL76" s="256" t="s">
+        <v>139</v>
+      </c>
       <c r="AM76" s="23"/>
-      <c r="AN76" s="148"/>
+      <c r="AN76" s="3"/>
       <c r="AO76" s="22"/>
       <c r="AP76" s="18"/>
     </row>
-    <row r="77" spans="1:42" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="174"/>
+    <row r="77" spans="1:42" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="261"/>
       <c r="B77" s="142" t="s">
         <v>133</v>
       </c>
@@ -9123,8 +9397,3964 @@
       <c r="AO77" s="31"/>
       <c r="AP77" s="145"/>
     </row>
-    <row r="78" spans="1:42" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="173" t="s">
+    <row r="78" spans="1:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="260" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C78" s="70"/>
+      <c r="D78" s="43"/>
+      <c r="E78" s="25"/>
+      <c r="F78" s="44"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="43"/>
+      <c r="I78" s="25"/>
+      <c r="J78" s="44"/>
+      <c r="K78" s="27"/>
+      <c r="L78" s="43"/>
+      <c r="M78" s="25"/>
+      <c r="N78" s="44"/>
+      <c r="O78" s="27"/>
+      <c r="P78" s="43"/>
+      <c r="Q78" s="25"/>
+      <c r="R78" s="44"/>
+      <c r="S78" s="27"/>
+      <c r="T78" s="43"/>
+      <c r="U78" s="25"/>
+      <c r="V78" s="44"/>
+      <c r="W78" s="25"/>
+      <c r="X78" s="43"/>
+      <c r="Y78" s="25"/>
+      <c r="Z78" s="44"/>
+      <c r="AA78" s="25"/>
+      <c r="AB78" s="43"/>
+      <c r="AC78" s="25"/>
+      <c r="AD78" s="44"/>
+      <c r="AE78" s="27"/>
+      <c r="AF78" s="43"/>
+      <c r="AG78" s="25"/>
+      <c r="AH78" s="44"/>
+      <c r="AI78" s="27"/>
+      <c r="AJ78" s="43"/>
+      <c r="AK78" s="25"/>
+      <c r="AL78" s="257" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM78" s="27"/>
+      <c r="AN78" s="43"/>
+      <c r="AO78" s="25"/>
+      <c r="AP78" s="44"/>
+    </row>
+    <row r="79" spans="1:42" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="261"/>
+      <c r="B79" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C79" s="109"/>
+      <c r="D79" s="254"/>
+      <c r="E79" s="90"/>
+      <c r="F79" s="255"/>
+      <c r="G79" s="109"/>
+      <c r="H79" s="254"/>
+      <c r="I79" s="90"/>
+      <c r="J79" s="255"/>
+      <c r="K79" s="109"/>
+      <c r="L79" s="254"/>
+      <c r="M79" s="90"/>
+      <c r="N79" s="255"/>
+      <c r="O79" s="109"/>
+      <c r="P79" s="254"/>
+      <c r="Q79" s="90"/>
+      <c r="R79" s="255"/>
+      <c r="S79" s="109"/>
+      <c r="T79" s="254"/>
+      <c r="U79" s="90"/>
+      <c r="V79" s="255"/>
+      <c r="W79" s="90"/>
+      <c r="X79" s="254"/>
+      <c r="Y79" s="90"/>
+      <c r="Z79" s="255"/>
+      <c r="AA79" s="90"/>
+      <c r="AB79" s="254"/>
+      <c r="AC79" s="90"/>
+      <c r="AD79" s="255"/>
+      <c r="AE79" s="109"/>
+      <c r="AF79" s="254"/>
+      <c r="AG79" s="90"/>
+      <c r="AH79" s="255"/>
+      <c r="AI79" s="109"/>
+      <c r="AJ79" s="254"/>
+      <c r="AK79" s="90"/>
+      <c r="AL79" s="255"/>
+      <c r="AM79" s="109"/>
+      <c r="AN79" s="254"/>
+      <c r="AO79" s="90"/>
+      <c r="AP79" s="255"/>
+    </row>
+    <row r="80" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="250" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="168" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="96"/>
+      <c r="D80" s="97"/>
+      <c r="E80" s="98"/>
+      <c r="F80" s="99"/>
+      <c r="G80" s="100"/>
+      <c r="H80" s="97"/>
+      <c r="I80" s="98"/>
+      <c r="J80" s="99"/>
+      <c r="K80" s="100"/>
+      <c r="L80" s="97"/>
+      <c r="M80" s="98"/>
+      <c r="N80" s="99"/>
+      <c r="O80" s="100"/>
+      <c r="P80" s="97"/>
+      <c r="Q80" s="98"/>
+      <c r="R80" s="99"/>
+      <c r="S80" s="100"/>
+      <c r="T80" s="97"/>
+      <c r="U80" s="98"/>
+      <c r="V80" s="99"/>
+      <c r="W80" s="98"/>
+      <c r="X80" s="97"/>
+      <c r="Y80" s="98"/>
+      <c r="Z80" s="99"/>
+      <c r="AA80" s="100"/>
+      <c r="AB80" s="97"/>
+      <c r="AC80" s="98"/>
+      <c r="AD80" s="99"/>
+      <c r="AE80" s="100"/>
+      <c r="AF80" s="97"/>
+      <c r="AG80" s="98"/>
+      <c r="AH80" s="99"/>
+      <c r="AI80" s="100"/>
+      <c r="AJ80" s="97"/>
+      <c r="AK80" s="98"/>
+      <c r="AL80" s="99"/>
+      <c r="AM80" s="251"/>
+      <c r="AN80" s="252"/>
+      <c r="AO80" s="251"/>
+      <c r="AP80" s="253"/>
+    </row>
+  </sheetData>
+  <mergeCells count="52">
+    <mergeCell ref="A1:AP1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:AP2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="K3:N3"/>
+    <mergeCell ref="O3:R3"/>
+    <mergeCell ref="S3:V3"/>
+    <mergeCell ref="W3:Z3"/>
+    <mergeCell ref="AA3:AD3"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI3:AL3"/>
+    <mergeCell ref="AM3:AP3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="G4:J4"/>
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="O4:R4"/>
+    <mergeCell ref="S4:V4"/>
+    <mergeCell ref="W4:Z4"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI4:AL4"/>
+    <mergeCell ref="AM4:AP4"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A63:A64"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A44:A45"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A58:A59"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="60" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter differentFirst="1" scaleWithDoc="0">
+    <oddFooter>Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99E93050-BE04-4DD6-80BE-C2638DEE928D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:BH80"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="42.85546875" customWidth="1"/>
+    <col min="2" max="2" width="7.5703125" customWidth="1"/>
+    <col min="3" max="42" width="2.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:51" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="203" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="203"/>
+      <c r="O1" s="203"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="203"/>
+      <c r="Y1" s="203"/>
+      <c r="Z1" s="203"/>
+      <c r="AA1" s="203"/>
+      <c r="AB1" s="203"/>
+      <c r="AC1" s="203"/>
+      <c r="AD1" s="203"/>
+      <c r="AE1" s="203"/>
+      <c r="AF1" s="203"/>
+      <c r="AG1" s="203"/>
+      <c r="AH1" s="203"/>
+      <c r="AI1" s="203"/>
+      <c r="AJ1" s="203"/>
+      <c r="AK1" s="203"/>
+      <c r="AL1" s="203"/>
+      <c r="AM1" s="203"/>
+      <c r="AN1" s="203"/>
+      <c r="AO1" s="203"/>
+      <c r="AP1" s="203"/>
+    </row>
+    <row r="2" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="14"/>
+      <c r="C2" s="227" t="s">
+        <v>140</v>
+      </c>
+      <c r="D2" s="228"/>
+      <c r="E2" s="227" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2" s="229"/>
+      <c r="G2" s="229"/>
+      <c r="H2" s="229"/>
+      <c r="I2" s="229"/>
+      <c r="J2" s="229"/>
+      <c r="K2" s="229"/>
+      <c r="L2" s="229"/>
+      <c r="M2" s="229"/>
+      <c r="N2" s="229"/>
+      <c r="O2" s="229"/>
+      <c r="P2" s="229"/>
+      <c r="Q2" s="229"/>
+      <c r="R2" s="229"/>
+      <c r="S2" s="229"/>
+      <c r="T2" s="229"/>
+      <c r="U2" s="229"/>
+      <c r="V2" s="229"/>
+      <c r="W2" s="229"/>
+      <c r="X2" s="229"/>
+      <c r="Y2" s="229"/>
+      <c r="Z2" s="229"/>
+      <c r="AA2" s="229"/>
+      <c r="AB2" s="229"/>
+      <c r="AC2" s="229"/>
+      <c r="AD2" s="229"/>
+      <c r="AE2" s="229"/>
+      <c r="AF2" s="229"/>
+      <c r="AG2" s="229"/>
+      <c r="AH2" s="229"/>
+      <c r="AI2" s="229"/>
+      <c r="AJ2" s="229"/>
+      <c r="AK2" s="229"/>
+      <c r="AL2" s="229"/>
+      <c r="AM2" s="229"/>
+      <c r="AN2" s="229"/>
+      <c r="AO2" s="229"/>
+      <c r="AP2" s="228"/>
+    </row>
+    <row r="3" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="15"/>
+      <c r="C3" s="208" t="s">
+        <v>94</v>
+      </c>
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="208" t="s">
+        <v>95</v>
+      </c>
+      <c r="H3" s="209"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="210"/>
+      <c r="K3" s="208" t="s">
+        <v>96</v>
+      </c>
+      <c r="L3" s="209"/>
+      <c r="M3" s="209"/>
+      <c r="N3" s="210"/>
+      <c r="O3" s="208" t="s">
+        <v>97</v>
+      </c>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="209"/>
+      <c r="R3" s="210"/>
+      <c r="S3" s="208" t="s">
+        <v>94</v>
+      </c>
+      <c r="T3" s="209"/>
+      <c r="U3" s="209"/>
+      <c r="V3" s="210"/>
+      <c r="W3" s="208" t="s">
+        <v>95</v>
+      </c>
+      <c r="X3" s="209"/>
+      <c r="Y3" s="209"/>
+      <c r="Z3" s="210"/>
+      <c r="AA3" s="208" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB3" s="209"/>
+      <c r="AC3" s="209"/>
+      <c r="AD3" s="210"/>
+      <c r="AE3" s="208" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF3" s="209"/>
+      <c r="AG3" s="209"/>
+      <c r="AH3" s="210"/>
+      <c r="AI3" s="208" t="s">
+        <v>98</v>
+      </c>
+      <c r="AJ3" s="209"/>
+      <c r="AK3" s="209"/>
+      <c r="AL3" s="210"/>
+      <c r="AM3" s="208" t="s">
+        <v>94</v>
+      </c>
+      <c r="AN3" s="209"/>
+      <c r="AO3" s="209"/>
+      <c r="AP3" s="210"/>
+    </row>
+    <row r="4" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
+        <v>46139</v>
+      </c>
+      <c r="B4" s="20"/>
+      <c r="C4" s="205" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="206"/>
+      <c r="E4" s="206"/>
+      <c r="F4" s="207"/>
+      <c r="G4" s="205" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="206"/>
+      <c r="I4" s="206"/>
+      <c r="J4" s="207"/>
+      <c r="K4" s="205" t="s">
+        <v>101</v>
+      </c>
+      <c r="L4" s="206"/>
+      <c r="M4" s="206"/>
+      <c r="N4" s="207"/>
+      <c r="O4" s="205" t="s">
+        <v>102</v>
+      </c>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="206"/>
+      <c r="R4" s="207"/>
+      <c r="S4" s="205" t="s">
+        <v>103</v>
+      </c>
+      <c r="T4" s="206"/>
+      <c r="U4" s="206"/>
+      <c r="V4" s="207"/>
+      <c r="W4" s="205" t="s">
+        <v>104</v>
+      </c>
+      <c r="X4" s="206"/>
+      <c r="Y4" s="206"/>
+      <c r="Z4" s="207"/>
+      <c r="AA4" s="205" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB4" s="206"/>
+      <c r="AC4" s="206"/>
+      <c r="AD4" s="207"/>
+      <c r="AE4" s="205" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF4" s="206"/>
+      <c r="AG4" s="206"/>
+      <c r="AH4" s="207"/>
+      <c r="AI4" s="205" t="s">
+        <v>107</v>
+      </c>
+      <c r="AJ4" s="206"/>
+      <c r="AK4" s="206"/>
+      <c r="AL4" s="207"/>
+      <c r="AM4" s="205" t="s">
+        <v>108</v>
+      </c>
+      <c r="AN4" s="206"/>
+      <c r="AO4" s="206"/>
+      <c r="AP4" s="207"/>
+    </row>
+    <row r="5" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="126" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="162" t="s">
+        <v>141</v>
+      </c>
+      <c r="C5" s="127"/>
+      <c r="D5" s="128"/>
+      <c r="E5" s="128"/>
+      <c r="F5" s="129"/>
+      <c r="G5" s="128"/>
+      <c r="H5" s="128"/>
+      <c r="I5" s="128"/>
+      <c r="J5" s="130"/>
+      <c r="K5" s="131"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="128"/>
+      <c r="N5" s="129"/>
+      <c r="O5" s="131"/>
+      <c r="P5" s="128"/>
+      <c r="Q5" s="128"/>
+      <c r="R5" s="129"/>
+      <c r="S5" s="128"/>
+      <c r="T5" s="128"/>
+      <c r="U5" s="128"/>
+      <c r="V5" s="129"/>
+      <c r="W5" s="127"/>
+      <c r="X5" s="128"/>
+      <c r="Y5" s="128"/>
+      <c r="Z5" s="128"/>
+      <c r="AA5" s="128"/>
+      <c r="AB5" s="128"/>
+      <c r="AC5" s="128"/>
+      <c r="AD5" s="128"/>
+      <c r="AE5" s="128"/>
+      <c r="AF5" s="128"/>
+      <c r="AG5" s="128"/>
+      <c r="AH5" s="128"/>
+      <c r="AI5" s="128"/>
+      <c r="AJ5" s="128"/>
+      <c r="AK5" s="128"/>
+      <c r="AL5" s="128"/>
+      <c r="AM5" s="128"/>
+      <c r="AN5" s="128"/>
+      <c r="AO5" s="128"/>
+      <c r="AP5" s="129"/>
+    </row>
+    <row r="6" spans="1:51" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="125" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="163" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="103"/>
+      <c r="D6" s="104"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="35"/>
+      <c r="H6" s="34"/>
+      <c r="I6" s="34"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="34"/>
+      <c r="X6" s="106"/>
+      <c r="Y6" s="34"/>
+      <c r="Z6" s="39"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="34"/>
+      <c r="AC6" s="34"/>
+      <c r="AD6" s="39"/>
+      <c r="AE6" s="35"/>
+      <c r="AF6" s="34"/>
+      <c r="AG6" s="34"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="35"/>
+      <c r="AJ6" s="34"/>
+      <c r="AK6" s="34"/>
+      <c r="AL6" s="107"/>
+      <c r="AM6" s="35"/>
+      <c r="AN6" s="34"/>
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="39"/>
+    </row>
+    <row r="7" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="214" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="148"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="23"/>
+      <c r="T7" s="22"/>
+      <c r="U7" s="22"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="23"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="22"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="23"/>
+      <c r="AB7" s="22"/>
+      <c r="AC7" s="22"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="23"/>
+      <c r="AF7" s="22"/>
+      <c r="AG7" s="22"/>
+      <c r="AH7" s="24"/>
+      <c r="AI7" s="23"/>
+      <c r="AJ7" s="22"/>
+      <c r="AK7" s="22"/>
+      <c r="AL7" s="24"/>
+      <c r="AM7" s="23"/>
+      <c r="AN7" s="22"/>
+      <c r="AO7" s="22"/>
+      <c r="AP7" s="24"/>
+    </row>
+    <row r="8" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="215"/>
+      <c r="B8" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="23"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="23"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="23"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="23"/>
+      <c r="T8" s="22"/>
+      <c r="U8" s="22"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="22"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="23"/>
+      <c r="AB8" s="22"/>
+      <c r="AC8" s="22"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="23"/>
+      <c r="AF8" s="22"/>
+      <c r="AG8" s="22"/>
+      <c r="AH8" s="24"/>
+      <c r="AI8" s="23"/>
+      <c r="AJ8" s="22"/>
+      <c r="AK8" s="22"/>
+      <c r="AL8" s="24"/>
+      <c r="AM8" s="23"/>
+      <c r="AN8" s="22"/>
+      <c r="AO8" s="22"/>
+      <c r="AP8" s="24"/>
+    </row>
+    <row r="9" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="214" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="E9" s="22"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="23"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="23"/>
+      <c r="T9" s="22"/>
+      <c r="U9" s="22"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="23"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="22"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="23"/>
+      <c r="AB9" s="22"/>
+      <c r="AC9" s="22"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="23"/>
+      <c r="AF9" s="22"/>
+      <c r="AG9" s="22"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="23"/>
+      <c r="AJ9" s="22"/>
+      <c r="AK9" s="22"/>
+      <c r="AL9" s="24"/>
+      <c r="AM9" s="23"/>
+      <c r="AN9" s="22"/>
+      <c r="AO9" s="22"/>
+      <c r="AP9" s="24"/>
+    </row>
+    <row r="10" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="215"/>
+      <c r="B10" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="23"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="23"/>
+      <c r="T10" s="22"/>
+      <c r="U10" s="22"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="23"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="22"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="23"/>
+      <c r="AB10" s="22"/>
+      <c r="AC10" s="22"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="23"/>
+      <c r="AF10" s="22"/>
+      <c r="AG10" s="22"/>
+      <c r="AH10" s="24"/>
+      <c r="AI10" s="23"/>
+      <c r="AJ10" s="22"/>
+      <c r="AK10" s="22"/>
+      <c r="AL10" s="24"/>
+      <c r="AM10" s="23"/>
+      <c r="AN10" s="22"/>
+      <c r="AO10" s="22"/>
+      <c r="AP10" s="24"/>
+    </row>
+    <row r="11" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="214" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="D11" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="F11" s="32"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="31"/>
+      <c r="Z11" s="32"/>
+      <c r="AA11" s="33"/>
+      <c r="AB11" s="31"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="32"/>
+      <c r="AE11" s="33"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="32"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="31"/>
+      <c r="AL11" s="32"/>
+      <c r="AM11" s="33"/>
+      <c r="AN11" s="31"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="32"/>
+    </row>
+    <row r="12" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="222"/>
+      <c r="B12" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" s="27"/>
+      <c r="D12" s="140" t="s">
+        <v>139</v>
+      </c>
+      <c r="E12" s="25"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="27"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="26"/>
+      <c r="O12" s="27"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="26"/>
+      <c r="S12" s="27"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="26"/>
+      <c r="W12" s="27"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="26"/>
+      <c r="AA12" s="27"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="26"/>
+      <c r="AE12" s="27"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="26"/>
+      <c r="AI12" s="27"/>
+      <c r="AJ12" s="25"/>
+      <c r="AK12" s="25"/>
+      <c r="AL12" s="26"/>
+      <c r="AM12" s="27"/>
+      <c r="AN12" s="25"/>
+      <c r="AO12" s="25"/>
+      <c r="AP12" s="26"/>
+    </row>
+    <row r="13" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="73" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="164" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" s="96"/>
+      <c r="D13" s="98"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="112"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="112"/>
+      <c r="K13" s="111"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="113"/>
+      <c r="O13" s="100"/>
+      <c r="P13" s="98"/>
+      <c r="Q13" s="98"/>
+      <c r="R13" s="113"/>
+      <c r="S13" s="100"/>
+      <c r="T13" s="98"/>
+      <c r="U13" s="98"/>
+      <c r="V13" s="113"/>
+      <c r="W13" s="98"/>
+      <c r="X13" s="98"/>
+      <c r="Y13" s="98"/>
+      <c r="Z13" s="113"/>
+      <c r="AA13" s="100"/>
+      <c r="AB13" s="98"/>
+      <c r="AC13" s="98"/>
+      <c r="AD13" s="113"/>
+      <c r="AE13" s="100"/>
+      <c r="AF13" s="98"/>
+      <c r="AG13" s="98"/>
+      <c r="AH13" s="113"/>
+      <c r="AI13" s="100"/>
+      <c r="AJ13" s="98"/>
+      <c r="AK13" s="98"/>
+      <c r="AL13" s="113"/>
+      <c r="AM13" s="100"/>
+      <c r="AN13" s="98"/>
+      <c r="AO13" s="98"/>
+      <c r="AP13" s="113"/>
+    </row>
+    <row r="14" spans="1:51" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="220" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="150"/>
+      <c r="F14" s="152"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="30"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29"/>
+      <c r="N14" s="30"/>
+      <c r="O14" s="28"/>
+      <c r="P14" s="29"/>
+      <c r="Q14" s="29"/>
+      <c r="R14" s="30"/>
+      <c r="S14" s="28"/>
+      <c r="T14" s="29"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="28"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="30"/>
+      <c r="AA14" s="28"/>
+      <c r="AB14" s="29"/>
+      <c r="AC14" s="29"/>
+      <c r="AD14" s="30"/>
+      <c r="AE14" s="28"/>
+      <c r="AF14" s="29"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="30"/>
+      <c r="AI14" s="28"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="29"/>
+      <c r="AL14" s="30"/>
+      <c r="AM14" s="28"/>
+      <c r="AN14" s="29"/>
+      <c r="AO14" s="29"/>
+      <c r="AP14" s="30"/>
+      <c r="AQ14" s="2"/>
+      <c r="AR14" s="2"/>
+      <c r="AS14" s="2"/>
+      <c r="AT14" s="2"/>
+      <c r="AU14" s="2"/>
+      <c r="AV14" s="2"/>
+      <c r="AW14" s="2"/>
+      <c r="AX14" s="2"/>
+      <c r="AY14" s="2"/>
+    </row>
+    <row r="15" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="221"/>
+      <c r="B15" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="28"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F15" s="30"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29"/>
+      <c r="N15" s="30"/>
+      <c r="O15" s="28"/>
+      <c r="P15" s="29"/>
+      <c r="Q15" s="29"/>
+      <c r="R15" s="30"/>
+      <c r="S15" s="28"/>
+      <c r="T15" s="29"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="30"/>
+      <c r="AA15" s="28"/>
+      <c r="AB15" s="29"/>
+      <c r="AC15" s="29"/>
+      <c r="AD15" s="30"/>
+      <c r="AE15" s="28"/>
+      <c r="AF15" s="29"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="28"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="29"/>
+      <c r="AL15" s="30"/>
+      <c r="AM15" s="28"/>
+      <c r="AN15" s="29"/>
+      <c r="AO15" s="29"/>
+      <c r="AP15" s="30"/>
+    </row>
+    <row r="16" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="220" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C16" s="138"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="137"/>
+      <c r="G16" s="148"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="137"/>
+      <c r="K16" s="138"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="137"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="139"/>
+      <c r="Q16" s="139"/>
+      <c r="R16" s="137"/>
+      <c r="S16" s="138"/>
+      <c r="T16" s="139"/>
+      <c r="U16" s="139"/>
+      <c r="V16" s="137"/>
+      <c r="W16" s="138"/>
+      <c r="X16" s="139"/>
+      <c r="Y16" s="139"/>
+      <c r="Z16" s="137"/>
+      <c r="AA16" s="138"/>
+      <c r="AB16" s="139"/>
+      <c r="AC16" s="139"/>
+      <c r="AD16" s="137"/>
+      <c r="AE16" s="138"/>
+      <c r="AF16" s="139"/>
+      <c r="AG16" s="139"/>
+      <c r="AH16" s="137"/>
+      <c r="AI16" s="138"/>
+      <c r="AJ16" s="139"/>
+      <c r="AK16" s="139"/>
+      <c r="AL16" s="137"/>
+      <c r="AM16" s="138"/>
+      <c r="AN16" s="139"/>
+      <c r="AO16" s="139"/>
+      <c r="AP16" s="137"/>
+    </row>
+    <row r="17" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="221"/>
+      <c r="B17" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C17" s="27"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="26"/>
+      <c r="K17" s="27"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="26"/>
+      <c r="O17" s="27"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="26"/>
+      <c r="S17" s="27"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="26"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="26"/>
+      <c r="AA17" s="27"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="26"/>
+      <c r="AE17" s="27"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="26"/>
+      <c r="AI17" s="27"/>
+      <c r="AJ17" s="25"/>
+      <c r="AK17" s="25"/>
+      <c r="AL17" s="26"/>
+      <c r="AM17" s="27"/>
+      <c r="AN17" s="25"/>
+      <c r="AO17" s="25"/>
+      <c r="AP17" s="26"/>
+    </row>
+    <row r="18" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="220" t="s">
+        <v>92</v>
+      </c>
+      <c r="B18" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="27"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="148"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="27"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="26"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="26"/>
+      <c r="AA18" s="27"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="26"/>
+      <c r="AE18" s="27"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="26"/>
+      <c r="AI18" s="27"/>
+      <c r="AJ18" s="25"/>
+      <c r="AK18" s="25"/>
+      <c r="AL18" s="26"/>
+      <c r="AM18" s="27"/>
+      <c r="AN18" s="25"/>
+      <c r="AO18" s="25"/>
+      <c r="AP18" s="26"/>
+    </row>
+    <row r="19" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="221"/>
+      <c r="B19" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C19" s="27"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="22"/>
+      <c r="F19" s="161" t="s">
+        <v>139</v>
+      </c>
+      <c r="G19" s="27"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="26"/>
+      <c r="K19" s="27"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="26"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="26"/>
+      <c r="AA19" s="27"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="26"/>
+      <c r="AE19" s="27"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="26"/>
+      <c r="AI19" s="27"/>
+      <c r="AJ19" s="25"/>
+      <c r="AK19" s="25"/>
+      <c r="AL19" s="26"/>
+      <c r="AM19" s="27"/>
+      <c r="AN19" s="25"/>
+      <c r="AO19" s="25"/>
+      <c r="AP19" s="26"/>
+    </row>
+    <row r="20" spans="1:60" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="220" t="s">
+        <v>90</v>
+      </c>
+      <c r="B20" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" s="33"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="32"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="148"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="32"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="32"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="32"/>
+      <c r="AA20" s="33"/>
+      <c r="AB20" s="31"/>
+      <c r="AC20" s="31"/>
+      <c r="AD20" s="32"/>
+      <c r="AE20" s="33"/>
+      <c r="AF20" s="31"/>
+      <c r="AG20" s="31"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="33"/>
+      <c r="AJ20" s="31"/>
+      <c r="AK20" s="31"/>
+      <c r="AL20" s="32"/>
+      <c r="AM20" s="33"/>
+      <c r="AN20" s="31"/>
+      <c r="AO20" s="31"/>
+      <c r="AP20" s="32"/>
+      <c r="AQ20" s="2"/>
+      <c r="AR20" s="2"/>
+      <c r="AS20" s="2"/>
+      <c r="AT20" s="2"/>
+      <c r="AU20" s="2"/>
+      <c r="AV20" s="2"/>
+      <c r="AW20" s="2"/>
+      <c r="AX20" s="2"/>
+      <c r="AY20" s="2"/>
+      <c r="AZ20" s="2"/>
+      <c r="BA20" s="2"/>
+      <c r="BB20" s="2"/>
+      <c r="BC20" s="2"/>
+      <c r="BD20" s="2"/>
+      <c r="BE20" s="2"/>
+      <c r="BF20" s="2"/>
+      <c r="BG20" s="2"/>
+      <c r="BH20" s="2"/>
+    </row>
+    <row r="21" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="221"/>
+      <c r="B21" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="135" t="s">
+        <v>139</v>
+      </c>
+      <c r="G21" s="23"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="23"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="24"/>
+      <c r="W21" s="23"/>
+      <c r="X21" s="22"/>
+      <c r="Y21" s="22"/>
+      <c r="Z21" s="24"/>
+      <c r="AA21" s="23"/>
+      <c r="AB21" s="22"/>
+      <c r="AC21" s="22"/>
+      <c r="AD21" s="24"/>
+      <c r="AE21" s="23"/>
+      <c r="AF21" s="22"/>
+      <c r="AG21" s="22"/>
+      <c r="AH21" s="24"/>
+      <c r="AI21" s="23"/>
+      <c r="AJ21" s="22"/>
+      <c r="AK21" s="22"/>
+      <c r="AL21" s="24"/>
+      <c r="AM21" s="23"/>
+      <c r="AN21" s="22"/>
+      <c r="AO21" s="22"/>
+      <c r="AP21" s="24"/>
+    </row>
+    <row r="22" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="220" t="s">
+        <v>118</v>
+      </c>
+      <c r="B22" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="D22" s="31"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="32"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="151"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="31"/>
+      <c r="N22" s="32"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="32"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="31"/>
+      <c r="Z22" s="32"/>
+      <c r="AA22" s="33"/>
+      <c r="AB22" s="31"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="32"/>
+      <c r="AE22" s="33"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="33"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="31"/>
+      <c r="AL22" s="32"/>
+      <c r="AM22" s="33"/>
+      <c r="AN22" s="31"/>
+      <c r="AO22" s="31"/>
+      <c r="AP22" s="32"/>
+    </row>
+    <row r="23" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="221"/>
+      <c r="B23" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C23" s="27"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="27"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="27"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="27"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="27"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="26"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="26"/>
+      <c r="AA23" s="27"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="26"/>
+      <c r="AE23" s="27"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="31"/>
+      <c r="AH23" s="26"/>
+      <c r="AI23" s="27"/>
+      <c r="AJ23" s="25"/>
+      <c r="AK23" s="31"/>
+      <c r="AL23" s="26"/>
+      <c r="AM23" s="27"/>
+      <c r="AN23" s="25"/>
+      <c r="AO23" s="31"/>
+      <c r="AP23" s="26"/>
+    </row>
+    <row r="24" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="220" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="27"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="27"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="L24" s="25"/>
+      <c r="M24" s="31"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="27"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="27"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="26"/>
+      <c r="W24" s="27"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="31"/>
+      <c r="Z24" s="26"/>
+      <c r="AA24" s="27"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="26"/>
+      <c r="AE24" s="27"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="26"/>
+      <c r="AI24" s="27"/>
+      <c r="AJ24" s="25"/>
+      <c r="AK24" s="31"/>
+      <c r="AL24" s="26"/>
+      <c r="AM24" s="27"/>
+      <c r="AN24" s="25"/>
+      <c r="AO24" s="31"/>
+      <c r="AP24" s="26"/>
+    </row>
+    <row r="25" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="221"/>
+      <c r="B25" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" s="27"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="27"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="27"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="26"/>
+      <c r="W25" s="27"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="26"/>
+      <c r="AA25" s="27"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="26"/>
+      <c r="AE25" s="27"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="26"/>
+      <c r="AI25" s="27"/>
+      <c r="AJ25" s="25"/>
+      <c r="AK25" s="25"/>
+      <c r="AL25" s="26"/>
+      <c r="AM25" s="27"/>
+      <c r="AN25" s="25"/>
+      <c r="AO25" s="25"/>
+      <c r="AP25" s="26"/>
+    </row>
+    <row r="26" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="220" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C26" s="27"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="27"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="L26" s="148"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="32"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="32"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="32"/>
+      <c r="AA26" s="27"/>
+      <c r="AB26" s="31"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="32"/>
+      <c r="AE26" s="27"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="27"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="31"/>
+      <c r="AL26" s="32"/>
+      <c r="AM26" s="27"/>
+      <c r="AN26" s="31"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="32"/>
+    </row>
+    <row r="27" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="221"/>
+      <c r="B27" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="27"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="27"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="27"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="27"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="27"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="22"/>
+      <c r="Y27" s="22"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="27"/>
+      <c r="AB27" s="22"/>
+      <c r="AC27" s="22"/>
+      <c r="AD27" s="24"/>
+      <c r="AE27" s="27"/>
+      <c r="AF27" s="22"/>
+      <c r="AG27" s="22"/>
+      <c r="AH27" s="24"/>
+      <c r="AI27" s="27"/>
+      <c r="AJ27" s="22"/>
+      <c r="AK27" s="22"/>
+      <c r="AL27" s="24"/>
+      <c r="AM27" s="27"/>
+      <c r="AN27" s="22"/>
+      <c r="AO27" s="22"/>
+      <c r="AP27" s="24"/>
+    </row>
+    <row r="28" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="220" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C28" s="27"/>
+      <c r="D28" s="31"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="27"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="148"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="31"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="31"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="27"/>
+      <c r="AB28" s="31"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="27"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="27"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="31"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="27"/>
+      <c r="AN28" s="31"/>
+      <c r="AO28" s="31"/>
+      <c r="AP28" s="32"/>
+    </row>
+    <row r="29" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="221"/>
+      <c r="B29" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C29" s="27"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="27"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="27"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="27"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="26"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="26"/>
+      <c r="AA29" s="27"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="26"/>
+      <c r="AE29" s="27"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="26"/>
+      <c r="AI29" s="27"/>
+      <c r="AJ29" s="25"/>
+      <c r="AK29" s="25"/>
+      <c r="AL29" s="26"/>
+      <c r="AM29" s="27"/>
+      <c r="AN29" s="25"/>
+      <c r="AO29" s="25"/>
+      <c r="AP29" s="26"/>
+    </row>
+    <row r="30" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="76" t="s">
+        <v>31</v>
+      </c>
+      <c r="B30" s="165" t="s">
+        <v>144</v>
+      </c>
+      <c r="C30" s="96"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="113"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="114"/>
+      <c r="M30" s="114"/>
+      <c r="N30" s="116"/>
+      <c r="O30" s="115"/>
+      <c r="P30" s="115"/>
+      <c r="Q30" s="98"/>
+      <c r="R30" s="113"/>
+      <c r="S30" s="100"/>
+      <c r="T30" s="98"/>
+      <c r="U30" s="98"/>
+      <c r="V30" s="113"/>
+      <c r="W30" s="100"/>
+      <c r="X30" s="98"/>
+      <c r="Y30" s="98"/>
+      <c r="Z30" s="113"/>
+      <c r="AA30" s="100"/>
+      <c r="AB30" s="98"/>
+      <c r="AC30" s="98"/>
+      <c r="AD30" s="113"/>
+      <c r="AE30" s="100"/>
+      <c r="AF30" s="98"/>
+      <c r="AG30" s="98"/>
+      <c r="AH30" s="113"/>
+      <c r="AI30" s="100"/>
+      <c r="AJ30" s="98"/>
+      <c r="AK30" s="98"/>
+      <c r="AL30" s="113"/>
+      <c r="AM30" s="100"/>
+      <c r="AN30" s="98"/>
+      <c r="AO30" s="98"/>
+      <c r="AP30" s="113"/>
+    </row>
+    <row r="31" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="219" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="39"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="39"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="150"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="39"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="29"/>
+      <c r="Z31" s="39"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="29"/>
+      <c r="AC31" s="29"/>
+      <c r="AD31" s="39"/>
+      <c r="AE31" s="29"/>
+      <c r="AF31" s="29"/>
+      <c r="AG31" s="29"/>
+      <c r="AH31" s="39"/>
+      <c r="AI31" s="29"/>
+      <c r="AJ31" s="29"/>
+      <c r="AK31" s="29"/>
+      <c r="AL31" s="39"/>
+      <c r="AM31" s="29"/>
+      <c r="AN31" s="29"/>
+      <c r="AO31" s="29"/>
+      <c r="AP31" s="39"/>
+    </row>
+    <row r="32" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="217"/>
+      <c r="B32" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C32" s="139"/>
+      <c r="D32" s="139"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="137"/>
+      <c r="G32" s="139"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="139"/>
+      <c r="J32" s="137"/>
+      <c r="K32" s="139"/>
+      <c r="L32" s="139"/>
+      <c r="M32" s="139"/>
+      <c r="N32" s="137"/>
+      <c r="O32" s="139"/>
+      <c r="P32" s="139"/>
+      <c r="Q32" s="139"/>
+      <c r="R32" s="137"/>
+      <c r="S32" s="139"/>
+      <c r="T32" s="139"/>
+      <c r="U32" s="139"/>
+      <c r="V32" s="137"/>
+      <c r="W32" s="139"/>
+      <c r="X32" s="139"/>
+      <c r="Y32" s="139"/>
+      <c r="Z32" s="137"/>
+      <c r="AA32" s="139"/>
+      <c r="AB32" s="139"/>
+      <c r="AC32" s="139"/>
+      <c r="AD32" s="137"/>
+      <c r="AE32" s="139"/>
+      <c r="AF32" s="139"/>
+      <c r="AG32" s="139"/>
+      <c r="AH32" s="137"/>
+      <c r="AI32" s="139"/>
+      <c r="AJ32" s="139"/>
+      <c r="AK32" s="139"/>
+      <c r="AL32" s="137"/>
+      <c r="AM32" s="139"/>
+      <c r="AN32" s="139"/>
+      <c r="AO32" s="139"/>
+      <c r="AP32" s="137"/>
+    </row>
+    <row r="33" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="216" t="s">
+        <v>110</v>
+      </c>
+      <c r="B33" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="25"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="26"/>
+      <c r="AA33" s="25"/>
+      <c r="AB33" s="25"/>
+      <c r="AC33" s="25"/>
+      <c r="AD33" s="26"/>
+      <c r="AE33" s="25"/>
+      <c r="AF33" s="25"/>
+      <c r="AG33" s="25"/>
+      <c r="AH33" s="26"/>
+      <c r="AI33" s="25"/>
+      <c r="AJ33" s="25"/>
+      <c r="AK33" s="25"/>
+      <c r="AL33" s="26"/>
+      <c r="AM33" s="25"/>
+      <c r="AN33" s="25"/>
+      <c r="AO33" s="25"/>
+      <c r="AP33" s="26"/>
+    </row>
+    <row r="34" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="217"/>
+      <c r="B34" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C34" s="25"/>
+      <c r="D34" s="25"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="25"/>
+      <c r="H34" s="25"/>
+      <c r="I34" s="25"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="25"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="25"/>
+      <c r="V34" s="26"/>
+      <c r="W34" s="25"/>
+      <c r="X34" s="25"/>
+      <c r="Y34" s="25"/>
+      <c r="Z34" s="26"/>
+      <c r="AA34" s="25"/>
+      <c r="AB34" s="25"/>
+      <c r="AC34" s="25"/>
+      <c r="AD34" s="26"/>
+      <c r="AE34" s="25"/>
+      <c r="AF34" s="25"/>
+      <c r="AG34" s="25"/>
+      <c r="AH34" s="26"/>
+      <c r="AI34" s="25"/>
+      <c r="AJ34" s="25"/>
+      <c r="AK34" s="25"/>
+      <c r="AL34" s="26"/>
+      <c r="AM34" s="25"/>
+      <c r="AN34" s="25"/>
+      <c r="AO34" s="25"/>
+      <c r="AP34" s="26"/>
+    </row>
+    <row r="35" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="216" t="s">
+        <v>111</v>
+      </c>
+      <c r="B35" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="25"/>
+      <c r="H35" s="25"/>
+      <c r="I35" s="25"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="25"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="25"/>
+      <c r="V35" s="26"/>
+      <c r="W35" s="25"/>
+      <c r="X35" s="25"/>
+      <c r="Y35" s="25"/>
+      <c r="Z35" s="26"/>
+      <c r="AA35" s="25"/>
+      <c r="AB35" s="25"/>
+      <c r="AC35" s="25"/>
+      <c r="AD35" s="26"/>
+      <c r="AE35" s="25"/>
+      <c r="AF35" s="25"/>
+      <c r="AG35" s="25"/>
+      <c r="AH35" s="26"/>
+      <c r="AI35" s="25"/>
+      <c r="AJ35" s="25"/>
+      <c r="AK35" s="25"/>
+      <c r="AL35" s="26"/>
+      <c r="AM35" s="25"/>
+      <c r="AN35" s="25"/>
+      <c r="AO35" s="25"/>
+      <c r="AP35" s="26"/>
+    </row>
+    <row r="36" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="218"/>
+      <c r="B36" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
+      <c r="E36" s="31"/>
+      <c r="F36" s="32"/>
+      <c r="G36" s="31"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="31"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="32"/>
+      <c r="O36" s="31"/>
+      <c r="P36" s="31"/>
+      <c r="Q36" s="31"/>
+      <c r="R36" s="32"/>
+      <c r="S36" s="31"/>
+      <c r="T36" s="31"/>
+      <c r="U36" s="31"/>
+      <c r="V36" s="32"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="31"/>
+      <c r="Y36" s="31"/>
+      <c r="Z36" s="32"/>
+      <c r="AA36" s="31"/>
+      <c r="AB36" s="31"/>
+      <c r="AC36" s="31"/>
+      <c r="AD36" s="32"/>
+      <c r="AE36" s="31"/>
+      <c r="AF36" s="31"/>
+      <c r="AG36" s="31"/>
+      <c r="AH36" s="32"/>
+      <c r="AI36" s="31"/>
+      <c r="AJ36" s="31"/>
+      <c r="AK36" s="31"/>
+      <c r="AL36" s="32"/>
+      <c r="AM36" s="31"/>
+      <c r="AN36" s="31"/>
+      <c r="AO36" s="31"/>
+      <c r="AP36" s="32"/>
+    </row>
+    <row r="37" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="216" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="22"/>
+      <c r="H37" s="22"/>
+      <c r="I37" s="22"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q37" s="22"/>
+      <c r="R37" s="24"/>
+      <c r="S37" s="22"/>
+      <c r="T37" s="22"/>
+      <c r="U37" s="22"/>
+      <c r="V37" s="24"/>
+      <c r="W37" s="22"/>
+      <c r="X37" s="22"/>
+      <c r="Y37" s="22"/>
+      <c r="Z37" s="24"/>
+      <c r="AA37" s="22"/>
+      <c r="AB37" s="22"/>
+      <c r="AC37" s="22"/>
+      <c r="AD37" s="24"/>
+      <c r="AE37" s="22"/>
+      <c r="AF37" s="22"/>
+      <c r="AG37" s="22"/>
+      <c r="AH37" s="24"/>
+      <c r="AI37" s="22"/>
+      <c r="AJ37" s="22"/>
+      <c r="AK37" s="22"/>
+      <c r="AL37" s="24"/>
+      <c r="AM37" s="22"/>
+      <c r="AN37" s="22"/>
+      <c r="AO37" s="22"/>
+      <c r="AP37" s="24"/>
+    </row>
+    <row r="38" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="217"/>
+      <c r="B38" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+      <c r="M38" s="31"/>
+      <c r="N38" s="32"/>
+      <c r="O38" s="31"/>
+      <c r="P38" s="31"/>
+      <c r="Q38" s="31"/>
+      <c r="R38" s="32"/>
+      <c r="S38" s="31"/>
+      <c r="T38" s="31"/>
+      <c r="U38" s="31"/>
+      <c r="V38" s="32"/>
+      <c r="W38" s="31"/>
+      <c r="X38" s="31"/>
+      <c r="Y38" s="31"/>
+      <c r="Z38" s="32"/>
+      <c r="AA38" s="31"/>
+      <c r="AB38" s="31"/>
+      <c r="AC38" s="31"/>
+      <c r="AD38" s="32"/>
+      <c r="AE38" s="31"/>
+      <c r="AF38" s="31"/>
+      <c r="AG38" s="31"/>
+      <c r="AH38" s="32"/>
+      <c r="AI38" s="31"/>
+      <c r="AJ38" s="31"/>
+      <c r="AK38" s="31"/>
+      <c r="AL38" s="32"/>
+      <c r="AM38" s="31"/>
+      <c r="AN38" s="31"/>
+      <c r="AO38" s="31"/>
+      <c r="AP38" s="32"/>
+    </row>
+    <row r="39" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="216" t="s">
+        <v>113</v>
+      </c>
+      <c r="B39" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+      <c r="M39" s="31"/>
+      <c r="N39" s="32"/>
+      <c r="O39" s="31"/>
+      <c r="P39" s="148" t="s">
+        <v>139</v>
+      </c>
+      <c r="Q39" s="31"/>
+      <c r="R39" s="32"/>
+      <c r="S39" s="31"/>
+      <c r="T39" s="31"/>
+      <c r="U39" s="31"/>
+      <c r="V39" s="32"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="31"/>
+      <c r="Y39" s="31"/>
+      <c r="Z39" s="32"/>
+      <c r="AA39" s="31"/>
+      <c r="AB39" s="31"/>
+      <c r="AC39" s="31"/>
+      <c r="AD39" s="32"/>
+      <c r="AE39" s="31"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
+      <c r="AH39" s="32"/>
+      <c r="AI39" s="31"/>
+      <c r="AJ39" s="31"/>
+      <c r="AK39" s="31"/>
+      <c r="AL39" s="32"/>
+      <c r="AM39" s="31"/>
+      <c r="AN39" s="31"/>
+      <c r="AO39" s="31"/>
+      <c r="AP39" s="32"/>
+    </row>
+    <row r="40" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="217"/>
+      <c r="B40" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="32"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="32"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="32"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="32"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="32"/>
+      <c r="AA40" s="31"/>
+      <c r="AB40" s="31"/>
+      <c r="AC40" s="31"/>
+      <c r="AD40" s="32"/>
+      <c r="AE40" s="31"/>
+      <c r="AF40" s="31"/>
+      <c r="AG40" s="31"/>
+      <c r="AH40" s="32"/>
+      <c r="AI40" s="31"/>
+      <c r="AJ40" s="31"/>
+      <c r="AK40" s="31"/>
+      <c r="AL40" s="32"/>
+      <c r="AM40" s="31"/>
+      <c r="AN40" s="31"/>
+      <c r="AO40" s="31"/>
+      <c r="AP40" s="32"/>
+    </row>
+    <row r="41" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="166" t="s">
+        <v>145</v>
+      </c>
+      <c r="C41" s="96"/>
+      <c r="D41" s="98"/>
+      <c r="E41" s="98"/>
+      <c r="F41" s="113"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="98"/>
+      <c r="I41" s="98"/>
+      <c r="J41" s="113"/>
+      <c r="K41" s="100"/>
+      <c r="L41" s="117"/>
+      <c r="M41" s="98"/>
+      <c r="N41" s="113"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="98"/>
+      <c r="Q41" s="118"/>
+      <c r="R41" s="119"/>
+      <c r="S41" s="157"/>
+      <c r="T41" s="118"/>
+      <c r="U41" s="118"/>
+      <c r="V41" s="119"/>
+      <c r="W41" s="118"/>
+      <c r="X41" s="118"/>
+      <c r="Y41" s="118"/>
+      <c r="Z41" s="119"/>
+      <c r="AA41" s="118"/>
+      <c r="AB41" s="118"/>
+      <c r="AC41" s="118"/>
+      <c r="AD41" s="119"/>
+      <c r="AE41" s="100"/>
+      <c r="AF41" s="98"/>
+      <c r="AG41" s="98"/>
+      <c r="AH41" s="113"/>
+      <c r="AI41" s="100"/>
+      <c r="AJ41" s="98"/>
+      <c r="AK41" s="98"/>
+      <c r="AL41" s="113"/>
+      <c r="AM41" s="100"/>
+      <c r="AN41" s="98"/>
+      <c r="AO41" s="98"/>
+      <c r="AP41" s="113"/>
+    </row>
+    <row r="42" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="212" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="94"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="30"/>
+      <c r="G42" s="94"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="94"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="30"/>
+      <c r="O42" s="94"/>
+      <c r="P42" s="29"/>
+      <c r="Q42" s="156"/>
+      <c r="R42" s="30"/>
+      <c r="S42" s="158"/>
+      <c r="T42" s="29"/>
+      <c r="U42" s="29"/>
+      <c r="V42" s="30"/>
+      <c r="W42" s="94"/>
+      <c r="X42" s="29"/>
+      <c r="Y42" s="29"/>
+      <c r="Z42" s="30"/>
+      <c r="AA42" s="94"/>
+      <c r="AB42" s="29"/>
+      <c r="AC42" s="29"/>
+      <c r="AD42" s="30"/>
+      <c r="AE42" s="94"/>
+      <c r="AF42" s="29"/>
+      <c r="AG42" s="29"/>
+      <c r="AH42" s="30"/>
+      <c r="AI42" s="94"/>
+      <c r="AJ42" s="29"/>
+      <c r="AK42" s="29"/>
+      <c r="AL42" s="30"/>
+      <c r="AM42" s="94"/>
+      <c r="AN42" s="29"/>
+      <c r="AO42" s="29"/>
+      <c r="AP42" s="30"/>
+    </row>
+    <row r="43" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="213"/>
+      <c r="B43" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C43" s="94"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="94"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="94"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="94"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="94"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="94"/>
+      <c r="X43" s="29"/>
+      <c r="Y43" s="29"/>
+      <c r="Z43" s="30"/>
+      <c r="AA43" s="94"/>
+      <c r="AB43" s="29"/>
+      <c r="AC43" s="29"/>
+      <c r="AD43" s="30"/>
+      <c r="AE43" s="94"/>
+      <c r="AF43" s="29"/>
+      <c r="AG43" s="29"/>
+      <c r="AH43" s="30"/>
+      <c r="AI43" s="94"/>
+      <c r="AJ43" s="29"/>
+      <c r="AK43" s="29"/>
+      <c r="AL43" s="30"/>
+      <c r="AM43" s="94"/>
+      <c r="AN43" s="29"/>
+      <c r="AO43" s="29"/>
+      <c r="AP43" s="30"/>
+    </row>
+    <row r="44" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="212" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="93"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="93"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="93"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="22"/>
+      <c r="N44" s="24"/>
+      <c r="O44" s="93"/>
+      <c r="P44" s="22"/>
+      <c r="Q44" s="22"/>
+      <c r="R44" s="151"/>
+      <c r="S44" s="93"/>
+      <c r="T44" s="23"/>
+      <c r="U44" s="22"/>
+      <c r="V44" s="24"/>
+      <c r="W44" s="93"/>
+      <c r="X44" s="22"/>
+      <c r="Y44" s="22"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="93"/>
+      <c r="AB44" s="22"/>
+      <c r="AC44" s="22"/>
+      <c r="AD44" s="24"/>
+      <c r="AE44" s="93"/>
+      <c r="AF44" s="22"/>
+      <c r="AG44" s="22"/>
+      <c r="AH44" s="24"/>
+      <c r="AI44" s="93"/>
+      <c r="AJ44" s="22"/>
+      <c r="AK44" s="22"/>
+      <c r="AL44" s="24"/>
+      <c r="AM44" s="93"/>
+      <c r="AN44" s="22"/>
+      <c r="AO44" s="22"/>
+      <c r="AP44" s="24"/>
+    </row>
+    <row r="45" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="213"/>
+      <c r="B45" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C45" s="93"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="93"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="93"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="22"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="93"/>
+      <c r="P45" s="22"/>
+      <c r="Q45" s="22"/>
+      <c r="R45" s="24"/>
+      <c r="S45" s="93"/>
+      <c r="T45" s="22"/>
+      <c r="U45" s="22"/>
+      <c r="V45" s="24"/>
+      <c r="W45" s="93"/>
+      <c r="X45" s="22"/>
+      <c r="Y45" s="22"/>
+      <c r="Z45" s="24"/>
+      <c r="AA45" s="93"/>
+      <c r="AB45" s="22"/>
+      <c r="AC45" s="22"/>
+      <c r="AD45" s="24"/>
+      <c r="AE45" s="93"/>
+      <c r="AF45" s="22"/>
+      <c r="AG45" s="22"/>
+      <c r="AH45" s="24"/>
+      <c r="AI45" s="93"/>
+      <c r="AJ45" s="22"/>
+      <c r="AK45" s="22"/>
+      <c r="AL45" s="24"/>
+      <c r="AM45" s="93"/>
+      <c r="AN45" s="22"/>
+      <c r="AO45" s="22"/>
+      <c r="AP45" s="24"/>
+    </row>
+    <row r="46" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="212" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="93"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="93"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="93"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="22"/>
+      <c r="N46" s="24"/>
+      <c r="O46" s="93"/>
+      <c r="P46" s="22"/>
+      <c r="Q46" s="22"/>
+      <c r="R46" s="24"/>
+      <c r="S46" s="153"/>
+      <c r="T46" s="159"/>
+      <c r="U46" s="23"/>
+      <c r="V46" s="23"/>
+      <c r="W46" s="93"/>
+      <c r="X46" s="22"/>
+      <c r="Y46" s="22"/>
+      <c r="Z46" s="24"/>
+      <c r="AA46" s="93"/>
+      <c r="AB46" s="22"/>
+      <c r="AC46" s="22"/>
+      <c r="AD46" s="24"/>
+      <c r="AE46" s="93"/>
+      <c r="AF46" s="22"/>
+      <c r="AG46" s="22"/>
+      <c r="AH46" s="24"/>
+      <c r="AI46" s="93"/>
+      <c r="AJ46" s="22"/>
+      <c r="AK46" s="22"/>
+      <c r="AL46" s="24"/>
+      <c r="AM46" s="93"/>
+      <c r="AN46" s="22"/>
+      <c r="AO46" s="22"/>
+      <c r="AP46" s="24"/>
+    </row>
+    <row r="47" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="213"/>
+      <c r="B47" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C47" s="93"/>
+      <c r="D47" s="22"/>
+      <c r="E47" s="22"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="93"/>
+      <c r="H47" s="22"/>
+      <c r="I47" s="22"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="93"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="22"/>
+      <c r="N47" s="24"/>
+      <c r="O47" s="93"/>
+      <c r="P47" s="22"/>
+      <c r="Q47" s="22"/>
+      <c r="R47" s="24"/>
+      <c r="S47" s="93"/>
+      <c r="T47" s="22"/>
+      <c r="U47" s="22"/>
+      <c r="V47" s="24"/>
+      <c r="W47" s="93"/>
+      <c r="X47" s="22"/>
+      <c r="Y47" s="22"/>
+      <c r="Z47" s="24"/>
+      <c r="AA47" s="93"/>
+      <c r="AB47" s="22"/>
+      <c r="AC47" s="22"/>
+      <c r="AD47" s="24"/>
+      <c r="AE47" s="93"/>
+      <c r="AF47" s="22"/>
+      <c r="AG47" s="22"/>
+      <c r="AH47" s="24"/>
+      <c r="AI47" s="93"/>
+      <c r="AJ47" s="22"/>
+      <c r="AK47" s="22"/>
+      <c r="AL47" s="24"/>
+      <c r="AM47" s="93"/>
+      <c r="AN47" s="22"/>
+      <c r="AO47" s="22"/>
+      <c r="AP47" s="24"/>
+    </row>
+    <row r="48" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="212" t="s">
+        <v>124</v>
+      </c>
+      <c r="B48" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="93"/>
+      <c r="D48" s="22"/>
+      <c r="E48" s="22"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="93"/>
+      <c r="H48" s="22"/>
+      <c r="I48" s="22"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="93"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="22"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="93"/>
+      <c r="P48" s="22"/>
+      <c r="Q48" s="22"/>
+      <c r="R48" s="24"/>
+      <c r="S48" s="93"/>
+      <c r="T48" s="22"/>
+      <c r="U48" s="159"/>
+      <c r="V48" s="151"/>
+      <c r="W48" s="23"/>
+      <c r="X48" s="23"/>
+      <c r="Y48" s="22"/>
+      <c r="Z48" s="24"/>
+      <c r="AA48" s="93"/>
+      <c r="AB48" s="22"/>
+      <c r="AC48" s="22"/>
+      <c r="AD48" s="24"/>
+      <c r="AE48" s="93"/>
+      <c r="AF48" s="22"/>
+      <c r="AG48" s="22"/>
+      <c r="AH48" s="24"/>
+      <c r="AI48" s="93"/>
+      <c r="AJ48" s="22"/>
+      <c r="AK48" s="22"/>
+      <c r="AL48" s="24"/>
+      <c r="AM48" s="93"/>
+      <c r="AN48" s="22"/>
+      <c r="AO48" s="22"/>
+      <c r="AP48" s="24"/>
+    </row>
+    <row r="49" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="213"/>
+      <c r="B49" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="95"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="95"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="95"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="32"/>
+      <c r="O49" s="95"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="32"/>
+      <c r="S49" s="95"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="32"/>
+      <c r="W49" s="95"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="32"/>
+      <c r="AA49" s="95"/>
+      <c r="AB49" s="31"/>
+      <c r="AC49" s="31"/>
+      <c r="AD49" s="32"/>
+      <c r="AE49" s="95"/>
+      <c r="AF49" s="31"/>
+      <c r="AG49" s="31"/>
+      <c r="AH49" s="32"/>
+      <c r="AI49" s="95"/>
+      <c r="AJ49" s="31"/>
+      <c r="AK49" s="31"/>
+      <c r="AL49" s="32"/>
+      <c r="AM49" s="95"/>
+      <c r="AN49" s="31"/>
+      <c r="AO49" s="31"/>
+      <c r="AP49" s="32"/>
+    </row>
+    <row r="50" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="212" t="s">
+        <v>119</v>
+      </c>
+      <c r="B50" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C50" s="70"/>
+      <c r="D50" s="25"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="25"/>
+      <c r="I50" s="25"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="70"/>
+      <c r="L50" s="25"/>
+      <c r="M50" s="25"/>
+      <c r="N50" s="26"/>
+      <c r="O50" s="70"/>
+      <c r="P50" s="25"/>
+      <c r="Q50" s="25"/>
+      <c r="R50" s="26"/>
+      <c r="S50" s="70"/>
+      <c r="T50" s="25"/>
+      <c r="U50" s="25"/>
+      <c r="V50" s="26"/>
+      <c r="W50" s="160"/>
+      <c r="X50" s="25"/>
+      <c r="Y50" s="23"/>
+      <c r="Z50" s="26"/>
+      <c r="AA50" s="70"/>
+      <c r="AB50" s="25"/>
+      <c r="AC50" s="25"/>
+      <c r="AD50" s="26"/>
+      <c r="AE50" s="70"/>
+      <c r="AF50" s="25"/>
+      <c r="AG50" s="25"/>
+      <c r="AH50" s="26"/>
+      <c r="AI50" s="70"/>
+      <c r="AJ50" s="25"/>
+      <c r="AK50" s="25"/>
+      <c r="AL50" s="26"/>
+      <c r="AM50" s="70"/>
+      <c r="AN50" s="25"/>
+      <c r="AO50" s="25"/>
+      <c r="AP50" s="26"/>
+    </row>
+    <row r="51" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="213"/>
+      <c r="B51" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C51" s="95"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="32"/>
+      <c r="G51" s="95"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="32"/>
+      <c r="K51" s="95"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="32"/>
+      <c r="O51" s="95"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="32"/>
+      <c r="S51" s="95"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="32"/>
+      <c r="W51" s="95"/>
+      <c r="X51" s="31"/>
+      <c r="Y51" s="31"/>
+      <c r="Z51" s="32"/>
+      <c r="AA51" s="95"/>
+      <c r="AB51" s="31"/>
+      <c r="AC51" s="31"/>
+      <c r="AD51" s="32"/>
+      <c r="AE51" s="95"/>
+      <c r="AF51" s="31"/>
+      <c r="AG51" s="31"/>
+      <c r="AH51" s="32"/>
+      <c r="AI51" s="95"/>
+      <c r="AJ51" s="31"/>
+      <c r="AK51" s="31"/>
+      <c r="AL51" s="32"/>
+      <c r="AM51" s="95"/>
+      <c r="AN51" s="31"/>
+      <c r="AO51" s="31"/>
+      <c r="AP51" s="32"/>
+    </row>
+    <row r="52" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="212" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C52" s="93"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="22"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="93"/>
+      <c r="H52" s="22"/>
+      <c r="I52" s="22"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="93"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="22"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="93"/>
+      <c r="P52" s="22"/>
+      <c r="Q52" s="22"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="93"/>
+      <c r="T52" s="22"/>
+      <c r="U52" s="22"/>
+      <c r="V52" s="24"/>
+      <c r="W52" s="93"/>
+      <c r="X52" s="159"/>
+      <c r="Y52" s="22"/>
+      <c r="Z52" s="23"/>
+      <c r="AA52" s="93"/>
+      <c r="AB52" s="22"/>
+      <c r="AC52" s="22"/>
+      <c r="AD52" s="24"/>
+      <c r="AE52" s="93"/>
+      <c r="AF52" s="22"/>
+      <c r="AG52" s="22"/>
+      <c r="AH52" s="24"/>
+      <c r="AI52" s="93"/>
+      <c r="AJ52" s="22"/>
+      <c r="AK52" s="22"/>
+      <c r="AL52" s="24"/>
+      <c r="AM52" s="93"/>
+      <c r="AN52" s="22"/>
+      <c r="AO52" s="22"/>
+      <c r="AP52" s="24"/>
+    </row>
+    <row r="53" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="213"/>
+      <c r="B53" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C53" s="93"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="93"/>
+      <c r="H53" s="22"/>
+      <c r="I53" s="22"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="93"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="22"/>
+      <c r="N53" s="24"/>
+      <c r="O53" s="93"/>
+      <c r="P53" s="22"/>
+      <c r="Q53" s="22"/>
+      <c r="R53" s="24"/>
+      <c r="S53" s="93"/>
+      <c r="T53" s="22"/>
+      <c r="U53" s="22"/>
+      <c r="V53" s="24"/>
+      <c r="W53" s="93"/>
+      <c r="X53" s="22"/>
+      <c r="Y53" s="22"/>
+      <c r="Z53" s="24"/>
+      <c r="AA53" s="93"/>
+      <c r="AB53" s="22"/>
+      <c r="AC53" s="22"/>
+      <c r="AD53" s="24"/>
+      <c r="AE53" s="93"/>
+      <c r="AF53" s="22"/>
+      <c r="AG53" s="22"/>
+      <c r="AH53" s="24"/>
+      <c r="AI53" s="93"/>
+      <c r="AJ53" s="22"/>
+      <c r="AK53" s="22"/>
+      <c r="AL53" s="24"/>
+      <c r="AM53" s="93"/>
+      <c r="AN53" s="22"/>
+      <c r="AO53" s="22"/>
+      <c r="AP53" s="24"/>
+    </row>
+    <row r="54" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="212" t="s">
+        <v>126</v>
+      </c>
+      <c r="B54" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C54" s="93"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="93"/>
+      <c r="H54" s="22"/>
+      <c r="I54" s="22"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="93"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="22"/>
+      <c r="N54" s="24"/>
+      <c r="O54" s="93"/>
+      <c r="P54" s="22"/>
+      <c r="Q54" s="22"/>
+      <c r="R54" s="24"/>
+      <c r="S54" s="93"/>
+      <c r="T54" s="22"/>
+      <c r="U54" s="22"/>
+      <c r="V54" s="24"/>
+      <c r="W54" s="93"/>
+      <c r="X54" s="22"/>
+      <c r="Y54" s="159"/>
+      <c r="Z54" s="151"/>
+      <c r="AA54" s="148"/>
+      <c r="AB54" s="22"/>
+      <c r="AC54" s="22"/>
+      <c r="AD54" s="24"/>
+      <c r="AE54" s="93"/>
+      <c r="AF54" s="22"/>
+      <c r="AG54" s="22"/>
+      <c r="AH54" s="24"/>
+      <c r="AI54" s="93"/>
+      <c r="AJ54" s="22"/>
+      <c r="AK54" s="22"/>
+      <c r="AL54" s="24"/>
+      <c r="AM54" s="93"/>
+      <c r="AN54" s="22"/>
+      <c r="AO54" s="22"/>
+      <c r="AP54" s="24"/>
+    </row>
+    <row r="55" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="213"/>
+      <c r="B55" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C55" s="95"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="32"/>
+      <c r="G55" s="95"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="32"/>
+      <c r="K55" s="95"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="32"/>
+      <c r="O55" s="95"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="32"/>
+      <c r="S55" s="95"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="31"/>
+      <c r="V55" s="32"/>
+      <c r="W55" s="95"/>
+      <c r="X55" s="31"/>
+      <c r="Y55" s="31"/>
+      <c r="Z55" s="32"/>
+      <c r="AA55" s="95"/>
+      <c r="AB55" s="31"/>
+      <c r="AC55" s="31"/>
+      <c r="AD55" s="32"/>
+      <c r="AE55" s="95"/>
+      <c r="AF55" s="31"/>
+      <c r="AG55" s="31"/>
+      <c r="AH55" s="32"/>
+      <c r="AI55" s="95"/>
+      <c r="AJ55" s="31"/>
+      <c r="AK55" s="31"/>
+      <c r="AL55" s="32"/>
+      <c r="AM55" s="95"/>
+      <c r="AN55" s="31"/>
+      <c r="AO55" s="31"/>
+      <c r="AP55" s="32"/>
+    </row>
+    <row r="56" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="212" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C56" s="95"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="32"/>
+      <c r="G56" s="95"/>
+      <c r="H56" s="31"/>
+      <c r="I56" s="31"/>
+      <c r="J56" s="32"/>
+      <c r="K56" s="95"/>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="32"/>
+      <c r="O56" s="95"/>
+      <c r="P56" s="31"/>
+      <c r="Q56" s="31"/>
+      <c r="R56" s="32"/>
+      <c r="S56" s="95"/>
+      <c r="T56" s="31"/>
+      <c r="U56" s="31"/>
+      <c r="V56" s="32"/>
+      <c r="W56" s="95"/>
+      <c r="X56" s="31"/>
+      <c r="Y56" s="31"/>
+      <c r="Z56" s="32"/>
+      <c r="AA56" s="95"/>
+      <c r="AB56" s="148"/>
+      <c r="AC56" s="31"/>
+      <c r="AD56" s="32"/>
+      <c r="AE56" s="95"/>
+      <c r="AF56" s="31"/>
+      <c r="AG56" s="31"/>
+      <c r="AH56" s="32"/>
+      <c r="AI56" s="95"/>
+      <c r="AJ56" s="31"/>
+      <c r="AK56" s="31"/>
+      <c r="AL56" s="32"/>
+      <c r="AM56" s="95"/>
+      <c r="AN56" s="31"/>
+      <c r="AO56" s="31"/>
+      <c r="AP56" s="32"/>
+    </row>
+    <row r="57" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="213"/>
+      <c r="B57" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C57" s="95"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="32"/>
+      <c r="G57" s="95"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="32"/>
+      <c r="K57" s="95"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+      <c r="N57" s="32"/>
+      <c r="O57" s="95"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="32"/>
+      <c r="S57" s="95"/>
+      <c r="T57" s="31"/>
+      <c r="U57" s="31"/>
+      <c r="V57" s="32"/>
+      <c r="W57" s="95"/>
+      <c r="X57" s="31"/>
+      <c r="Y57" s="31"/>
+      <c r="Z57" s="32"/>
+      <c r="AA57" s="95"/>
+      <c r="AB57" s="31"/>
+      <c r="AC57" s="31"/>
+      <c r="AD57" s="32"/>
+      <c r="AE57" s="95"/>
+      <c r="AF57" s="31"/>
+      <c r="AG57" s="31"/>
+      <c r="AH57" s="32"/>
+      <c r="AI57" s="95"/>
+      <c r="AJ57" s="31"/>
+      <c r="AK57" s="31"/>
+      <c r="AL57" s="32"/>
+      <c r="AM57" s="95"/>
+      <c r="AN57" s="31"/>
+      <c r="AO57" s="31"/>
+      <c r="AP57" s="32"/>
+    </row>
+    <row r="58" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="212" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" s="70"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="25"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="70"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="70"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="26"/>
+      <c r="O58" s="70"/>
+      <c r="P58" s="25"/>
+      <c r="Q58" s="25"/>
+      <c r="R58" s="26"/>
+      <c r="S58" s="70"/>
+      <c r="T58" s="25"/>
+      <c r="U58" s="25"/>
+      <c r="V58" s="26"/>
+      <c r="W58" s="70"/>
+      <c r="X58" s="25"/>
+      <c r="Y58" s="25"/>
+      <c r="Z58" s="26"/>
+      <c r="AA58" s="70"/>
+      <c r="AB58" s="25"/>
+      <c r="AC58" s="148"/>
+      <c r="AD58" s="26"/>
+      <c r="AE58" s="70"/>
+      <c r="AF58" s="25"/>
+      <c r="AG58" s="25"/>
+      <c r="AH58" s="26"/>
+      <c r="AI58" s="70"/>
+      <c r="AJ58" s="25"/>
+      <c r="AK58" s="25"/>
+      <c r="AL58" s="26"/>
+      <c r="AM58" s="70"/>
+      <c r="AN58" s="25"/>
+      <c r="AO58" s="25"/>
+      <c r="AP58" s="26"/>
+    </row>
+    <row r="59" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="213"/>
+      <c r="B59" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="95"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="95"/>
+      <c r="H59" s="31"/>
+      <c r="I59" s="31"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="95"/>
+      <c r="L59" s="31"/>
+      <c r="M59" s="31"/>
+      <c r="N59" s="32"/>
+      <c r="O59" s="95"/>
+      <c r="P59" s="31"/>
+      <c r="Q59" s="31"/>
+      <c r="R59" s="32"/>
+      <c r="S59" s="95"/>
+      <c r="T59" s="31"/>
+      <c r="U59" s="31"/>
+      <c r="V59" s="32"/>
+      <c r="W59" s="95"/>
+      <c r="X59" s="31"/>
+      <c r="Y59" s="31"/>
+      <c r="Z59" s="32"/>
+      <c r="AA59" s="95"/>
+      <c r="AB59" s="31"/>
+      <c r="AC59" s="31"/>
+      <c r="AD59" s="32"/>
+      <c r="AE59" s="95"/>
+      <c r="AF59" s="31"/>
+      <c r="AG59" s="31"/>
+      <c r="AH59" s="32"/>
+      <c r="AI59" s="95"/>
+      <c r="AJ59" s="31"/>
+      <c r="AK59" s="31"/>
+      <c r="AL59" s="32"/>
+      <c r="AM59" s="95"/>
+      <c r="AN59" s="31"/>
+      <c r="AO59" s="31"/>
+      <c r="AP59" s="32"/>
+    </row>
+    <row r="60" spans="1:51" s="40" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="212" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="70"/>
+      <c r="D60" s="25"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="25"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="70"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="25"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="70"/>
+      <c r="P60" s="25"/>
+      <c r="Q60" s="25"/>
+      <c r="R60" s="26"/>
+      <c r="S60" s="70"/>
+      <c r="T60" s="25"/>
+      <c r="U60" s="25"/>
+      <c r="V60" s="26"/>
+      <c r="W60" s="70"/>
+      <c r="X60" s="25"/>
+      <c r="Y60" s="25"/>
+      <c r="Z60" s="26"/>
+      <c r="AA60" s="70"/>
+      <c r="AB60" s="25"/>
+      <c r="AC60" s="25"/>
+      <c r="AD60" s="148"/>
+      <c r="AE60" s="70"/>
+      <c r="AF60" s="25"/>
+      <c r="AG60" s="25"/>
+      <c r="AH60" s="26"/>
+      <c r="AI60" s="70"/>
+      <c r="AJ60" s="25"/>
+      <c r="AK60" s="25"/>
+      <c r="AL60" s="26"/>
+      <c r="AM60" s="70"/>
+      <c r="AN60" s="25"/>
+      <c r="AO60" s="25"/>
+      <c r="AP60" s="26"/>
+      <c r="AQ60" s="2"/>
+      <c r="AR60" s="2"/>
+      <c r="AS60" s="2"/>
+      <c r="AT60" s="2"/>
+      <c r="AU60" s="2"/>
+      <c r="AV60" s="2"/>
+      <c r="AW60" s="2"/>
+      <c r="AX60" s="2"/>
+      <c r="AY60" s="2"/>
+    </row>
+    <row r="61" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="226"/>
+      <c r="B61" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" s="70"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="25"/>
+      <c r="I61" s="25"/>
+      <c r="J61" s="26"/>
+      <c r="K61" s="70"/>
+      <c r="L61" s="25"/>
+      <c r="M61" s="25"/>
+      <c r="N61" s="26"/>
+      <c r="O61" s="70"/>
+      <c r="P61" s="25"/>
+      <c r="Q61" s="25"/>
+      <c r="R61" s="26"/>
+      <c r="S61" s="70"/>
+      <c r="T61" s="25"/>
+      <c r="U61" s="25"/>
+      <c r="V61" s="26"/>
+      <c r="W61" s="70"/>
+      <c r="X61" s="25"/>
+      <c r="Y61" s="25"/>
+      <c r="Z61" s="26"/>
+      <c r="AA61" s="70"/>
+      <c r="AB61" s="25"/>
+      <c r="AC61" s="25"/>
+      <c r="AD61" s="26"/>
+      <c r="AE61" s="70"/>
+      <c r="AF61" s="25"/>
+      <c r="AG61" s="25"/>
+      <c r="AH61" s="26"/>
+      <c r="AI61" s="70"/>
+      <c r="AJ61" s="25"/>
+      <c r="AK61" s="25"/>
+      <c r="AL61" s="26"/>
+      <c r="AM61" s="70"/>
+      <c r="AN61" s="25"/>
+      <c r="AO61" s="25"/>
+      <c r="AP61" s="26"/>
+    </row>
+    <row r="62" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="82" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" s="167" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="96"/>
+      <c r="D62" s="98"/>
+      <c r="E62" s="98"/>
+      <c r="F62" s="113"/>
+      <c r="G62" s="100"/>
+      <c r="H62" s="98"/>
+      <c r="I62" s="98"/>
+      <c r="J62" s="113"/>
+      <c r="K62" s="100"/>
+      <c r="L62" s="98"/>
+      <c r="M62" s="98"/>
+      <c r="N62" s="113"/>
+      <c r="O62" s="100"/>
+      <c r="P62" s="98"/>
+      <c r="Q62" s="98"/>
+      <c r="R62" s="113"/>
+      <c r="S62" s="100"/>
+      <c r="T62" s="98"/>
+      <c r="U62" s="98"/>
+      <c r="V62" s="113"/>
+      <c r="W62" s="98"/>
+      <c r="X62" s="98"/>
+      <c r="Y62" s="98"/>
+      <c r="Z62" s="113"/>
+      <c r="AA62" s="98"/>
+      <c r="AB62" s="98"/>
+      <c r="AC62" s="98"/>
+      <c r="AD62" s="114"/>
+      <c r="AE62" s="120"/>
+      <c r="AF62" s="121"/>
+      <c r="AG62" s="121"/>
+      <c r="AH62" s="122"/>
+      <c r="AI62" s="100"/>
+      <c r="AJ62" s="98"/>
+      <c r="AK62" s="98"/>
+      <c r="AL62" s="113"/>
+      <c r="AM62" s="100"/>
+      <c r="AN62" s="98"/>
+      <c r="AO62" s="98"/>
+      <c r="AP62" s="113"/>
+    </row>
+    <row r="63" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="223" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63" s="94"/>
+      <c r="D63" s="29"/>
+      <c r="E63" s="29"/>
+      <c r="F63" s="30"/>
+      <c r="G63" s="94"/>
+      <c r="H63" s="29"/>
+      <c r="I63" s="29"/>
+      <c r="J63" s="30"/>
+      <c r="K63" s="94"/>
+      <c r="L63" s="29"/>
+      <c r="M63" s="29"/>
+      <c r="N63" s="30"/>
+      <c r="O63" s="94"/>
+      <c r="P63" s="29"/>
+      <c r="Q63" s="29"/>
+      <c r="R63" s="30"/>
+      <c r="S63" s="94"/>
+      <c r="T63" s="29"/>
+      <c r="U63" s="29"/>
+      <c r="V63" s="30"/>
+      <c r="W63" s="94"/>
+      <c r="X63" s="29"/>
+      <c r="Y63" s="29"/>
+      <c r="Z63" s="30"/>
+      <c r="AA63" s="94"/>
+      <c r="AB63" s="29"/>
+      <c r="AC63" s="29"/>
+      <c r="AD63" s="30"/>
+      <c r="AE63" s="150"/>
+      <c r="AF63" s="29"/>
+      <c r="AG63" s="29"/>
+      <c r="AH63" s="30"/>
+      <c r="AI63" s="94"/>
+      <c r="AJ63" s="29"/>
+      <c r="AK63" s="29"/>
+      <c r="AL63" s="30"/>
+      <c r="AM63" s="94"/>
+      <c r="AN63" s="29"/>
+      <c r="AO63" s="29"/>
+      <c r="AP63" s="30"/>
+    </row>
+    <row r="64" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="225"/>
+      <c r="B64" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C64" s="94"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="94"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="94"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="94"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="94"/>
+      <c r="T64" s="29"/>
+      <c r="U64" s="29"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="94"/>
+      <c r="X64" s="29"/>
+      <c r="Y64" s="29"/>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="94"/>
+      <c r="AB64" s="29"/>
+      <c r="AC64" s="29"/>
+      <c r="AD64" s="30"/>
+      <c r="AE64" s="94"/>
+      <c r="AF64" s="29"/>
+      <c r="AG64" s="29"/>
+      <c r="AH64" s="30"/>
+      <c r="AI64" s="94"/>
+      <c r="AJ64" s="29"/>
+      <c r="AK64" s="29"/>
+      <c r="AL64" s="30"/>
+      <c r="AM64" s="94"/>
+      <c r="AN64" s="29"/>
+      <c r="AO64" s="29"/>
+      <c r="AP64" s="30"/>
+    </row>
+    <row r="65" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="223" t="s">
+        <v>46</v>
+      </c>
+      <c r="B65" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C65" s="93"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="24"/>
+      <c r="G65" s="93"/>
+      <c r="H65" s="22"/>
+      <c r="I65" s="22"/>
+      <c r="J65" s="24"/>
+      <c r="K65" s="93"/>
+      <c r="L65" s="22"/>
+      <c r="M65" s="22"/>
+      <c r="N65" s="24"/>
+      <c r="O65" s="93"/>
+      <c r="P65" s="22"/>
+      <c r="Q65" s="22"/>
+      <c r="R65" s="24"/>
+      <c r="S65" s="93"/>
+      <c r="T65" s="22"/>
+      <c r="U65" s="22"/>
+      <c r="V65" s="24"/>
+      <c r="W65" s="93"/>
+      <c r="X65" s="22"/>
+      <c r="Y65" s="22"/>
+      <c r="Z65" s="24"/>
+      <c r="AA65" s="93"/>
+      <c r="AB65" s="22"/>
+      <c r="AC65" s="22"/>
+      <c r="AD65" s="24"/>
+      <c r="AE65" s="93"/>
+      <c r="AF65" s="148"/>
+      <c r="AG65" s="22"/>
+      <c r="AH65" s="24"/>
+      <c r="AI65" s="93"/>
+      <c r="AJ65" s="22"/>
+      <c r="AK65" s="22"/>
+      <c r="AL65" s="24"/>
+      <c r="AM65" s="93"/>
+      <c r="AN65" s="22"/>
+      <c r="AO65" s="22"/>
+      <c r="AP65" s="24"/>
+    </row>
+    <row r="66" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="225"/>
+      <c r="B66" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C66" s="95"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="32"/>
+      <c r="G66" s="95"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="32"/>
+      <c r="K66" s="95"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="31"/>
+      <c r="N66" s="32"/>
+      <c r="O66" s="95"/>
+      <c r="P66" s="31"/>
+      <c r="Q66" s="31"/>
+      <c r="R66" s="32"/>
+      <c r="S66" s="95"/>
+      <c r="T66" s="31"/>
+      <c r="U66" s="31"/>
+      <c r="V66" s="32"/>
+      <c r="W66" s="95"/>
+      <c r="X66" s="31"/>
+      <c r="Y66" s="31"/>
+      <c r="Z66" s="32"/>
+      <c r="AA66" s="95"/>
+      <c r="AB66" s="31"/>
+      <c r="AC66" s="31"/>
+      <c r="AD66" s="32"/>
+      <c r="AE66" s="95"/>
+      <c r="AF66" s="31"/>
+      <c r="AG66" s="31"/>
+      <c r="AH66" s="32"/>
+      <c r="AI66" s="95"/>
+      <c r="AJ66" s="31"/>
+      <c r="AK66" s="31"/>
+      <c r="AL66" s="32"/>
+      <c r="AM66" s="95"/>
+      <c r="AN66" s="31"/>
+      <c r="AO66" s="31"/>
+      <c r="AP66" s="32"/>
+    </row>
+    <row r="67" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="223" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="93"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="93"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="22"/>
+      <c r="J67" s="24"/>
+      <c r="K67" s="93"/>
+      <c r="L67" s="22"/>
+      <c r="M67" s="22"/>
+      <c r="N67" s="24"/>
+      <c r="O67" s="93"/>
+      <c r="P67" s="22"/>
+      <c r="Q67" s="22"/>
+      <c r="R67" s="24"/>
+      <c r="S67" s="93"/>
+      <c r="T67" s="22"/>
+      <c r="U67" s="22"/>
+      <c r="V67" s="24"/>
+      <c r="W67" s="93"/>
+      <c r="X67" s="22"/>
+      <c r="Y67" s="22"/>
+      <c r="Z67" s="24"/>
+      <c r="AA67" s="93"/>
+      <c r="AB67" s="22"/>
+      <c r="AC67" s="22"/>
+      <c r="AD67" s="24"/>
+      <c r="AE67" s="93"/>
+      <c r="AF67" s="22"/>
+      <c r="AG67" s="148"/>
+      <c r="AH67" s="148"/>
+      <c r="AI67" s="93"/>
+      <c r="AJ67" s="22"/>
+      <c r="AK67" s="22"/>
+      <c r="AL67" s="24"/>
+      <c r="AM67" s="93"/>
+      <c r="AN67" s="22"/>
+      <c r="AO67" s="22"/>
+      <c r="AP67" s="24"/>
+    </row>
+    <row r="68" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="224"/>
+      <c r="B68" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="136"/>
+      <c r="D68" s="134"/>
+      <c r="E68" s="139"/>
+      <c r="F68" s="143"/>
+      <c r="G68" s="136"/>
+      <c r="H68" s="134"/>
+      <c r="I68" s="139"/>
+      <c r="J68" s="143"/>
+      <c r="K68" s="136"/>
+      <c r="L68" s="134"/>
+      <c r="M68" s="139"/>
+      <c r="N68" s="143"/>
+      <c r="O68" s="136"/>
+      <c r="P68" s="134"/>
+      <c r="Q68" s="139"/>
+      <c r="R68" s="143"/>
+      <c r="S68" s="136"/>
+      <c r="T68" s="134"/>
+      <c r="U68" s="139"/>
+      <c r="V68" s="143"/>
+      <c r="W68" s="136"/>
+      <c r="X68" s="134"/>
+      <c r="Y68" s="139"/>
+      <c r="Z68" s="143"/>
+      <c r="AA68" s="136"/>
+      <c r="AB68" s="134"/>
+      <c r="AC68" s="139"/>
+      <c r="AD68" s="143"/>
+      <c r="AE68" s="136"/>
+      <c r="AF68" s="134"/>
+      <c r="AG68" s="139"/>
+      <c r="AH68" s="143"/>
+      <c r="AI68" s="136"/>
+      <c r="AJ68" s="134"/>
+      <c r="AK68" s="139"/>
+      <c r="AL68" s="143"/>
+      <c r="AM68" s="136"/>
+      <c r="AN68" s="134"/>
+      <c r="AO68" s="139"/>
+      <c r="AP68" s="143"/>
+    </row>
+    <row r="69" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="85" t="s">
+        <v>42</v>
+      </c>
+      <c r="B69" s="168" t="s">
+        <v>146</v>
+      </c>
+      <c r="C69" s="96"/>
+      <c r="D69" s="97"/>
+      <c r="E69" s="98"/>
+      <c r="F69" s="99"/>
+      <c r="G69" s="100"/>
+      <c r="H69" s="97"/>
+      <c r="I69" s="98"/>
+      <c r="J69" s="99"/>
+      <c r="K69" s="100"/>
+      <c r="L69" s="97"/>
+      <c r="M69" s="98"/>
+      <c r="N69" s="99"/>
+      <c r="O69" s="100"/>
+      <c r="P69" s="97"/>
+      <c r="Q69" s="98"/>
+      <c r="R69" s="99"/>
+      <c r="S69" s="100"/>
+      <c r="T69" s="97"/>
+      <c r="U69" s="98"/>
+      <c r="V69" s="99"/>
+      <c r="W69" s="98"/>
+      <c r="X69" s="97"/>
+      <c r="Y69" s="98"/>
+      <c r="Z69" s="99"/>
+      <c r="AA69" s="98"/>
+      <c r="AB69" s="97"/>
+      <c r="AC69" s="98"/>
+      <c r="AD69" s="99"/>
+      <c r="AE69" s="98"/>
+      <c r="AF69" s="97"/>
+      <c r="AG69" s="98"/>
+      <c r="AH69" s="97"/>
+      <c r="AI69" s="101"/>
+      <c r="AJ69" s="102"/>
+      <c r="AK69" s="102"/>
+      <c r="AL69" s="102"/>
+      <c r="AM69" s="101"/>
+      <c r="AN69" s="102"/>
+      <c r="AO69" s="102"/>
+      <c r="AP69" s="102"/>
+    </row>
+    <row r="70" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="258" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C70" s="28"/>
+      <c r="D70" s="88"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="91"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="88"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="91"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="88"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="91"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="88"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="91"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="88"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="91"/>
+      <c r="W70" s="29"/>
+      <c r="X70" s="88"/>
+      <c r="Y70" s="29"/>
+      <c r="Z70" s="91"/>
+      <c r="AA70" s="29"/>
+      <c r="AB70" s="88"/>
+      <c r="AC70" s="29"/>
+      <c r="AD70" s="91"/>
+      <c r="AE70" s="28"/>
+      <c r="AF70" s="88"/>
+      <c r="AG70" s="29"/>
+      <c r="AH70" s="91"/>
+      <c r="AI70" s="148"/>
+      <c r="AJ70" s="88"/>
+      <c r="AK70" s="29"/>
+      <c r="AL70" s="91"/>
+      <c r="AM70" s="28"/>
+      <c r="AN70" s="88"/>
+      <c r="AO70" s="29"/>
+      <c r="AP70" s="91"/>
+    </row>
+    <row r="71" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="259"/>
+      <c r="B71" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="28"/>
+      <c r="D71" s="88"/>
+      <c r="E71" s="29"/>
+      <c r="F71" s="91"/>
+      <c r="G71" s="28"/>
+      <c r="H71" s="88"/>
+      <c r="I71" s="29"/>
+      <c r="J71" s="91"/>
+      <c r="K71" s="28"/>
+      <c r="L71" s="88"/>
+      <c r="M71" s="29"/>
+      <c r="N71" s="91"/>
+      <c r="O71" s="28"/>
+      <c r="P71" s="88"/>
+      <c r="Q71" s="29"/>
+      <c r="R71" s="91"/>
+      <c r="S71" s="28"/>
+      <c r="T71" s="88"/>
+      <c r="U71" s="29"/>
+      <c r="V71" s="91"/>
+      <c r="W71" s="29"/>
+      <c r="X71" s="88"/>
+      <c r="Y71" s="29"/>
+      <c r="Z71" s="91"/>
+      <c r="AA71" s="29"/>
+      <c r="AB71" s="88"/>
+      <c r="AC71" s="29"/>
+      <c r="AD71" s="91"/>
+      <c r="AE71" s="28"/>
+      <c r="AF71" s="88"/>
+      <c r="AG71" s="29"/>
+      <c r="AH71" s="91"/>
+      <c r="AI71" s="28"/>
+      <c r="AJ71" s="88"/>
+      <c r="AK71" s="29"/>
+      <c r="AL71" s="91"/>
+      <c r="AM71" s="28"/>
+      <c r="AN71" s="88"/>
+      <c r="AO71" s="29"/>
+      <c r="AP71" s="91"/>
+    </row>
+    <row r="72" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="258" t="s">
+        <v>131</v>
+      </c>
+      <c r="B72" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="23"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="18"/>
+      <c r="G72" s="23"/>
+      <c r="H72" s="3"/>
+      <c r="I72" s="22"/>
+      <c r="J72" s="18"/>
+      <c r="K72" s="23"/>
+      <c r="L72" s="3"/>
+      <c r="M72" s="22"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="23"/>
+      <c r="P72" s="3"/>
+      <c r="Q72" s="22"/>
+      <c r="R72" s="18"/>
+      <c r="S72" s="23"/>
+      <c r="T72" s="3"/>
+      <c r="U72" s="22"/>
+      <c r="V72" s="18"/>
+      <c r="W72" s="22"/>
+      <c r="X72" s="3"/>
+      <c r="Y72" s="22"/>
+      <c r="Z72" s="18"/>
+      <c r="AA72" s="22"/>
+      <c r="AB72" s="3"/>
+      <c r="AC72" s="22"/>
+      <c r="AD72" s="18"/>
+      <c r="AE72" s="23"/>
+      <c r="AF72" s="3"/>
+      <c r="AG72" s="22"/>
+      <c r="AH72" s="18"/>
+      <c r="AI72" s="23"/>
+      <c r="AJ72" s="148"/>
+      <c r="AK72" s="22"/>
+      <c r="AL72" s="18"/>
+      <c r="AM72" s="23"/>
+      <c r="AN72" s="3"/>
+      <c r="AO72" s="22"/>
+      <c r="AP72" s="18"/>
+    </row>
+    <row r="73" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="259"/>
+      <c r="B73" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C73" s="23"/>
+      <c r="D73" s="3"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="18"/>
+      <c r="G73" s="23"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="22"/>
+      <c r="J73" s="18"/>
+      <c r="K73" s="23"/>
+      <c r="L73" s="3"/>
+      <c r="M73" s="22"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="23"/>
+      <c r="P73" s="3"/>
+      <c r="Q73" s="22"/>
+      <c r="R73" s="18"/>
+      <c r="S73" s="23"/>
+      <c r="T73" s="3"/>
+      <c r="U73" s="22"/>
+      <c r="V73" s="18"/>
+      <c r="W73" s="22"/>
+      <c r="X73" s="3"/>
+      <c r="Y73" s="22"/>
+      <c r="Z73" s="18"/>
+      <c r="AA73" s="22"/>
+      <c r="AB73" s="3"/>
+      <c r="AC73" s="22"/>
+      <c r="AD73" s="18"/>
+      <c r="AE73" s="23"/>
+      <c r="AF73" s="3"/>
+      <c r="AG73" s="22"/>
+      <c r="AH73" s="18"/>
+      <c r="AI73" s="23"/>
+      <c r="AJ73" s="3"/>
+      <c r="AK73" s="22"/>
+      <c r="AL73" s="18"/>
+      <c r="AM73" s="23"/>
+      <c r="AN73" s="3"/>
+      <c r="AO73" s="22"/>
+      <c r="AP73" s="18"/>
+    </row>
+    <row r="74" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="258" t="s">
+        <v>135</v>
+      </c>
+      <c r="B74" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C74" s="23"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="18"/>
+      <c r="G74" s="23"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="22"/>
+      <c r="J74" s="18"/>
+      <c r="K74" s="23"/>
+      <c r="L74" s="3"/>
+      <c r="M74" s="22"/>
+      <c r="N74" s="18"/>
+      <c r="O74" s="23"/>
+      <c r="P74" s="3"/>
+      <c r="Q74" s="22"/>
+      <c r="R74" s="18"/>
+      <c r="S74" s="23"/>
+      <c r="T74" s="3"/>
+      <c r="U74" s="22"/>
+      <c r="V74" s="18"/>
+      <c r="W74" s="22"/>
+      <c r="X74" s="3"/>
+      <c r="Y74" s="22"/>
+      <c r="Z74" s="18"/>
+      <c r="AA74" s="22"/>
+      <c r="AB74" s="3"/>
+      <c r="AC74" s="22"/>
+      <c r="AD74" s="18"/>
+      <c r="AE74" s="23"/>
+      <c r="AF74" s="3"/>
+      <c r="AG74" s="22"/>
+      <c r="AH74" s="18"/>
+      <c r="AI74" s="146"/>
+      <c r="AJ74" s="154"/>
+      <c r="AK74" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL74" s="18"/>
+      <c r="AM74" s="23"/>
+      <c r="AN74" s="3"/>
+      <c r="AO74" s="22"/>
+      <c r="AP74" s="18"/>
+    </row>
+    <row r="75" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="259"/>
+      <c r="B75" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" s="23"/>
+      <c r="D75" s="3"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="23"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="22"/>
+      <c r="J75" s="18"/>
+      <c r="K75" s="23"/>
+      <c r="L75" s="3"/>
+      <c r="M75" s="22"/>
+      <c r="N75" s="18"/>
+      <c r="O75" s="23"/>
+      <c r="P75" s="3"/>
+      <c r="Q75" s="22"/>
+      <c r="R75" s="18"/>
+      <c r="S75" s="23"/>
+      <c r="T75" s="3"/>
+      <c r="U75" s="22"/>
+      <c r="V75" s="18"/>
+      <c r="W75" s="22"/>
+      <c r="X75" s="3"/>
+      <c r="Y75" s="22"/>
+      <c r="Z75" s="18"/>
+      <c r="AA75" s="22"/>
+      <c r="AB75" s="3"/>
+      <c r="AC75" s="22"/>
+      <c r="AD75" s="18"/>
+      <c r="AE75" s="23"/>
+      <c r="AF75" s="3"/>
+      <c r="AG75" s="22"/>
+      <c r="AH75" s="18"/>
+      <c r="AI75" s="23"/>
+      <c r="AJ75" s="3"/>
+      <c r="AK75" s="22"/>
+      <c r="AL75" s="18"/>
+      <c r="AM75" s="23"/>
+      <c r="AN75" s="3"/>
+      <c r="AO75" s="22"/>
+      <c r="AP75" s="18"/>
+    </row>
+    <row r="76" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="258" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="141" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" s="23"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="18"/>
+      <c r="G76" s="23"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="22"/>
+      <c r="J76" s="18"/>
+      <c r="K76" s="23"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="22"/>
+      <c r="N76" s="18"/>
+      <c r="O76" s="23"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="22"/>
+      <c r="R76" s="18"/>
+      <c r="S76" s="23"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="22"/>
+      <c r="V76" s="18"/>
+      <c r="W76" s="22"/>
+      <c r="X76" s="3"/>
+      <c r="Y76" s="22"/>
+      <c r="Z76" s="18"/>
+      <c r="AA76" s="22"/>
+      <c r="AB76" s="3"/>
+      <c r="AC76" s="22"/>
+      <c r="AD76" s="18"/>
+      <c r="AE76" s="23"/>
+      <c r="AF76" s="3"/>
+      <c r="AG76" s="22"/>
+      <c r="AH76" s="18"/>
+      <c r="AI76" s="23"/>
+      <c r="AJ76" s="3"/>
+      <c r="AK76" s="155" t="s">
+        <v>139</v>
+      </c>
+      <c r="AL76" s="256" t="s">
+        <v>139</v>
+      </c>
+      <c r="AM76" s="23"/>
+      <c r="AN76" s="3"/>
+      <c r="AO76" s="22"/>
+      <c r="AP76" s="18"/>
+    </row>
+    <row r="77" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="259"/>
+      <c r="B77" s="142" t="s">
+        <v>133</v>
+      </c>
+      <c r="C77" s="33"/>
+      <c r="D77" s="144"/>
+      <c r="E77" s="31"/>
+      <c r="F77" s="145"/>
+      <c r="G77" s="33"/>
+      <c r="H77" s="144"/>
+      <c r="I77" s="31"/>
+      <c r="J77" s="145"/>
+      <c r="K77" s="33"/>
+      <c r="L77" s="144"/>
+      <c r="M77" s="31"/>
+      <c r="N77" s="145"/>
+      <c r="O77" s="33"/>
+      <c r="P77" s="144"/>
+      <c r="Q77" s="31"/>
+      <c r="R77" s="145"/>
+      <c r="S77" s="33"/>
+      <c r="T77" s="144"/>
+      <c r="U77" s="31"/>
+      <c r="V77" s="145"/>
+      <c r="W77" s="31"/>
+      <c r="X77" s="144"/>
+      <c r="Y77" s="31"/>
+      <c r="Z77" s="145"/>
+      <c r="AA77" s="31"/>
+      <c r="AB77" s="144"/>
+      <c r="AC77" s="31"/>
+      <c r="AD77" s="145"/>
+      <c r="AE77" s="33"/>
+      <c r="AF77" s="144"/>
+      <c r="AG77" s="31"/>
+      <c r="AH77" s="145"/>
+      <c r="AI77" s="33"/>
+      <c r="AJ77" s="144"/>
+      <c r="AK77" s="31"/>
+      <c r="AL77" s="145"/>
+      <c r="AM77" s="33"/>
+      <c r="AN77" s="144"/>
+      <c r="AO77" s="31"/>
+      <c r="AP77" s="145"/>
+    </row>
+    <row r="78" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="B78" s="141" t="s">
@@ -9162,17 +13392,19 @@
       <c r="AF78" s="3"/>
       <c r="AG78" s="22"/>
       <c r="AH78" s="18"/>
-      <c r="AI78" s="23"/>
-      <c r="AJ78" s="3"/>
-      <c r="AK78" s="22"/>
-      <c r="AL78" s="18"/>
+      <c r="AI78" s="27"/>
+      <c r="AJ78" s="43"/>
+      <c r="AK78" s="25"/>
+      <c r="AL78" s="257" t="s">
+        <v>139</v>
+      </c>
       <c r="AM78" s="23"/>
       <c r="AN78" s="3"/>
-      <c r="AO78" s="148"/>
-      <c r="AP78" s="148"/>
-    </row>
-    <row r="79" spans="1:42" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="174"/>
+      <c r="AO78" s="22"/>
+      <c r="AP78" s="18"/>
+    </row>
+    <row r="79" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="259"/>
       <c r="B79" s="142" t="s">
         <v>133</v>
       </c>
@@ -9217,8 +13449,56 @@
       <c r="AO79" s="25"/>
       <c r="AP79" s="44"/>
     </row>
+    <row r="80" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="250" t="s">
+        <v>166</v>
+      </c>
+      <c r="B80" s="168" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="96"/>
+      <c r="D80" s="97"/>
+      <c r="E80" s="98"/>
+      <c r="F80" s="99"/>
+      <c r="G80" s="100"/>
+      <c r="H80" s="97"/>
+      <c r="I80" s="98"/>
+      <c r="J80" s="99"/>
+      <c r="K80" s="100"/>
+      <c r="L80" s="97"/>
+      <c r="M80" s="98"/>
+      <c r="N80" s="99"/>
+      <c r="O80" s="100"/>
+      <c r="P80" s="97"/>
+      <c r="Q80" s="98"/>
+      <c r="R80" s="99"/>
+      <c r="S80" s="100"/>
+      <c r="T80" s="97"/>
+      <c r="U80" s="98"/>
+      <c r="V80" s="99"/>
+      <c r="W80" s="98"/>
+      <c r="X80" s="97"/>
+      <c r="Y80" s="98"/>
+      <c r="Z80" s="99"/>
+      <c r="AA80" s="100"/>
+      <c r="AB80" s="97"/>
+      <c r="AC80" s="98"/>
+      <c r="AD80" s="99"/>
+      <c r="AE80" s="100"/>
+      <c r="AF80" s="97"/>
+      <c r="AG80" s="98"/>
+      <c r="AH80" s="99"/>
+      <c r="AI80" s="100"/>
+      <c r="AJ80" s="97"/>
+      <c r="AK80" s="98"/>
+      <c r="AL80" s="99"/>
+      <c r="AM80" s="251"/>
+      <c r="AN80" s="252"/>
+      <c r="AO80" s="251"/>
+      <c r="AP80" s="253"/>
+    </row>
   </sheetData>
-  <mergeCells count="56">
+  <mergeCells count="52">
     <mergeCell ref="A1:AP1"/>
     <mergeCell ref="C3:F3"/>
     <mergeCell ref="G3:J3"/>
@@ -9230,26 +13510,20 @@
     <mergeCell ref="AE3:AH3"/>
     <mergeCell ref="AI3:AL3"/>
     <mergeCell ref="AM3:AP3"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:AP2"/>
+    <mergeCell ref="AI4:AL4"/>
+    <mergeCell ref="AM4:AP4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="O4:R4"/>
     <mergeCell ref="S4:V4"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A20:A21"/>
     <mergeCell ref="W4:Z4"/>
     <mergeCell ref="AA4:AD4"/>
     <mergeCell ref="AE4:AH4"/>
-    <mergeCell ref="AI4:AL4"/>
-    <mergeCell ref="AM4:AP4"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="A78:A79"/>
     <mergeCell ref="A54:A55"/>
     <mergeCell ref="A52:A53"/>
     <mergeCell ref="A50:A51"/>
@@ -9260,12 +13534,6 @@
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="A56:A57"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A70:A71"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A9:A10"/>
@@ -9275,6 +13543,14 @@
     <mergeCell ref="A35:A36"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A31:A32"/>
+    <mergeCell ref="A18:A19"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="A42:A43"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A24:A25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
@@ -9285,7 +13561,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACB918FC-3D05-4FF4-9E9E-CDCD199190E4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -9298,49 +13574,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="194" t="s">
+      <c r="A1" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="194"/>
-      <c r="C1" s="194"/>
-      <c r="D1" s="194"/>
-      <c r="E1" s="194"/>
-      <c r="F1" s="194"/>
-      <c r="G1" s="194"/>
-      <c r="H1" s="194"/>
-      <c r="I1" s="194"/>
-      <c r="J1" s="194"/>
-      <c r="K1" s="194"/>
-      <c r="L1" s="194"/>
-      <c r="M1" s="194"/>
-      <c r="N1" s="194"/>
-      <c r="O1" s="194"/>
-      <c r="P1" s="194"/>
-      <c r="Q1" s="194"/>
-      <c r="R1" s="194"/>
-      <c r="S1" s="194"/>
-      <c r="T1" s="194"/>
-      <c r="U1" s="194"/>
-      <c r="V1" s="194"/>
-      <c r="W1" s="194"/>
-      <c r="X1" s="194"/>
-      <c r="Y1" s="194"/>
-      <c r="Z1" s="194"/>
-      <c r="AA1" s="194"/>
-      <c r="AB1" s="194"/>
-      <c r="AC1" s="194"/>
-      <c r="AD1" s="194"/>
-      <c r="AE1" s="194"/>
-      <c r="AF1" s="194"/>
-      <c r="AG1" s="194"/>
-      <c r="AH1" s="194"/>
-      <c r="AI1" s="194"/>
-      <c r="AJ1" s="194"/>
-      <c r="AK1" s="194"/>
-      <c r="AL1" s="194"/>
-      <c r="AM1" s="194"/>
-      <c r="AN1" s="194"/>
-      <c r="AO1" s="194"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
+      <c r="H1" s="203"/>
+      <c r="I1" s="203"/>
+      <c r="J1" s="203"/>
+      <c r="K1" s="203"/>
+      <c r="L1" s="203"/>
+      <c r="M1" s="203"/>
+      <c r="N1" s="203"/>
+      <c r="O1" s="203"/>
+      <c r="P1" s="203"/>
+      <c r="Q1" s="203"/>
+      <c r="R1" s="203"/>
+      <c r="S1" s="203"/>
+      <c r="T1" s="203"/>
+      <c r="U1" s="203"/>
+      <c r="V1" s="203"/>
+      <c r="W1" s="203"/>
+      <c r="X1" s="203"/>
+      <c r="Y1" s="203"/>
+      <c r="Z1" s="203"/>
+      <c r="AA1" s="203"/>
+      <c r="AB1" s="203"/>
+      <c r="AC1" s="203"/>
+      <c r="AD1" s="203"/>
+      <c r="AE1" s="203"/>
+      <c r="AF1" s="203"/>
+      <c r="AG1" s="203"/>
+      <c r="AH1" s="203"/>
+      <c r="AI1" s="203"/>
+      <c r="AJ1" s="203"/>
+      <c r="AK1" s="203"/>
+      <c r="AL1" s="203"/>
+      <c r="AM1" s="203"/>
+      <c r="AN1" s="203"/>
+      <c r="AO1" s="203"/>
     </row>
     <row r="2" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -9351,131 +13627,131 @@
       <c r="A3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="191" t="s">
+      <c r="B3" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="193"/>
-      <c r="F3" s="191" t="s">
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="210"/>
+      <c r="F3" s="208" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192"/>
-      <c r="I3" s="193"/>
-      <c r="J3" s="191" t="s">
+      <c r="G3" s="209"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="210"/>
+      <c r="J3" s="208" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="192"/>
-      <c r="L3" s="192"/>
-      <c r="M3" s="193"/>
-      <c r="N3" s="191" t="s">
+      <c r="K3" s="209"/>
+      <c r="L3" s="209"/>
+      <c r="M3" s="210"/>
+      <c r="N3" s="208" t="s">
         <v>97</v>
       </c>
-      <c r="O3" s="192"/>
-      <c r="P3" s="192"/>
-      <c r="Q3" s="193"/>
-      <c r="R3" s="191" t="s">
+      <c r="O3" s="209"/>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="210"/>
+      <c r="R3" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="S3" s="192"/>
-      <c r="T3" s="192"/>
-      <c r="U3" s="193"/>
-      <c r="V3" s="191" t="s">
+      <c r="S3" s="209"/>
+      <c r="T3" s="209"/>
+      <c r="U3" s="210"/>
+      <c r="V3" s="208" t="s">
         <v>95</v>
       </c>
-      <c r="W3" s="192"/>
-      <c r="X3" s="192"/>
-      <c r="Y3" s="193"/>
-      <c r="Z3" s="191" t="s">
+      <c r="W3" s="209"/>
+      <c r="X3" s="209"/>
+      <c r="Y3" s="210"/>
+      <c r="Z3" s="208" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="192"/>
-      <c r="AB3" s="192"/>
-      <c r="AC3" s="193"/>
-      <c r="AD3" s="191" t="s">
+      <c r="AA3" s="209"/>
+      <c r="AB3" s="209"/>
+      <c r="AC3" s="210"/>
+      <c r="AD3" s="208" t="s">
         <v>97</v>
       </c>
-      <c r="AE3" s="192"/>
-      <c r="AF3" s="192"/>
-      <c r="AG3" s="193"/>
-      <c r="AH3" s="191" t="s">
+      <c r="AE3" s="209"/>
+      <c r="AF3" s="209"/>
+      <c r="AG3" s="210"/>
+      <c r="AH3" s="208" t="s">
         <v>98</v>
       </c>
-      <c r="AI3" s="192"/>
-      <c r="AJ3" s="192"/>
-      <c r="AK3" s="193"/>
-      <c r="AL3" s="191" t="s">
+      <c r="AI3" s="209"/>
+      <c r="AJ3" s="209"/>
+      <c r="AK3" s="210"/>
+      <c r="AL3" s="208" t="s">
         <v>94</v>
       </c>
-      <c r="AM3" s="192"/>
-      <c r="AN3" s="192"/>
-      <c r="AO3" s="193"/>
+      <c r="AM3" s="209"/>
+      <c r="AN3" s="209"/>
+      <c r="AO3" s="210"/>
     </row>
     <row r="4" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>46139</v>
       </c>
-      <c r="B4" s="185" t="s">
+      <c r="B4" s="205" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="187"/>
-      <c r="F4" s="185" t="s">
+      <c r="C4" s="206"/>
+      <c r="D4" s="206"/>
+      <c r="E4" s="207"/>
+      <c r="F4" s="205" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="187"/>
-      <c r="J4" s="185" t="s">
+      <c r="G4" s="206"/>
+      <c r="H4" s="206"/>
+      <c r="I4" s="207"/>
+      <c r="J4" s="205" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
-      <c r="M4" s="187"/>
-      <c r="N4" s="185" t="s">
+      <c r="K4" s="206"/>
+      <c r="L4" s="206"/>
+      <c r="M4" s="207"/>
+      <c r="N4" s="205" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="186"/>
-      <c r="P4" s="186"/>
-      <c r="Q4" s="187"/>
-      <c r="R4" s="185" t="s">
+      <c r="O4" s="206"/>
+      <c r="P4" s="206"/>
+      <c r="Q4" s="207"/>
+      <c r="R4" s="205" t="s">
         <v>103</v>
       </c>
-      <c r="S4" s="186"/>
-      <c r="T4" s="186"/>
-      <c r="U4" s="187"/>
-      <c r="V4" s="185" t="s">
+      <c r="S4" s="206"/>
+      <c r="T4" s="206"/>
+      <c r="U4" s="207"/>
+      <c r="V4" s="205" t="s">
         <v>104</v>
       </c>
-      <c r="W4" s="186"/>
-      <c r="X4" s="186"/>
-      <c r="Y4" s="187"/>
-      <c r="Z4" s="185" t="s">
+      <c r="W4" s="206"/>
+      <c r="X4" s="206"/>
+      <c r="Y4" s="207"/>
+      <c r="Z4" s="205" t="s">
         <v>105</v>
       </c>
-      <c r="AA4" s="186"/>
-      <c r="AB4" s="186"/>
-      <c r="AC4" s="187"/>
-      <c r="AD4" s="185" t="s">
+      <c r="AA4" s="206"/>
+      <c r="AB4" s="206"/>
+      <c r="AC4" s="207"/>
+      <c r="AD4" s="205" t="s">
         <v>106</v>
       </c>
-      <c r="AE4" s="186"/>
-      <c r="AF4" s="186"/>
-      <c r="AG4" s="187"/>
-      <c r="AH4" s="185" t="s">
+      <c r="AE4" s="206"/>
+      <c r="AF4" s="206"/>
+      <c r="AG4" s="207"/>
+      <c r="AH4" s="205" t="s">
         <v>107</v>
       </c>
-      <c r="AI4" s="186"/>
-      <c r="AJ4" s="186"/>
-      <c r="AK4" s="187"/>
-      <c r="AL4" s="185" t="s">
+      <c r="AI4" s="206"/>
+      <c r="AJ4" s="206"/>
+      <c r="AK4" s="207"/>
+      <c r="AL4" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="AM4" s="186"/>
-      <c r="AN4" s="186"/>
-      <c r="AO4" s="187"/>
+      <c r="AM4" s="206"/>
+      <c r="AN4" s="206"/>
+      <c r="AO4" s="207"/>
     </row>
     <row r="5" spans="1:59" s="38" customFormat="1" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="123" t="s">
@@ -11039,38 +15315,38 @@
       </c>
     </row>
     <row r="40" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Z40" s="195" t="s">
+      <c r="Z40" s="230" t="s">
         <v>21</v>
       </c>
-      <c r="AA40" s="196"/>
-      <c r="AB40" s="199" t="s">
+      <c r="AA40" s="231"/>
+      <c r="AB40" s="234" t="s">
         <v>88</v>
       </c>
-      <c r="AC40" s="200"/>
-      <c r="AD40" s="203" t="s">
+      <c r="AC40" s="235"/>
+      <c r="AD40" s="238" t="s">
         <v>22</v>
       </c>
-      <c r="AE40" s="204"/>
-      <c r="AF40" s="207" t="s">
+      <c r="AE40" s="239"/>
+      <c r="AF40" s="242" t="s">
         <v>50</v>
       </c>
-      <c r="AG40" s="208"/>
-      <c r="AH40" s="211" t="s">
+      <c r="AG40" s="243"/>
+      <c r="AH40" s="246" t="s">
         <v>49</v>
       </c>
-      <c r="AI40" s="212"/>
+      <c r="AI40" s="247"/>
     </row>
     <row r="41" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Z41" s="197"/>
-      <c r="AA41" s="198"/>
-      <c r="AB41" s="201"/>
-      <c r="AC41" s="202"/>
-      <c r="AD41" s="205"/>
-      <c r="AE41" s="206"/>
-      <c r="AF41" s="209"/>
-      <c r="AG41" s="210"/>
-      <c r="AH41" s="213"/>
-      <c r="AI41" s="214"/>
+      <c r="Z41" s="232"/>
+      <c r="AA41" s="233"/>
+      <c r="AB41" s="236"/>
+      <c r="AC41" s="237"/>
+      <c r="AD41" s="240"/>
+      <c r="AE41" s="241"/>
+      <c r="AF41" s="244"/>
+      <c r="AG41" s="245"/>
+      <c r="AH41" s="248"/>
+      <c r="AI41" s="249"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -11140,7 +15416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD0909FF-ECD9-424D-94FC-D75424C77729}">
   <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -11323,7 +15599,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
@@ -11424,21 +15700,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100FCF048E0986C15438F7A127842D0194A" ma:contentTypeVersion="4" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7cab3d809e4a910b1c584eedef949ce5">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="2853aef8-30e6-4fd3-8cd7-0e6e5ead6b25" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f65b7f7a473b6f476768514c8a355f09" ns3:_="">
     <xsd:import namespace="2853aef8-30e6-4fd3-8cd7-0e6e5ead6b25"/>
@@ -11582,15 +15849,16 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5144944C-1F1D-4162-962A-96F3FC8455D8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
@@ -11606,7 +15874,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3E44D37-32CE-46BD-B496-8A4726A23AD3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -11624,6 +15892,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8FE8ED85-58B3-4608-8E91-0433556D50CE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{7b4c4ed3-e3fa-42f6-b1f6-2820b014570a}" enabled="1" method="Standard" siteId="{9e3cc295-461f-41c6-9bf4-f0d2c086e9a1}" removed="0"/>

--- a/Gantt Zeitplan Josiah Spilker.xlsx
+++ b/Gantt Zeitplan Josiah Spilker.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1DA0B313-9E82-4B7E-BCAF-0F02F07A6644}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D1EC714-81D8-4DD8-BE18-6DE63698BD93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="29010" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project plan" sheetId="11" r:id="rId1"/>
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="168">
   <si>
     <t>EINFACHES GANTT-DIAGRAMM von Vertex42.com</t>
   </si>
@@ -547,31 +547,34 @@
     <t>Wed.</t>
   </si>
   <si>
-    <t>T3 : Decide                                              5h</t>
-  </si>
-  <si>
-    <t>T5 : Control                                              6h</t>
-  </si>
-  <si>
-    <t>T1 : Inform                                               3h</t>
-  </si>
-  <si>
-    <t>T2 : Plan                                                 14h</t>
-  </si>
-  <si>
     <t>27.04.2026                                   / = &lt;1h</t>
   </si>
   <si>
-    <t>T0 : Documentation/Administration  16h</t>
-  </si>
-  <si>
-    <t>T4 : Realise                                            18h</t>
-  </si>
-  <si>
-    <t>T6 : Evaluate                                          8h</t>
-  </si>
-  <si>
     <t>T7 : Buffer                                             8h</t>
+  </si>
+  <si>
+    <t>T1 : Inform                                       3h</t>
+  </si>
+  <si>
+    <t>T0 : Documentation/Admin.        16h</t>
+  </si>
+  <si>
+    <t>T2 : Plan                                         14h</t>
+  </si>
+  <si>
+    <t>T3 : Decide                                       5h</t>
+  </si>
+  <si>
+    <t>T4 : Realise                                    18h</t>
+  </si>
+  <si>
+    <t>T5 : Control                                      6h</t>
+  </si>
+  <si>
+    <t>T6 : Evaluate                                    8h</t>
+  </si>
+  <si>
+    <t>T7 : Buffer                                        8h</t>
   </si>
 </sst>
 </file>
@@ -2152,7 +2155,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="3" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="3" applyFont="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="262">
+  <cellXfs count="265">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2691,6 +2694,48 @@
     <xf numFmtId="0" fontId="0" fillId="51" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="53" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="53" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="48" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="48" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="53" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="47" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="46" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2700,6 +2745,12 @@
     <xf numFmtId="0" fontId="35" fillId="46" borderId="41" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="69" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="68" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="35" fillId="9" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2709,12 +2760,6 @@
     <xf numFmtId="0" fontId="35" fillId="9" borderId="41" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="69" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="68" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="3" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2727,6 +2772,15 @@
     <xf numFmtId="0" fontId="35" fillId="10" borderId="61" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="61" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="44" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="35" fillId="6" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2736,18 +2790,9 @@
     <xf numFmtId="49" fontId="35" fillId="6" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="35" fillId="2" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="2" borderId="61" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="44" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2775,6 +2820,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2799,12 +2850,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2889,41 +2934,8 @@
     <xf numFmtId="0" fontId="32" fillId="52" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="53" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="53" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="50" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="45" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="48" borderId="17" xfId="12" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="48" borderId="45" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="48" borderId="17" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="58">
@@ -3523,233 +3535,233 @@
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="42.85546875" customWidth="1"/>
-    <col min="2" max="13" width="2.7109375" hidden="1" customWidth="1"/>
-    <col min="14" max="41" width="2.7109375" customWidth="1"/>
+    <col min="2" max="17" width="2.7109375" hidden="1" customWidth="1"/>
+    <col min="18" max="41" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="217" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="203"/>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="203"/>
-      <c r="Y1" s="203"/>
-      <c r="Z1" s="203"/>
-      <c r="AA1" s="203"/>
-      <c r="AB1" s="203"/>
-      <c r="AC1" s="203"/>
-      <c r="AD1" s="203"/>
-      <c r="AE1" s="203"/>
-      <c r="AF1" s="203"/>
-      <c r="AG1" s="203"/>
-      <c r="AH1" s="203"/>
-      <c r="AI1" s="203"/>
-      <c r="AJ1" s="203"/>
-      <c r="AK1" s="203"/>
-      <c r="AL1" s="203"/>
-      <c r="AM1" s="203"/>
-      <c r="AN1" s="203"/>
-      <c r="AO1" s="203"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="217"/>
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="217"/>
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="217"/>
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="217"/>
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="217"/>
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="217"/>
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="217"/>
     </row>
     <row r="2" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
       <c r="B2" s="172"/>
-      <c r="C2" s="211" t="s">
+      <c r="C2" s="225" t="s">
         <v>148</v>
       </c>
-      <c r="D2" s="211"/>
-      <c r="E2" s="211"/>
-      <c r="F2" s="211"/>
-      <c r="G2" s="211"/>
-      <c r="H2" s="211"/>
-      <c r="I2" s="211"/>
-      <c r="J2" s="211"/>
-      <c r="K2" s="211"/>
-      <c r="L2" s="211"/>
-      <c r="M2" s="211"/>
-      <c r="N2" s="211"/>
-      <c r="O2" s="211"/>
-      <c r="P2" s="211"/>
-      <c r="Q2" s="211"/>
-      <c r="R2" s="211"/>
-      <c r="S2" s="211"/>
-      <c r="T2" s="211"/>
-      <c r="U2" s="211"/>
-      <c r="V2" s="211"/>
-      <c r="W2" s="211"/>
-      <c r="X2" s="211"/>
-      <c r="Y2" s="211"/>
-      <c r="Z2" s="211"/>
-      <c r="AA2" s="211"/>
-      <c r="AB2" s="211"/>
-      <c r="AC2" s="211"/>
-      <c r="AD2" s="211"/>
-      <c r="AE2" s="211"/>
-      <c r="AF2" s="211"/>
-      <c r="AG2" s="211"/>
-      <c r="AH2" s="211"/>
-      <c r="AI2" s="211"/>
-      <c r="AJ2" s="211"/>
-      <c r="AK2" s="211"/>
-      <c r="AL2" s="211"/>
-      <c r="AM2" s="211"/>
-      <c r="AN2" s="211"/>
-      <c r="AO2" s="211"/>
+      <c r="D2" s="225"/>
+      <c r="E2" s="225"/>
+      <c r="F2" s="225"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="225"/>
+      <c r="I2" s="225"/>
+      <c r="J2" s="225"/>
+      <c r="K2" s="225"/>
+      <c r="L2" s="225"/>
+      <c r="M2" s="225"/>
+      <c r="N2" s="225"/>
+      <c r="O2" s="225"/>
+      <c r="P2" s="225"/>
+      <c r="Q2" s="225"/>
+      <c r="R2" s="225"/>
+      <c r="S2" s="225"/>
+      <c r="T2" s="225"/>
+      <c r="U2" s="225"/>
+      <c r="V2" s="225"/>
+      <c r="W2" s="225"/>
+      <c r="X2" s="225"/>
+      <c r="Y2" s="225"/>
+      <c r="Z2" s="225"/>
+      <c r="AA2" s="225"/>
+      <c r="AB2" s="225"/>
+      <c r="AC2" s="225"/>
+      <c r="AD2" s="225"/>
+      <c r="AE2" s="225"/>
+      <c r="AF2" s="225"/>
+      <c r="AG2" s="225"/>
+      <c r="AH2" s="225"/>
+      <c r="AI2" s="225"/>
+      <c r="AJ2" s="225"/>
+      <c r="AK2" s="225"/>
+      <c r="AL2" s="225"/>
+      <c r="AM2" s="225"/>
+      <c r="AN2" s="225"/>
+      <c r="AO2" s="225"/>
     </row>
     <row r="3" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="208" t="s">
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="209"/>
-      <c r="H3" s="209"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="208" t="s">
+      <c r="G3" s="223"/>
+      <c r="H3" s="223"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="222" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="208" t="s">
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
+      <c r="M3" s="224"/>
+      <c r="N3" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="O3" s="209"/>
-      <c r="P3" s="209"/>
-      <c r="Q3" s="210"/>
-      <c r="R3" s="208" t="s">
+      <c r="O3" s="223"/>
+      <c r="P3" s="223"/>
+      <c r="Q3" s="224"/>
+      <c r="R3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="S3" s="209"/>
-      <c r="T3" s="209"/>
-      <c r="U3" s="210"/>
-      <c r="V3" s="208" t="s">
+      <c r="S3" s="223"/>
+      <c r="T3" s="223"/>
+      <c r="U3" s="224"/>
+      <c r="V3" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="W3" s="209"/>
-      <c r="X3" s="209"/>
-      <c r="Y3" s="210"/>
-      <c r="Z3" s="208" t="s">
+      <c r="W3" s="223"/>
+      <c r="X3" s="223"/>
+      <c r="Y3" s="224"/>
+      <c r="Z3" s="222" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="209"/>
-      <c r="AB3" s="209"/>
-      <c r="AC3" s="210"/>
-      <c r="AD3" s="208" t="s">
+      <c r="AA3" s="223"/>
+      <c r="AB3" s="223"/>
+      <c r="AC3" s="224"/>
+      <c r="AD3" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="209"/>
-      <c r="AG3" s="210"/>
-      <c r="AH3" s="208" t="s">
+      <c r="AE3" s="223"/>
+      <c r="AF3" s="223"/>
+      <c r="AG3" s="224"/>
+      <c r="AH3" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="AI3" s="209"/>
-      <c r="AJ3" s="209"/>
-      <c r="AK3" s="210"/>
-      <c r="AL3" s="208" t="s">
+      <c r="AI3" s="223"/>
+      <c r="AJ3" s="223"/>
+      <c r="AK3" s="224"/>
+      <c r="AL3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="AM3" s="209"/>
-      <c r="AN3" s="209"/>
-      <c r="AO3" s="210"/>
-    </row>
-    <row r="4" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AM3" s="223"/>
+      <c r="AN3" s="223"/>
+      <c r="AO3" s="224"/>
+    </row>
+    <row r="4" spans="1:59" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>46139</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="219" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="205" t="s">
+      <c r="C4" s="220"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="219" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="205" t="s">
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="219" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="206"/>
-      <c r="L4" s="206"/>
-      <c r="M4" s="207"/>
-      <c r="N4" s="205" t="s">
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="205" t="s">
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="207"/>
-      <c r="V4" s="205" t="s">
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="219" t="s">
         <v>104</v>
       </c>
-      <c r="W4" s="206"/>
-      <c r="X4" s="206"/>
-      <c r="Y4" s="207"/>
-      <c r="Z4" s="205" t="s">
+      <c r="W4" s="220"/>
+      <c r="X4" s="220"/>
+      <c r="Y4" s="221"/>
+      <c r="Z4" s="219" t="s">
         <v>105</v>
       </c>
-      <c r="AA4" s="206"/>
-      <c r="AB4" s="206"/>
-      <c r="AC4" s="207"/>
-      <c r="AD4" s="205" t="s">
+      <c r="AA4" s="220"/>
+      <c r="AB4" s="220"/>
+      <c r="AC4" s="221"/>
+      <c r="AD4" s="219" t="s">
         <v>106</v>
       </c>
-      <c r="AE4" s="206"/>
-      <c r="AF4" s="206"/>
-      <c r="AG4" s="207"/>
-      <c r="AH4" s="205" t="s">
+      <c r="AE4" s="220"/>
+      <c r="AF4" s="220"/>
+      <c r="AG4" s="221"/>
+      <c r="AH4" s="219" t="s">
         <v>107</v>
       </c>
-      <c r="AI4" s="206"/>
-      <c r="AJ4" s="206"/>
-      <c r="AK4" s="207"/>
-      <c r="AL4" s="205" t="s">
+      <c r="AI4" s="220"/>
+      <c r="AJ4" s="220"/>
+      <c r="AK4" s="221"/>
+      <c r="AL4" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="AM4" s="206"/>
-      <c r="AN4" s="206"/>
-      <c r="AO4" s="207"/>
-    </row>
-    <row r="5" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AM4" s="220"/>
+      <c r="AN4" s="220"/>
+      <c r="AO4" s="221"/>
+    </row>
+    <row r="5" spans="1:59" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="126" t="s">
         <v>114</v>
       </c>
@@ -3794,7 +3806,7 @@
       <c r="AN5" s="128"/>
       <c r="AO5" s="129"/>
     </row>
-    <row r="6" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="125" t="s">
         <v>25</v>
       </c>
@@ -3839,7 +3851,7 @@
       <c r="AN6" s="34"/>
       <c r="AO6" s="39"/>
     </row>
-    <row r="7" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="71" t="s">
         <v>26</v>
       </c>
@@ -3884,7 +3896,7 @@
       <c r="AN7" s="22"/>
       <c r="AO7" s="24"/>
     </row>
-    <row r="8" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="71" t="s">
         <v>27</v>
       </c>
@@ -3929,7 +3941,7 @@
       <c r="AN8" s="22"/>
       <c r="AO8" s="24"/>
     </row>
-    <row r="9" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="72" t="s">
         <v>28</v>
       </c>
@@ -3974,7 +3986,7 @@
       <c r="AN9" s="25"/>
       <c r="AO9" s="26"/>
     </row>
-    <row r="10" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="73" t="s">
         <v>29</v>
       </c>
@@ -4019,7 +4031,7 @@
       <c r="AN10" s="98"/>
       <c r="AO10" s="113"/>
     </row>
-    <row r="11" spans="1:59" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:59" s="19" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="74" t="s">
         <v>30</v>
       </c>
@@ -4073,7 +4085,7 @@
       <c r="AW11" s="2"/>
       <c r="AX11" s="2"/>
     </row>
-    <row r="12" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="75" t="s">
         <v>116</v>
       </c>
@@ -4118,7 +4130,7 @@
       <c r="AN12" s="25"/>
       <c r="AO12" s="26"/>
     </row>
-    <row r="13" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="75" t="s">
         <v>92</v>
       </c>
@@ -4163,7 +4175,7 @@
       <c r="AN13" s="25"/>
       <c r="AO13" s="26"/>
     </row>
-    <row r="14" spans="1:59" s="19" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:59" s="19" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="74" t="s">
         <v>90</v>
       </c>
@@ -4226,7 +4238,7 @@
       <c r="BF14" s="2"/>
       <c r="BG14" s="2"/>
     </row>
-    <row r="15" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="133" t="s">
         <v>118</v>
       </c>
@@ -4271,7 +4283,7 @@
       <c r="AN15" s="25"/>
       <c r="AO15" s="26"/>
     </row>
-    <row r="16" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:59" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="133" t="s">
         <v>117</v>
       </c>
@@ -4316,7 +4328,7 @@
       <c r="AN16" s="25"/>
       <c r="AO16" s="26"/>
     </row>
-    <row r="17" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="133" t="s">
         <v>121</v>
       </c>
@@ -4361,7 +4373,7 @@
       <c r="AN17" s="22"/>
       <c r="AO17" s="24"/>
     </row>
-    <row r="18" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
         <v>122</v>
       </c>
@@ -4406,7 +4418,7 @@
       <c r="AN18" s="25"/>
       <c r="AO18" s="26"/>
     </row>
-    <row r="19" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="76" t="s">
         <v>31</v>
       </c>
@@ -4451,7 +4463,7 @@
       <c r="AN19" s="98"/>
       <c r="AO19" s="113"/>
     </row>
-    <row r="20" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="77" t="s">
         <v>32</v>
       </c>
@@ -4496,7 +4508,7 @@
       <c r="AN20" s="29"/>
       <c r="AO20" s="39"/>
     </row>
-    <row r="21" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="132" t="s">
         <v>110</v>
       </c>
@@ -4541,7 +4553,7 @@
       <c r="AN21" s="25"/>
       <c r="AO21" s="26"/>
     </row>
-    <row r="22" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="132" t="s">
         <v>111</v>
       </c>
@@ -4586,7 +4598,7 @@
       <c r="AN22" s="25"/>
       <c r="AO22" s="26"/>
     </row>
-    <row r="23" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="132" t="s">
         <v>112</v>
       </c>
@@ -4631,7 +4643,7 @@
       <c r="AN23" s="22"/>
       <c r="AO23" s="24"/>
     </row>
-    <row r="24" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" s="2" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="132" t="s">
         <v>113</v>
       </c>
@@ -4876,8 +4888,8 @@
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
       <c r="Q29" s="21"/>
-      <c r="R29" s="23"/>
-      <c r="S29" s="22"/>
+      <c r="R29" s="264"/>
+      <c r="S29" s="21"/>
       <c r="T29" s="23"/>
       <c r="U29" s="24"/>
       <c r="V29" s="23"/>
@@ -5399,11 +5411,11 @@
       <c r="AH40" s="101"/>
       <c r="AI40" s="102"/>
       <c r="AJ40" s="102"/>
-      <c r="AK40" s="102"/>
-      <c r="AL40" s="101"/>
-      <c r="AM40" s="102"/>
-      <c r="AN40" s="102"/>
-      <c r="AO40" s="102"/>
+      <c r="AK40" s="197"/>
+      <c r="AL40" s="100"/>
+      <c r="AM40" s="98"/>
+      <c r="AN40" s="98"/>
+      <c r="AO40" s="113"/>
     </row>
     <row r="41" spans="1:50" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="86" t="s">
@@ -5673,238 +5685,238 @@
   <dimension ref="A1:BH80"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.7109375" customWidth="1"/>
+    <col min="1" max="1" width="48.85546875" customWidth="1"/>
     <col min="2" max="2" width="7.5703125" hidden="1" customWidth="1"/>
     <col min="3" max="42" width="2.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="217" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="203"/>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="203"/>
-      <c r="Y1" s="203"/>
-      <c r="Z1" s="203"/>
-      <c r="AA1" s="203"/>
-      <c r="AB1" s="203"/>
-      <c r="AC1" s="203"/>
-      <c r="AD1" s="203"/>
-      <c r="AE1" s="203"/>
-      <c r="AF1" s="203"/>
-      <c r="AG1" s="203"/>
-      <c r="AH1" s="203"/>
-      <c r="AI1" s="203"/>
-      <c r="AJ1" s="203"/>
-      <c r="AK1" s="203"/>
-      <c r="AL1" s="203"/>
-      <c r="AM1" s="203"/>
-      <c r="AN1" s="203"/>
-      <c r="AO1" s="203"/>
-      <c r="AP1" s="203"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="217"/>
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="217"/>
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="217"/>
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="217"/>
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="217"/>
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="217"/>
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="217"/>
+      <c r="AP1" s="217"/>
     </row>
     <row r="2" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="173" t="s">
         <v>109</v>
       </c>
       <c r="B2" s="14"/>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
-      <c r="I2" s="204"/>
-      <c r="J2" s="204"/>
-      <c r="K2" s="204"/>
-      <c r="L2" s="204"/>
-      <c r="M2" s="204"/>
-      <c r="N2" s="204"/>
-      <c r="O2" s="204"/>
-      <c r="P2" s="204"/>
-      <c r="Q2" s="204"/>
-      <c r="R2" s="204"/>
-      <c r="S2" s="204"/>
-      <c r="T2" s="204"/>
-      <c r="U2" s="204"/>
-      <c r="V2" s="204"/>
-      <c r="W2" s="204"/>
-      <c r="X2" s="204"/>
-      <c r="Y2" s="204"/>
-      <c r="Z2" s="204"/>
-      <c r="AA2" s="204"/>
-      <c r="AB2" s="204"/>
-      <c r="AC2" s="204"/>
-      <c r="AD2" s="204"/>
-      <c r="AE2" s="204"/>
-      <c r="AF2" s="204"/>
-      <c r="AG2" s="204"/>
-      <c r="AH2" s="204"/>
-      <c r="AI2" s="204"/>
-      <c r="AJ2" s="204"/>
-      <c r="AK2" s="204"/>
-      <c r="AL2" s="204"/>
-      <c r="AM2" s="204"/>
-      <c r="AN2" s="204"/>
-      <c r="AO2" s="204"/>
-      <c r="AP2" s="204"/>
+      <c r="C2" s="218"/>
+      <c r="D2" s="218"/>
+      <c r="E2" s="218"/>
+      <c r="F2" s="218"/>
+      <c r="G2" s="218"/>
+      <c r="H2" s="218"/>
+      <c r="I2" s="218"/>
+      <c r="J2" s="218"/>
+      <c r="K2" s="218"/>
+      <c r="L2" s="218"/>
+      <c r="M2" s="218"/>
+      <c r="N2" s="218"/>
+      <c r="O2" s="218"/>
+      <c r="P2" s="218"/>
+      <c r="Q2" s="218"/>
+      <c r="R2" s="218"/>
+      <c r="S2" s="218"/>
+      <c r="T2" s="218"/>
+      <c r="U2" s="218"/>
+      <c r="V2" s="218"/>
+      <c r="W2" s="218"/>
+      <c r="X2" s="218"/>
+      <c r="Y2" s="218"/>
+      <c r="Z2" s="218"/>
+      <c r="AA2" s="218"/>
+      <c r="AB2" s="218"/>
+      <c r="AC2" s="218"/>
+      <c r="AD2" s="218"/>
+      <c r="AE2" s="218"/>
+      <c r="AF2" s="218"/>
+      <c r="AG2" s="218"/>
+      <c r="AH2" s="218"/>
+      <c r="AI2" s="218"/>
+      <c r="AJ2" s="218"/>
+      <c r="AK2" s="218"/>
+      <c r="AL2" s="218"/>
+      <c r="AM2" s="218"/>
+      <c r="AN2" s="218"/>
+      <c r="AO2" s="218"/>
+      <c r="AP2" s="218"/>
     </row>
     <row r="3" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="174" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="15"/>
-      <c r="C3" s="202" t="s">
+      <c r="C3" s="212" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="202"/>
-      <c r="E3" s="202"/>
-      <c r="F3" s="202"/>
-      <c r="G3" s="202" t="s">
+      <c r="D3" s="212"/>
+      <c r="E3" s="212"/>
+      <c r="F3" s="212"/>
+      <c r="G3" s="212" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="202"/>
-      <c r="I3" s="202"/>
-      <c r="J3" s="202"/>
-      <c r="K3" s="202" t="s">
+      <c r="H3" s="212"/>
+      <c r="I3" s="212"/>
+      <c r="J3" s="212"/>
+      <c r="K3" s="212" t="s">
         <v>157</v>
       </c>
-      <c r="L3" s="202"/>
-      <c r="M3" s="202"/>
-      <c r="N3" s="202"/>
-      <c r="O3" s="202" t="s">
+      <c r="L3" s="212"/>
+      <c r="M3" s="212"/>
+      <c r="N3" s="212"/>
+      <c r="O3" s="212" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="202"/>
-      <c r="Q3" s="202"/>
-      <c r="R3" s="202"/>
-      <c r="S3" s="202" t="s">
+      <c r="P3" s="212"/>
+      <c r="Q3" s="212"/>
+      <c r="R3" s="212"/>
+      <c r="S3" s="212" t="s">
         <v>94</v>
       </c>
-      <c r="T3" s="202"/>
-      <c r="U3" s="202"/>
-      <c r="V3" s="202"/>
-      <c r="W3" s="202" t="s">
+      <c r="T3" s="212"/>
+      <c r="U3" s="212"/>
+      <c r="V3" s="212"/>
+      <c r="W3" s="212" t="s">
         <v>95</v>
       </c>
-      <c r="X3" s="202"/>
-      <c r="Y3" s="202"/>
-      <c r="Z3" s="202"/>
-      <c r="AA3" s="202" t="s">
+      <c r="X3" s="212"/>
+      <c r="Y3" s="212"/>
+      <c r="Z3" s="212"/>
+      <c r="AA3" s="212" t="s">
         <v>157</v>
       </c>
-      <c r="AB3" s="202"/>
-      <c r="AC3" s="202"/>
-      <c r="AD3" s="202"/>
-      <c r="AE3" s="202" t="s">
+      <c r="AB3" s="212"/>
+      <c r="AC3" s="212"/>
+      <c r="AD3" s="212"/>
+      <c r="AE3" s="212" t="s">
         <v>97</v>
       </c>
-      <c r="AF3" s="202"/>
-      <c r="AG3" s="202"/>
-      <c r="AH3" s="202"/>
-      <c r="AI3" s="202" t="s">
+      <c r="AF3" s="212"/>
+      <c r="AG3" s="212"/>
+      <c r="AH3" s="212"/>
+      <c r="AI3" s="212" t="s">
         <v>98</v>
       </c>
-      <c r="AJ3" s="202"/>
-      <c r="AK3" s="202"/>
-      <c r="AL3" s="202"/>
-      <c r="AM3" s="202" t="s">
+      <c r="AJ3" s="212"/>
+      <c r="AK3" s="212"/>
+      <c r="AL3" s="212"/>
+      <c r="AM3" s="212" t="s">
         <v>94</v>
       </c>
-      <c r="AN3" s="202"/>
-      <c r="AO3" s="202"/>
-      <c r="AP3" s="202"/>
+      <c r="AN3" s="212"/>
+      <c r="AO3" s="212"/>
+      <c r="AP3" s="212"/>
     </row>
     <row r="4" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="175" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B4" s="20"/>
-      <c r="C4" s="196" t="s">
+      <c r="C4" s="213" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="198"/>
-      <c r="G4" s="196" t="s">
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="215"/>
+      <c r="G4" s="213" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="197"/>
-      <c r="I4" s="197"/>
-      <c r="J4" s="198"/>
-      <c r="K4" s="196" t="s">
+      <c r="H4" s="214"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="215"/>
+      <c r="K4" s="213" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="197"/>
-      <c r="M4" s="197"/>
-      <c r="N4" s="198"/>
-      <c r="O4" s="196" t="s">
+      <c r="L4" s="214"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="215"/>
+      <c r="O4" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="P4" s="197"/>
-      <c r="Q4" s="197"/>
-      <c r="R4" s="198"/>
-      <c r="S4" s="196" t="s">
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="215"/>
+      <c r="S4" s="213" t="s">
         <v>103</v>
       </c>
-      <c r="T4" s="197"/>
-      <c r="U4" s="197"/>
-      <c r="V4" s="198"/>
-      <c r="W4" s="196" t="s">
+      <c r="T4" s="214"/>
+      <c r="U4" s="214"/>
+      <c r="V4" s="215"/>
+      <c r="W4" s="213" t="s">
         <v>104</v>
       </c>
-      <c r="X4" s="197"/>
-      <c r="Y4" s="197"/>
-      <c r="Z4" s="198"/>
-      <c r="AA4" s="196" t="s">
+      <c r="X4" s="214"/>
+      <c r="Y4" s="214"/>
+      <c r="Z4" s="215"/>
+      <c r="AA4" s="213" t="s">
         <v>105</v>
       </c>
-      <c r="AB4" s="197"/>
-      <c r="AC4" s="197"/>
-      <c r="AD4" s="198"/>
-      <c r="AE4" s="196" t="s">
+      <c r="AB4" s="214"/>
+      <c r="AC4" s="214"/>
+      <c r="AD4" s="215"/>
+      <c r="AE4" s="213" t="s">
         <v>106</v>
       </c>
-      <c r="AF4" s="197"/>
-      <c r="AG4" s="197"/>
-      <c r="AH4" s="198"/>
-      <c r="AI4" s="196" t="s">
+      <c r="AF4" s="214"/>
+      <c r="AG4" s="214"/>
+      <c r="AH4" s="215"/>
+      <c r="AI4" s="213" t="s">
         <v>107</v>
       </c>
-      <c r="AJ4" s="197"/>
-      <c r="AK4" s="197"/>
-      <c r="AL4" s="198"/>
-      <c r="AM4" s="196" t="s">
+      <c r="AJ4" s="214"/>
+      <c r="AK4" s="214"/>
+      <c r="AL4" s="215"/>
+      <c r="AM4" s="213" t="s">
         <v>108</v>
       </c>
-      <c r="AN4" s="197"/>
-      <c r="AO4" s="197"/>
-      <c r="AP4" s="198"/>
+      <c r="AN4" s="214"/>
+      <c r="AO4" s="214"/>
+      <c r="AP4" s="215"/>
     </row>
     <row r="5" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="176" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B5" s="162" t="s">
         <v>141</v>
@@ -5999,7 +6011,7 @@
       <c r="AP6" s="39"/>
     </row>
     <row r="7" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="199" t="s">
+      <c r="A7" s="210" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="141" t="s">
@@ -6047,7 +6059,7 @@
       <c r="AP7" s="24"/>
     </row>
     <row r="8" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="200"/>
+      <c r="A8" s="216"/>
       <c r="B8" s="142" t="s">
         <v>133</v>
       </c>
@@ -6093,7 +6105,7 @@
       <c r="AP8" s="24"/>
     </row>
     <row r="9" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="199" t="s">
+      <c r="A9" s="210" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="141" t="s">
@@ -6143,7 +6155,7 @@
       <c r="AP9" s="24"/>
     </row>
     <row r="10" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="200"/>
+      <c r="A10" s="216"/>
       <c r="B10" s="142" t="s">
         <v>133</v>
       </c>
@@ -6188,15 +6200,15 @@
       <c r="AO10" s="22"/>
       <c r="AP10" s="24"/>
     </row>
-    <row r="11" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="199" t="s">
+    <row r="11" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="210" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="141" t="s">
         <v>132</v>
       </c>
       <c r="C11" s="33"/>
-      <c r="D11" s="148" t="s">
+      <c r="D11" s="183" t="s">
         <v>139</v>
       </c>
       <c r="F11" s="32"/>
@@ -6238,12 +6250,12 @@
       <c r="AP11" s="32"/>
     </row>
     <row r="12" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="201"/>
+      <c r="A12" s="211"/>
       <c r="B12" s="142" t="s">
         <v>133</v>
       </c>
       <c r="C12" s="23"/>
-      <c r="D12" s="22"/>
+      <c r="D12" s="139"/>
       <c r="E12" s="22"/>
       <c r="F12" s="24"/>
       <c r="G12" s="27"/>
@@ -6285,7 +6297,7 @@
     </row>
     <row r="13" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="178" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="164" t="s">
         <v>147</v>
@@ -6332,7 +6344,7 @@
       <c r="AP13" s="113"/>
     </row>
     <row r="14" spans="1:51" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="192" t="s">
+      <c r="A14" s="206" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="141" t="s">
@@ -6389,7 +6401,7 @@
       <c r="AY14" s="2"/>
     </row>
     <row r="15" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="193"/>
+      <c r="A15" s="207"/>
       <c r="B15" s="142" t="s">
         <v>133</v>
       </c>
@@ -6435,7 +6447,7 @@
       <c r="AP15" s="30"/>
     </row>
     <row r="16" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="192" t="s">
+      <c r="A16" s="206" t="s">
         <v>116</v>
       </c>
       <c r="B16" s="141" t="s">
@@ -6483,7 +6495,7 @@
       <c r="AP16" s="137"/>
     </row>
     <row r="17" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="193"/>
+      <c r="A17" s="207"/>
       <c r="B17" s="142" t="s">
         <v>133</v>
       </c>
@@ -6529,7 +6541,7 @@
       <c r="AP17" s="26"/>
     </row>
     <row r="18" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="192" t="s">
+      <c r="A18" s="206" t="s">
         <v>92</v>
       </c>
       <c r="B18" s="141" t="s">
@@ -6577,7 +6589,7 @@
       <c r="AP18" s="26"/>
     </row>
     <row r="19" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="193"/>
+      <c r="A19" s="207"/>
       <c r="B19" s="142" t="s">
         <v>133</v>
       </c>
@@ -6623,7 +6635,7 @@
       <c r="AP19" s="26"/>
     </row>
     <row r="20" spans="1:60" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="192" t="s">
+      <c r="A20" s="206" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="141" t="s">
@@ -6689,7 +6701,7 @@
       <c r="BH20" s="2"/>
     </row>
     <row r="21" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="193"/>
+      <c r="A21" s="207"/>
       <c r="B21" s="142" t="s">
         <v>133</v>
       </c>
@@ -6735,7 +6747,7 @@
       <c r="AP21" s="24"/>
     </row>
     <row r="22" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="192" t="s">
+      <c r="A22" s="206" t="s">
         <v>118</v>
       </c>
       <c r="B22" s="141" t="s">
@@ -6783,7 +6795,7 @@
       <c r="AP22" s="32"/>
     </row>
     <row r="23" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="193"/>
+      <c r="A23" s="207"/>
       <c r="B23" s="142" t="s">
         <v>133</v>
       </c>
@@ -6829,7 +6841,7 @@
       <c r="AP23" s="26"/>
     </row>
     <row r="24" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="192" t="s">
+      <c r="A24" s="206" t="s">
         <v>152</v>
       </c>
       <c r="B24" s="141" t="s">
@@ -6879,7 +6891,7 @@
       <c r="AP24" s="26"/>
     </row>
     <row r="25" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="193"/>
+      <c r="A25" s="207"/>
       <c r="B25" s="142" t="s">
         <v>133</v>
       </c>
@@ -6925,7 +6937,7 @@
       <c r="AP25" s="26"/>
     </row>
     <row r="26" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="192" t="s">
+      <c r="A26" s="206" t="s">
         <v>121</v>
       </c>
       <c r="B26" s="141" t="s">
@@ -6975,7 +6987,7 @@
       <c r="AP26" s="32"/>
     </row>
     <row r="27" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="193"/>
+      <c r="A27" s="207"/>
       <c r="B27" s="142" t="s">
         <v>133</v>
       </c>
@@ -7021,7 +7033,7 @@
       <c r="AP27" s="24"/>
     </row>
     <row r="28" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="192" t="s">
+      <c r="A28" s="206" t="s">
         <v>122</v>
       </c>
       <c r="B28" s="141" t="s">
@@ -7069,7 +7081,7 @@
       <c r="AP28" s="32"/>
     </row>
     <row r="29" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="193"/>
+      <c r="A29" s="207"/>
       <c r="B29" s="142" t="s">
         <v>133</v>
       </c>
@@ -7116,7 +7128,7 @@
     </row>
     <row r="30" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="179" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B30" s="165" t="s">
         <v>144</v>
@@ -7163,7 +7175,7 @@
       <c r="AP30" s="113"/>
     </row>
     <row r="31" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="194" t="s">
+      <c r="A31" s="208" t="s">
         <v>153</v>
       </c>
       <c r="B31" s="141" t="s">
@@ -7211,7 +7223,7 @@
       <c r="AP31" s="39"/>
     </row>
     <row r="32" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="191"/>
+      <c r="A32" s="202"/>
       <c r="B32" s="142" t="s">
         <v>133</v>
       </c>
@@ -7257,7 +7269,7 @@
       <c r="AP32" s="137"/>
     </row>
     <row r="33" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="190" t="s">
+      <c r="A33" s="201" t="s">
         <v>110</v>
       </c>
       <c r="B33" s="141" t="s">
@@ -7307,7 +7319,7 @@
       <c r="AP33" s="26"/>
     </row>
     <row r="34" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="191"/>
+      <c r="A34" s="202"/>
       <c r="B34" s="142" t="s">
         <v>133</v>
       </c>
@@ -7353,7 +7365,7 @@
       <c r="AP34" s="26"/>
     </row>
     <row r="35" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="190" t="s">
+      <c r="A35" s="201" t="s">
         <v>151</v>
       </c>
       <c r="B35" s="141" t="s">
@@ -7403,7 +7415,7 @@
       <c r="AP35" s="26"/>
     </row>
     <row r="36" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="195"/>
+      <c r="A36" s="209"/>
       <c r="B36" s="142" t="s">
         <v>133</v>
       </c>
@@ -7449,7 +7461,7 @@
       <c r="AP36" s="32"/>
     </row>
     <row r="37" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="190" t="s">
+      <c r="A37" s="201" t="s">
         <v>154</v>
       </c>
       <c r="B37" s="141" t="s">
@@ -7499,7 +7511,7 @@
       <c r="AP37" s="24"/>
     </row>
     <row r="38" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="191"/>
+      <c r="A38" s="202"/>
       <c r="B38" s="142" t="s">
         <v>133</v>
       </c>
@@ -7545,7 +7557,7 @@
       <c r="AP38" s="32"/>
     </row>
     <row r="39" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="190" t="s">
+      <c r="A39" s="201" t="s">
         <v>113</v>
       </c>
       <c r="B39" s="141" t="s">
@@ -7595,7 +7607,7 @@
       <c r="AP39" s="32"/>
     </row>
     <row r="40" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="191"/>
+      <c r="A40" s="202"/>
       <c r="B40" s="142" t="s">
         <v>133</v>
       </c>
@@ -7689,7 +7701,7 @@
       <c r="AP41" s="113"/>
     </row>
     <row r="42" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="187" t="s">
+      <c r="A42" s="203" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="141" t="s">
@@ -7737,7 +7749,7 @@
       <c r="AP42" s="30"/>
     </row>
     <row r="43" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="188"/>
+      <c r="A43" s="204"/>
       <c r="B43" s="142" t="s">
         <v>133</v>
       </c>
@@ -7783,7 +7795,7 @@
       <c r="AP43" s="30"/>
     </row>
     <row r="44" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="187" t="s">
+      <c r="A44" s="203" t="s">
         <v>115</v>
       </c>
       <c r="B44" s="141" t="s">
@@ -7831,7 +7843,7 @@
       <c r="AP44" s="24"/>
     </row>
     <row r="45" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="188"/>
+      <c r="A45" s="204"/>
       <c r="B45" s="142" t="s">
         <v>133</v>
       </c>
@@ -7877,7 +7889,7 @@
       <c r="AP45" s="24"/>
     </row>
     <row r="46" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="187" t="s">
+      <c r="A46" s="203" t="s">
         <v>123</v>
       </c>
       <c r="B46" s="141" t="s">
@@ -7925,7 +7937,7 @@
       <c r="AP46" s="24"/>
     </row>
     <row r="47" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="188"/>
+      <c r="A47" s="204"/>
       <c r="B47" s="142" t="s">
         <v>133</v>
       </c>
@@ -7971,7 +7983,7 @@
       <c r="AP47" s="24"/>
     </row>
     <row r="48" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="187" t="s">
+      <c r="A48" s="203" t="s">
         <v>124</v>
       </c>
       <c r="B48" s="141" t="s">
@@ -8019,7 +8031,7 @@
       <c r="AP48" s="24"/>
     </row>
     <row r="49" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="188"/>
+      <c r="A49" s="204"/>
       <c r="B49" s="142" t="s">
         <v>133</v>
       </c>
@@ -8065,7 +8077,7 @@
       <c r="AP49" s="32"/>
     </row>
     <row r="50" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="187" t="s">
+      <c r="A50" s="203" t="s">
         <v>119</v>
       </c>
       <c r="B50" s="141" t="s">
@@ -8113,7 +8125,7 @@
       <c r="AP50" s="26"/>
     </row>
     <row r="51" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="188"/>
+      <c r="A51" s="204"/>
       <c r="B51" s="142" t="s">
         <v>133</v>
       </c>
@@ -8159,7 +8171,7 @@
       <c r="AP51" s="32"/>
     </row>
     <row r="52" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="187" t="s">
+      <c r="A52" s="203" t="s">
         <v>125</v>
       </c>
       <c r="B52" s="141" t="s">
@@ -8207,7 +8219,7 @@
       <c r="AP52" s="24"/>
     </row>
     <row r="53" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="188"/>
+      <c r="A53" s="204"/>
       <c r="B53" s="142" t="s">
         <v>133</v>
       </c>
@@ -8253,7 +8265,7 @@
       <c r="AP53" s="24"/>
     </row>
     <row r="54" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="187" t="s">
+      <c r="A54" s="203" t="s">
         <v>150</v>
       </c>
       <c r="B54" s="141" t="s">
@@ -8301,7 +8313,7 @@
       <c r="AP54" s="24"/>
     </row>
     <row r="55" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="188"/>
+      <c r="A55" s="204"/>
       <c r="B55" s="142" t="s">
         <v>133</v>
       </c>
@@ -8347,7 +8359,7 @@
       <c r="AP55" s="32"/>
     </row>
     <row r="56" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="187" t="s">
+      <c r="A56" s="203" t="s">
         <v>129</v>
       </c>
       <c r="B56" s="141" t="s">
@@ -8395,7 +8407,7 @@
       <c r="AP56" s="32"/>
     </row>
     <row r="57" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="188"/>
+      <c r="A57" s="204"/>
       <c r="B57" s="142" t="s">
         <v>133</v>
       </c>
@@ -8441,7 +8453,7 @@
       <c r="AP57" s="32"/>
     </row>
     <row r="58" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="187" t="s">
+      <c r="A58" s="203" t="s">
         <v>127</v>
       </c>
       <c r="B58" s="141" t="s">
@@ -8489,7 +8501,7 @@
       <c r="AP58" s="26"/>
     </row>
     <row r="59" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="188"/>
+      <c r="A59" s="204"/>
       <c r="B59" s="142" t="s">
         <v>133</v>
       </c>
@@ -8535,7 +8547,7 @@
       <c r="AP59" s="32"/>
     </row>
     <row r="60" spans="1:51" s="40" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="187" t="s">
+      <c r="A60" s="203" t="s">
         <v>128</v>
       </c>
       <c r="B60" s="141" t="s">
@@ -8592,7 +8604,7 @@
       <c r="AY60" s="2"/>
     </row>
     <row r="61" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="189"/>
+      <c r="A61" s="205"/>
       <c r="B61" s="142" t="s">
         <v>133</v>
       </c>
@@ -8639,7 +8651,7 @@
     </row>
     <row r="62" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="181" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B62" s="167" t="s">
         <v>146</v>
@@ -8686,7 +8698,7 @@
       <c r="AP62" s="113"/>
     </row>
     <row r="63" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="184" t="s">
+      <c r="A63" s="198" t="s">
         <v>155</v>
       </c>
       <c r="B63" s="141" t="s">
@@ -8734,7 +8746,7 @@
       <c r="AP63" s="30"/>
     </row>
     <row r="64" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="185"/>
+      <c r="A64" s="199"/>
       <c r="B64" s="142" t="s">
         <v>133</v>
       </c>
@@ -8780,7 +8792,7 @@
       <c r="AP64" s="30"/>
     </row>
     <row r="65" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="184" t="s">
+      <c r="A65" s="198" t="s">
         <v>156</v>
       </c>
       <c r="B65" s="141" t="s">
@@ -8828,7 +8840,7 @@
       <c r="AP65" s="24"/>
     </row>
     <row r="66" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="185"/>
+      <c r="A66" s="199"/>
       <c r="B66" s="142" t="s">
         <v>133</v>
       </c>
@@ -8874,7 +8886,7 @@
       <c r="AP66" s="32"/>
     </row>
     <row r="67" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="184" t="s">
+      <c r="A67" s="198" t="s">
         <v>120</v>
       </c>
       <c r="B67" s="141" t="s">
@@ -8922,7 +8934,7 @@
       <c r="AP67" s="24"/>
     </row>
     <row r="68" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="186"/>
+      <c r="A68" s="200"/>
       <c r="B68" s="142" t="s">
         <v>133</v>
       </c>
@@ -8969,7 +8981,7 @@
     </row>
     <row r="69" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A69" s="182" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B69" s="168" t="s">
         <v>143</v>
@@ -9016,7 +9028,7 @@
       <c r="AP69" s="102"/>
     </row>
     <row r="70" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="260" t="s">
+      <c r="A70" s="194" t="s">
         <v>130</v>
       </c>
       <c r="B70" s="141" t="s">
@@ -9064,7 +9076,7 @@
       <c r="AP70" s="91"/>
     </row>
     <row r="71" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="261"/>
+      <c r="A71" s="195"/>
       <c r="B71" s="142" t="s">
         <v>133</v>
       </c>
@@ -9110,7 +9122,7 @@
       <c r="AP71" s="91"/>
     </row>
     <row r="72" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="260" t="s">
+      <c r="A72" s="194" t="s">
         <v>131</v>
       </c>
       <c r="B72" s="141" t="s">
@@ -9158,7 +9170,7 @@
       <c r="AP72" s="18"/>
     </row>
     <row r="73" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="261"/>
+      <c r="A73" s="195"/>
       <c r="B73" s="142" t="s">
         <v>133</v>
       </c>
@@ -9204,7 +9216,7 @@
       <c r="AP73" s="18"/>
     </row>
     <row r="74" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="260" t="s">
+      <c r="A74" s="194" t="s">
         <v>135</v>
       </c>
       <c r="B74" s="141" t="s">
@@ -9254,7 +9266,7 @@
       <c r="AP74" s="18"/>
     </row>
     <row r="75" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="261"/>
+      <c r="A75" s="195"/>
       <c r="B75" s="142" t="s">
         <v>133</v>
       </c>
@@ -9300,7 +9312,7 @@
       <c r="AP75" s="18"/>
     </row>
     <row r="76" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="260" t="s">
+      <c r="A76" s="194" t="s">
         <v>136</v>
       </c>
       <c r="B76" s="141" t="s">
@@ -9343,7 +9355,7 @@
       <c r="AK76" s="155" t="s">
         <v>139</v>
       </c>
-      <c r="AL76" s="256" t="s">
+      <c r="AL76" s="190" t="s">
         <v>139</v>
       </c>
       <c r="AM76" s="23"/>
@@ -9352,7 +9364,7 @@
       <c r="AP76" s="18"/>
     </row>
     <row r="77" spans="1:42" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="261"/>
+      <c r="A77" s="195"/>
       <c r="B77" s="142" t="s">
         <v>133</v>
       </c>
@@ -9398,7 +9410,7 @@
       <c r="AP77" s="145"/>
     </row>
     <row r="78" spans="1:42" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="260" t="s">
+      <c r="A78" s="194" t="s">
         <v>137</v>
       </c>
       <c r="B78" s="141" t="s">
@@ -9439,7 +9451,7 @@
       <c r="AI78" s="27"/>
       <c r="AJ78" s="43"/>
       <c r="AK78" s="25"/>
-      <c r="AL78" s="257" t="s">
+      <c r="AL78" s="191" t="s">
         <v>139</v>
       </c>
       <c r="AM78" s="27"/>
@@ -9448,54 +9460,54 @@
       <c r="AP78" s="44"/>
     </row>
     <row r="79" spans="1:42" ht="17.100000000000001" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="261"/>
+      <c r="A79" s="195"/>
       <c r="B79" s="142" t="s">
         <v>133</v>
       </c>
       <c r="C79" s="109"/>
-      <c r="D79" s="254"/>
+      <c r="D79" s="188"/>
       <c r="E79" s="90"/>
-      <c r="F79" s="255"/>
+      <c r="F79" s="189"/>
       <c r="G79" s="109"/>
-      <c r="H79" s="254"/>
+      <c r="H79" s="188"/>
       <c r="I79" s="90"/>
-      <c r="J79" s="255"/>
+      <c r="J79" s="189"/>
       <c r="K79" s="109"/>
-      <c r="L79" s="254"/>
+      <c r="L79" s="188"/>
       <c r="M79" s="90"/>
-      <c r="N79" s="255"/>
+      <c r="N79" s="189"/>
       <c r="O79" s="109"/>
-      <c r="P79" s="254"/>
+      <c r="P79" s="188"/>
       <c r="Q79" s="90"/>
-      <c r="R79" s="255"/>
+      <c r="R79" s="189"/>
       <c r="S79" s="109"/>
-      <c r="T79" s="254"/>
+      <c r="T79" s="188"/>
       <c r="U79" s="90"/>
-      <c r="V79" s="255"/>
+      <c r="V79" s="189"/>
       <c r="W79" s="90"/>
-      <c r="X79" s="254"/>
+      <c r="X79" s="188"/>
       <c r="Y79" s="90"/>
-      <c r="Z79" s="255"/>
+      <c r="Z79" s="189"/>
       <c r="AA79" s="90"/>
-      <c r="AB79" s="254"/>
+      <c r="AB79" s="188"/>
       <c r="AC79" s="90"/>
-      <c r="AD79" s="255"/>
+      <c r="AD79" s="189"/>
       <c r="AE79" s="109"/>
-      <c r="AF79" s="254"/>
+      <c r="AF79" s="188"/>
       <c r="AG79" s="90"/>
-      <c r="AH79" s="255"/>
+      <c r="AH79" s="189"/>
       <c r="AI79" s="109"/>
-      <c r="AJ79" s="254"/>
+      <c r="AJ79" s="188"/>
       <c r="AK79" s="90"/>
-      <c r="AL79" s="255"/>
+      <c r="AL79" s="189"/>
       <c r="AM79" s="109"/>
-      <c r="AN79" s="254"/>
+      <c r="AN79" s="188"/>
       <c r="AO79" s="90"/>
-      <c r="AP79" s="255"/>
+      <c r="AP79" s="189"/>
     </row>
     <row r="80" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="250" t="s">
-        <v>166</v>
+      <c r="A80" s="184" t="s">
+        <v>167</v>
       </c>
       <c r="B80" s="168" t="s">
         <v>143</v>
@@ -9536,10 +9548,10 @@
       <c r="AJ80" s="97"/>
       <c r="AK80" s="98"/>
       <c r="AL80" s="99"/>
-      <c r="AM80" s="251"/>
-      <c r="AN80" s="252"/>
-      <c r="AO80" s="251"/>
-      <c r="AP80" s="253"/>
+      <c r="AM80" s="185"/>
+      <c r="AN80" s="186"/>
+      <c r="AO80" s="185"/>
+      <c r="AP80" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -9581,6 +9593,8 @@
     <mergeCell ref="A31:A32"/>
     <mergeCell ref="A33:A34"/>
     <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A65:A66"/>
+    <mergeCell ref="A67:A68"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A39:A40"/>
     <mergeCell ref="A42:A43"/>
@@ -9593,8 +9607,6 @@
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A58:A59"/>
     <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A65:A66"/>
-    <mergeCell ref="A67:A68"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
@@ -9619,232 +9631,232 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="217" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="203"/>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="203"/>
-      <c r="Y1" s="203"/>
-      <c r="Z1" s="203"/>
-      <c r="AA1" s="203"/>
-      <c r="AB1" s="203"/>
-      <c r="AC1" s="203"/>
-      <c r="AD1" s="203"/>
-      <c r="AE1" s="203"/>
-      <c r="AF1" s="203"/>
-      <c r="AG1" s="203"/>
-      <c r="AH1" s="203"/>
-      <c r="AI1" s="203"/>
-      <c r="AJ1" s="203"/>
-      <c r="AK1" s="203"/>
-      <c r="AL1" s="203"/>
-      <c r="AM1" s="203"/>
-      <c r="AN1" s="203"/>
-      <c r="AO1" s="203"/>
-      <c r="AP1" s="203"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="217"/>
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="217"/>
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="217"/>
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="217"/>
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="217"/>
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="217"/>
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="217"/>
+      <c r="AP1" s="217"/>
     </row>
     <row r="2" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>109</v>
       </c>
       <c r="B2" s="14"/>
-      <c r="C2" s="227" t="s">
+      <c r="C2" s="241" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="228"/>
-      <c r="E2" s="227" t="s">
+      <c r="D2" s="242"/>
+      <c r="E2" s="241" t="s">
         <v>149</v>
       </c>
-      <c r="F2" s="229"/>
-      <c r="G2" s="229"/>
-      <c r="H2" s="229"/>
-      <c r="I2" s="229"/>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="229"/>
-      <c r="S2" s="229"/>
-      <c r="T2" s="229"/>
-      <c r="U2" s="229"/>
-      <c r="V2" s="229"/>
-      <c r="W2" s="229"/>
-      <c r="X2" s="229"/>
-      <c r="Y2" s="229"/>
-      <c r="Z2" s="229"/>
-      <c r="AA2" s="229"/>
-      <c r="AB2" s="229"/>
-      <c r="AC2" s="229"/>
-      <c r="AD2" s="229"/>
-      <c r="AE2" s="229"/>
-      <c r="AF2" s="229"/>
-      <c r="AG2" s="229"/>
-      <c r="AH2" s="229"/>
-      <c r="AI2" s="229"/>
-      <c r="AJ2" s="229"/>
-      <c r="AK2" s="229"/>
-      <c r="AL2" s="229"/>
-      <c r="AM2" s="229"/>
-      <c r="AN2" s="229"/>
-      <c r="AO2" s="229"/>
-      <c r="AP2" s="228"/>
+      <c r="F2" s="243"/>
+      <c r="G2" s="243"/>
+      <c r="H2" s="243"/>
+      <c r="I2" s="243"/>
+      <c r="J2" s="243"/>
+      <c r="K2" s="243"/>
+      <c r="L2" s="243"/>
+      <c r="M2" s="243"/>
+      <c r="N2" s="243"/>
+      <c r="O2" s="243"/>
+      <c r="P2" s="243"/>
+      <c r="Q2" s="243"/>
+      <c r="R2" s="243"/>
+      <c r="S2" s="243"/>
+      <c r="T2" s="243"/>
+      <c r="U2" s="243"/>
+      <c r="V2" s="243"/>
+      <c r="W2" s="243"/>
+      <c r="X2" s="243"/>
+      <c r="Y2" s="243"/>
+      <c r="Z2" s="243"/>
+      <c r="AA2" s="243"/>
+      <c r="AB2" s="243"/>
+      <c r="AC2" s="243"/>
+      <c r="AD2" s="243"/>
+      <c r="AE2" s="243"/>
+      <c r="AF2" s="243"/>
+      <c r="AG2" s="243"/>
+      <c r="AH2" s="243"/>
+      <c r="AI2" s="243"/>
+      <c r="AJ2" s="243"/>
+      <c r="AK2" s="243"/>
+      <c r="AL2" s="243"/>
+      <c r="AM2" s="243"/>
+      <c r="AN2" s="243"/>
+      <c r="AO2" s="243"/>
+      <c r="AP2" s="242"/>
     </row>
     <row r="3" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>15</v>
       </c>
       <c r="B3" s="15"/>
-      <c r="C3" s="208" t="s">
+      <c r="C3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="D3" s="209"/>
-      <c r="E3" s="209"/>
-      <c r="F3" s="210"/>
-      <c r="G3" s="208" t="s">
+      <c r="D3" s="223"/>
+      <c r="E3" s="223"/>
+      <c r="F3" s="224"/>
+      <c r="G3" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="H3" s="209"/>
-      <c r="I3" s="209"/>
-      <c r="J3" s="210"/>
-      <c r="K3" s="208" t="s">
+      <c r="H3" s="223"/>
+      <c r="I3" s="223"/>
+      <c r="J3" s="224"/>
+      <c r="K3" s="222" t="s">
         <v>96</v>
       </c>
-      <c r="L3" s="209"/>
-      <c r="M3" s="209"/>
-      <c r="N3" s="210"/>
-      <c r="O3" s="208" t="s">
+      <c r="L3" s="223"/>
+      <c r="M3" s="223"/>
+      <c r="N3" s="224"/>
+      <c r="O3" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="P3" s="209"/>
-      <c r="Q3" s="209"/>
-      <c r="R3" s="210"/>
-      <c r="S3" s="208" t="s">
+      <c r="P3" s="223"/>
+      <c r="Q3" s="223"/>
+      <c r="R3" s="224"/>
+      <c r="S3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="T3" s="209"/>
-      <c r="U3" s="209"/>
-      <c r="V3" s="210"/>
-      <c r="W3" s="208" t="s">
+      <c r="T3" s="223"/>
+      <c r="U3" s="223"/>
+      <c r="V3" s="224"/>
+      <c r="W3" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="X3" s="209"/>
-      <c r="Y3" s="209"/>
-      <c r="Z3" s="210"/>
-      <c r="AA3" s="208" t="s">
+      <c r="X3" s="223"/>
+      <c r="Y3" s="223"/>
+      <c r="Z3" s="224"/>
+      <c r="AA3" s="222" t="s">
         <v>96</v>
       </c>
-      <c r="AB3" s="209"/>
-      <c r="AC3" s="209"/>
-      <c r="AD3" s="210"/>
-      <c r="AE3" s="208" t="s">
+      <c r="AB3" s="223"/>
+      <c r="AC3" s="223"/>
+      <c r="AD3" s="224"/>
+      <c r="AE3" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="AF3" s="209"/>
-      <c r="AG3" s="209"/>
-      <c r="AH3" s="210"/>
-      <c r="AI3" s="208" t="s">
+      <c r="AF3" s="223"/>
+      <c r="AG3" s="223"/>
+      <c r="AH3" s="224"/>
+      <c r="AI3" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="AJ3" s="209"/>
-      <c r="AK3" s="209"/>
-      <c r="AL3" s="210"/>
-      <c r="AM3" s="208" t="s">
+      <c r="AJ3" s="223"/>
+      <c r="AK3" s="223"/>
+      <c r="AL3" s="224"/>
+      <c r="AM3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="AN3" s="209"/>
-      <c r="AO3" s="209"/>
-      <c r="AP3" s="210"/>
+      <c r="AN3" s="223"/>
+      <c r="AO3" s="223"/>
+      <c r="AP3" s="224"/>
     </row>
     <row r="4" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>46139</v>
       </c>
       <c r="B4" s="20"/>
-      <c r="C4" s="205" t="s">
+      <c r="C4" s="219" t="s">
         <v>99</v>
       </c>
-      <c r="D4" s="206"/>
-      <c r="E4" s="206"/>
-      <c r="F4" s="207"/>
-      <c r="G4" s="205" t="s">
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="219" t="s">
         <v>100</v>
       </c>
-      <c r="H4" s="206"/>
-      <c r="I4" s="206"/>
-      <c r="J4" s="207"/>
-      <c r="K4" s="205" t="s">
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="221"/>
+      <c r="K4" s="219" t="s">
         <v>101</v>
       </c>
-      <c r="L4" s="206"/>
-      <c r="M4" s="206"/>
-      <c r="N4" s="207"/>
-      <c r="O4" s="205" t="s">
+      <c r="L4" s="220"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="221"/>
+      <c r="O4" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="206"/>
-      <c r="R4" s="207"/>
-      <c r="S4" s="205" t="s">
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="221"/>
+      <c r="S4" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="T4" s="206"/>
-      <c r="U4" s="206"/>
-      <c r="V4" s="207"/>
-      <c r="W4" s="205" t="s">
+      <c r="T4" s="220"/>
+      <c r="U4" s="220"/>
+      <c r="V4" s="221"/>
+      <c r="W4" s="219" t="s">
         <v>104</v>
       </c>
-      <c r="X4" s="206"/>
-      <c r="Y4" s="206"/>
-      <c r="Z4" s="207"/>
-      <c r="AA4" s="205" t="s">
+      <c r="X4" s="220"/>
+      <c r="Y4" s="220"/>
+      <c r="Z4" s="221"/>
+      <c r="AA4" s="219" t="s">
         <v>105</v>
       </c>
-      <c r="AB4" s="206"/>
-      <c r="AC4" s="206"/>
-      <c r="AD4" s="207"/>
-      <c r="AE4" s="205" t="s">
+      <c r="AB4" s="220"/>
+      <c r="AC4" s="220"/>
+      <c r="AD4" s="221"/>
+      <c r="AE4" s="219" t="s">
         <v>106</v>
       </c>
-      <c r="AF4" s="206"/>
-      <c r="AG4" s="206"/>
-      <c r="AH4" s="207"/>
-      <c r="AI4" s="205" t="s">
+      <c r="AF4" s="220"/>
+      <c r="AG4" s="220"/>
+      <c r="AH4" s="221"/>
+      <c r="AI4" s="219" t="s">
         <v>107</v>
       </c>
-      <c r="AJ4" s="206"/>
-      <c r="AK4" s="206"/>
-      <c r="AL4" s="207"/>
-      <c r="AM4" s="205" t="s">
+      <c r="AJ4" s="220"/>
+      <c r="AK4" s="220"/>
+      <c r="AL4" s="221"/>
+      <c r="AM4" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="AN4" s="206"/>
-      <c r="AO4" s="206"/>
-      <c r="AP4" s="207"/>
+      <c r="AN4" s="220"/>
+      <c r="AO4" s="220"/>
+      <c r="AP4" s="221"/>
     </row>
     <row r="5" spans="1:51" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="126" t="s">
@@ -9943,7 +9955,7 @@
       <c r="AP6" s="39"/>
     </row>
     <row r="7" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="214" t="s">
+      <c r="A7" s="230" t="s">
         <v>26</v>
       </c>
       <c r="B7" s="141" t="s">
@@ -9991,7 +10003,7 @@
       <c r="AP7" s="24"/>
     </row>
     <row r="8" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="215"/>
+      <c r="A8" s="231"/>
       <c r="B8" s="142" t="s">
         <v>133</v>
       </c>
@@ -10037,7 +10049,7 @@
       <c r="AP8" s="24"/>
     </row>
     <row r="9" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="214" t="s">
+      <c r="A9" s="230" t="s">
         <v>27</v>
       </c>
       <c r="B9" s="141" t="s">
@@ -10087,7 +10099,7 @@
       <c r="AP9" s="24"/>
     </row>
     <row r="10" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="215"/>
+      <c r="A10" s="231"/>
       <c r="B10" s="142" t="s">
         <v>133</v>
       </c>
@@ -10135,7 +10147,7 @@
       <c r="AP10" s="24"/>
     </row>
     <row r="11" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="214" t="s">
+      <c r="A11" s="230" t="s">
         <v>28</v>
       </c>
       <c r="B11" s="141" t="s">
@@ -10184,7 +10196,7 @@
       <c r="AP11" s="32"/>
     </row>
     <row r="12" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="222"/>
+      <c r="A12" s="236"/>
       <c r="B12" s="142" t="s">
         <v>133</v>
       </c>
@@ -10280,7 +10292,7 @@
       <c r="AP13" s="113"/>
     </row>
     <row r="14" spans="1:51" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="220" t="s">
+      <c r="A14" s="226" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="141" t="s">
@@ -10337,7 +10349,7 @@
       <c r="AY14" s="2"/>
     </row>
     <row r="15" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="221"/>
+      <c r="A15" s="227"/>
       <c r="B15" s="142" t="s">
         <v>133</v>
       </c>
@@ -10385,7 +10397,7 @@
       <c r="AP15" s="30"/>
     </row>
     <row r="16" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="220" t="s">
+      <c r="A16" s="226" t="s">
         <v>116</v>
       </c>
       <c r="B16" s="141" t="s">
@@ -10433,7 +10445,7 @@
       <c r="AP16" s="137"/>
     </row>
     <row r="17" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="221"/>
+      <c r="A17" s="227"/>
       <c r="B17" s="142" t="s">
         <v>133</v>
       </c>
@@ -10481,7 +10493,7 @@
       <c r="AP17" s="26"/>
     </row>
     <row r="18" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="220" t="s">
+      <c r="A18" s="226" t="s">
         <v>92</v>
       </c>
       <c r="B18" s="141" t="s">
@@ -10529,7 +10541,7 @@
       <c r="AP18" s="26"/>
     </row>
     <row r="19" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="221"/>
+      <c r="A19" s="227"/>
       <c r="B19" s="142" t="s">
         <v>133</v>
       </c>
@@ -10577,7 +10589,7 @@
       <c r="AP19" s="26"/>
     </row>
     <row r="20" spans="1:60" s="19" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="220" t="s">
+      <c r="A20" s="226" t="s">
         <v>90</v>
       </c>
       <c r="B20" s="141" t="s">
@@ -10643,7 +10655,7 @@
       <c r="BH20" s="2"/>
     </row>
     <row r="21" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="221"/>
+      <c r="A21" s="227"/>
       <c r="B21" s="142" t="s">
         <v>133</v>
       </c>
@@ -10691,7 +10703,7 @@
       <c r="AP21" s="24"/>
     </row>
     <row r="22" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="220" t="s">
+      <c r="A22" s="226" t="s">
         <v>118</v>
       </c>
       <c r="B22" s="141" t="s">
@@ -10739,7 +10751,7 @@
       <c r="AP22" s="32"/>
     </row>
     <row r="23" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="221"/>
+      <c r="A23" s="227"/>
       <c r="B23" s="142" t="s">
         <v>133</v>
       </c>
@@ -10785,7 +10797,7 @@
       <c r="AP23" s="26"/>
     </row>
     <row r="24" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="220" t="s">
+      <c r="A24" s="226" t="s">
         <v>117</v>
       </c>
       <c r="B24" s="141" t="s">
@@ -10835,7 +10847,7 @@
       <c r="AP24" s="26"/>
     </row>
     <row r="25" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="221"/>
+      <c r="A25" s="227"/>
       <c r="B25" s="142" t="s">
         <v>133</v>
       </c>
@@ -10881,7 +10893,7 @@
       <c r="AP25" s="26"/>
     </row>
     <row r="26" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="220" t="s">
+      <c r="A26" s="226" t="s">
         <v>121</v>
       </c>
       <c r="B26" s="141" t="s">
@@ -10931,7 +10943,7 @@
       <c r="AP26" s="32"/>
     </row>
     <row r="27" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="221"/>
+      <c r="A27" s="227"/>
       <c r="B27" s="142" t="s">
         <v>133</v>
       </c>
@@ -10977,7 +10989,7 @@
       <c r="AP27" s="24"/>
     </row>
     <row r="28" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="220" t="s">
+      <c r="A28" s="226" t="s">
         <v>122</v>
       </c>
       <c r="B28" s="141" t="s">
@@ -11025,7 +11037,7 @@
       <c r="AP28" s="32"/>
     </row>
     <row r="29" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="221"/>
+      <c r="A29" s="227"/>
       <c r="B29" s="142" t="s">
         <v>133</v>
       </c>
@@ -11119,7 +11131,7 @@
       <c r="AP30" s="113"/>
     </row>
     <row r="31" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="219" t="s">
+      <c r="A31" s="235" t="s">
         <v>32</v>
       </c>
       <c r="B31" s="141" t="s">
@@ -11167,7 +11179,7 @@
       <c r="AP31" s="39"/>
     </row>
     <row r="32" spans="1:60" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="217"/>
+      <c r="A32" s="233"/>
       <c r="B32" s="142" t="s">
         <v>133</v>
       </c>
@@ -11213,7 +11225,7 @@
       <c r="AP32" s="137"/>
     </row>
     <row r="33" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="216" t="s">
+      <c r="A33" s="232" t="s">
         <v>110</v>
       </c>
       <c r="B33" s="141" t="s">
@@ -11263,7 +11275,7 @@
       <c r="AP33" s="26"/>
     </row>
     <row r="34" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="217"/>
+      <c r="A34" s="233"/>
       <c r="B34" s="142" t="s">
         <v>133</v>
       </c>
@@ -11309,7 +11321,7 @@
       <c r="AP34" s="26"/>
     </row>
     <row r="35" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="216" t="s">
+      <c r="A35" s="232" t="s">
         <v>111</v>
       </c>
       <c r="B35" s="141" t="s">
@@ -11359,7 +11371,7 @@
       <c r="AP35" s="26"/>
     </row>
     <row r="36" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="218"/>
+      <c r="A36" s="234"/>
       <c r="B36" s="142" t="s">
         <v>133</v>
       </c>
@@ -11405,7 +11417,7 @@
       <c r="AP36" s="32"/>
     </row>
     <row r="37" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="216" t="s">
+      <c r="A37" s="232" t="s">
         <v>112</v>
       </c>
       <c r="B37" s="141" t="s">
@@ -11455,7 +11467,7 @@
       <c r="AP37" s="24"/>
     </row>
     <row r="38" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="217"/>
+      <c r="A38" s="233"/>
       <c r="B38" s="142" t="s">
         <v>133</v>
       </c>
@@ -11501,7 +11513,7 @@
       <c r="AP38" s="32"/>
     </row>
     <row r="39" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="216" t="s">
+      <c r="A39" s="232" t="s">
         <v>113</v>
       </c>
       <c r="B39" s="141" t="s">
@@ -11551,7 +11563,7 @@
       <c r="AP39" s="32"/>
     </row>
     <row r="40" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="217"/>
+      <c r="A40" s="233"/>
       <c r="B40" s="142" t="s">
         <v>133</v>
       </c>
@@ -11645,7 +11657,7 @@
       <c r="AP41" s="113"/>
     </row>
     <row r="42" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="212" t="s">
+      <c r="A42" s="228" t="s">
         <v>34</v>
       </c>
       <c r="B42" s="141" t="s">
@@ -11693,7 +11705,7 @@
       <c r="AP42" s="30"/>
     </row>
     <row r="43" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="213"/>
+      <c r="A43" s="229"/>
       <c r="B43" s="142" t="s">
         <v>133</v>
       </c>
@@ -11739,7 +11751,7 @@
       <c r="AP43" s="30"/>
     </row>
     <row r="44" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="212" t="s">
+      <c r="A44" s="228" t="s">
         <v>115</v>
       </c>
       <c r="B44" s="141" t="s">
@@ -11787,7 +11799,7 @@
       <c r="AP44" s="24"/>
     </row>
     <row r="45" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="213"/>
+      <c r="A45" s="229"/>
       <c r="B45" s="142" t="s">
         <v>133</v>
       </c>
@@ -11833,7 +11845,7 @@
       <c r="AP45" s="24"/>
     </row>
     <row r="46" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="212" t="s">
+      <c r="A46" s="228" t="s">
         <v>123</v>
       </c>
       <c r="B46" s="141" t="s">
@@ -11881,7 +11893,7 @@
       <c r="AP46" s="24"/>
     </row>
     <row r="47" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="213"/>
+      <c r="A47" s="229"/>
       <c r="B47" s="142" t="s">
         <v>133</v>
       </c>
@@ -11927,7 +11939,7 @@
       <c r="AP47" s="24"/>
     </row>
     <row r="48" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="212" t="s">
+      <c r="A48" s="228" t="s">
         <v>124</v>
       </c>
       <c r="B48" s="141" t="s">
@@ -11975,7 +11987,7 @@
       <c r="AP48" s="24"/>
     </row>
     <row r="49" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="213"/>
+      <c r="A49" s="229"/>
       <c r="B49" s="142" t="s">
         <v>133</v>
       </c>
@@ -12021,7 +12033,7 @@
       <c r="AP49" s="32"/>
     </row>
     <row r="50" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="212" t="s">
+      <c r="A50" s="228" t="s">
         <v>119</v>
       </c>
       <c r="B50" s="141" t="s">
@@ -12069,7 +12081,7 @@
       <c r="AP50" s="26"/>
     </row>
     <row r="51" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="213"/>
+      <c r="A51" s="229"/>
       <c r="B51" s="142" t="s">
         <v>133</v>
       </c>
@@ -12115,7 +12127,7 @@
       <c r="AP51" s="32"/>
     </row>
     <row r="52" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="212" t="s">
+      <c r="A52" s="228" t="s">
         <v>125</v>
       </c>
       <c r="B52" s="141" t="s">
@@ -12163,7 +12175,7 @@
       <c r="AP52" s="24"/>
     </row>
     <row r="53" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="213"/>
+      <c r="A53" s="229"/>
       <c r="B53" s="142" t="s">
         <v>133</v>
       </c>
@@ -12209,7 +12221,7 @@
       <c r="AP53" s="24"/>
     </row>
     <row r="54" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="212" t="s">
+      <c r="A54" s="228" t="s">
         <v>126</v>
       </c>
       <c r="B54" s="141" t="s">
@@ -12257,7 +12269,7 @@
       <c r="AP54" s="24"/>
     </row>
     <row r="55" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="213"/>
+      <c r="A55" s="229"/>
       <c r="B55" s="142" t="s">
         <v>133</v>
       </c>
@@ -12303,7 +12315,7 @@
       <c r="AP55" s="32"/>
     </row>
     <row r="56" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="212" t="s">
+      <c r="A56" s="228" t="s">
         <v>129</v>
       </c>
       <c r="B56" s="141" t="s">
@@ -12351,7 +12363,7 @@
       <c r="AP56" s="32"/>
     </row>
     <row r="57" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="213"/>
+      <c r="A57" s="229"/>
       <c r="B57" s="142" t="s">
         <v>133</v>
       </c>
@@ -12397,7 +12409,7 @@
       <c r="AP57" s="32"/>
     </row>
     <row r="58" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="212" t="s">
+      <c r="A58" s="228" t="s">
         <v>127</v>
       </c>
       <c r="B58" s="141" t="s">
@@ -12445,7 +12457,7 @@
       <c r="AP58" s="26"/>
     </row>
     <row r="59" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="213"/>
+      <c r="A59" s="229"/>
       <c r="B59" s="142" t="s">
         <v>133</v>
       </c>
@@ -12491,7 +12503,7 @@
       <c r="AP59" s="32"/>
     </row>
     <row r="60" spans="1:51" s="40" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="212" t="s">
+      <c r="A60" s="228" t="s">
         <v>128</v>
       </c>
       <c r="B60" s="141" t="s">
@@ -12548,7 +12560,7 @@
       <c r="AY60" s="2"/>
     </row>
     <row r="61" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="226"/>
+      <c r="A61" s="240"/>
       <c r="B61" s="142" t="s">
         <v>133</v>
       </c>
@@ -12642,7 +12654,7 @@
       <c r="AP62" s="113"/>
     </row>
     <row r="63" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="223" t="s">
+      <c r="A63" s="237" t="s">
         <v>45</v>
       </c>
       <c r="B63" s="141" t="s">
@@ -12690,7 +12702,7 @@
       <c r="AP63" s="30"/>
     </row>
     <row r="64" spans="1:51" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="225"/>
+      <c r="A64" s="239"/>
       <c r="B64" s="142" t="s">
         <v>133</v>
       </c>
@@ -12736,7 +12748,7 @@
       <c r="AP64" s="30"/>
     </row>
     <row r="65" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="223" t="s">
+      <c r="A65" s="237" t="s">
         <v>46</v>
       </c>
       <c r="B65" s="141" t="s">
@@ -12784,7 +12796,7 @@
       <c r="AP65" s="24"/>
     </row>
     <row r="66" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="225"/>
+      <c r="A66" s="239"/>
       <c r="B66" s="142" t="s">
         <v>133</v>
       </c>
@@ -12830,7 +12842,7 @@
       <c r="AP66" s="32"/>
     </row>
     <row r="67" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="223" t="s">
+      <c r="A67" s="237" t="s">
         <v>120</v>
       </c>
       <c r="B67" s="141" t="s">
@@ -12878,7 +12890,7 @@
       <c r="AP67" s="24"/>
     </row>
     <row r="68" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="224"/>
+      <c r="A68" s="238"/>
       <c r="B68" s="142" t="s">
         <v>133</v>
       </c>
@@ -12965,14 +12977,14 @@
       <c r="AI69" s="101"/>
       <c r="AJ69" s="102"/>
       <c r="AK69" s="102"/>
-      <c r="AL69" s="102"/>
-      <c r="AM69" s="101"/>
-      <c r="AN69" s="102"/>
-      <c r="AO69" s="102"/>
-      <c r="AP69" s="102"/>
+      <c r="AL69" s="197"/>
+      <c r="AM69" s="100"/>
+      <c r="AN69" s="98"/>
+      <c r="AO69" s="98"/>
+      <c r="AP69" s="113"/>
     </row>
     <row r="70" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="258" t="s">
+      <c r="A70" s="192" t="s">
         <v>130</v>
       </c>
       <c r="B70" s="141" t="s">
@@ -13020,7 +13032,7 @@
       <c r="AP70" s="91"/>
     </row>
     <row r="71" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="259"/>
+      <c r="A71" s="193"/>
       <c r="B71" s="142" t="s">
         <v>133</v>
       </c>
@@ -13066,7 +13078,7 @@
       <c r="AP71" s="91"/>
     </row>
     <row r="72" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="258" t="s">
+      <c r="A72" s="192" t="s">
         <v>131</v>
       </c>
       <c r="B72" s="141" t="s">
@@ -13114,7 +13126,7 @@
       <c r="AP72" s="18"/>
     </row>
     <row r="73" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="259"/>
+      <c r="A73" s="193"/>
       <c r="B73" s="142" t="s">
         <v>133</v>
       </c>
@@ -13160,7 +13172,7 @@
       <c r="AP73" s="18"/>
     </row>
     <row r="74" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="258" t="s">
+      <c r="A74" s="192" t="s">
         <v>135</v>
       </c>
       <c r="B74" s="141" t="s">
@@ -13210,7 +13222,7 @@
       <c r="AP74" s="18"/>
     </row>
     <row r="75" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="259"/>
+      <c r="A75" s="193"/>
       <c r="B75" s="142" t="s">
         <v>133</v>
       </c>
@@ -13256,7 +13268,7 @@
       <c r="AP75" s="18"/>
     </row>
     <row r="76" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="258" t="s">
+      <c r="A76" s="192" t="s">
         <v>136</v>
       </c>
       <c r="B76" s="141" t="s">
@@ -13299,7 +13311,7 @@
       <c r="AK76" s="155" t="s">
         <v>139</v>
       </c>
-      <c r="AL76" s="256" t="s">
+      <c r="AL76" s="190" t="s">
         <v>139</v>
       </c>
       <c r="AM76" s="23"/>
@@ -13308,7 +13320,7 @@
       <c r="AP76" s="18"/>
     </row>
     <row r="77" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="259"/>
+      <c r="A77" s="193"/>
       <c r="B77" s="142" t="s">
         <v>133</v>
       </c>
@@ -13354,7 +13366,7 @@
       <c r="AP77" s="145"/>
     </row>
     <row r="78" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="258" t="s">
+      <c r="A78" s="192" t="s">
         <v>137</v>
       </c>
       <c r="B78" s="141" t="s">
@@ -13395,7 +13407,7 @@
       <c r="AI78" s="27"/>
       <c r="AJ78" s="43"/>
       <c r="AK78" s="25"/>
-      <c r="AL78" s="257" t="s">
+      <c r="AL78" s="191" t="s">
         <v>139</v>
       </c>
       <c r="AM78" s="23"/>
@@ -13404,7 +13416,7 @@
       <c r="AP78" s="18"/>
     </row>
     <row r="79" spans="1:42" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="259"/>
+      <c r="A79" s="193"/>
       <c r="B79" s="142" t="s">
         <v>133</v>
       </c>
@@ -13450,11 +13462,11 @@
       <c r="AP79" s="44"/>
     </row>
     <row r="80" spans="1:42" s="2" customFormat="1" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="250" t="s">
-        <v>166</v>
-      </c>
-      <c r="B80" s="168" t="s">
-        <v>143</v>
+      <c r="A80" s="184" t="s">
+        <v>159</v>
+      </c>
+      <c r="B80" s="196" t="s">
+        <v>146</v>
       </c>
       <c r="C80" s="96"/>
       <c r="D80" s="97"/>
@@ -13492,10 +13504,10 @@
       <c r="AJ80" s="97"/>
       <c r="AK80" s="98"/>
       <c r="AL80" s="99"/>
-      <c r="AM80" s="251"/>
-      <c r="AN80" s="252"/>
-      <c r="AO80" s="251"/>
-      <c r="AP80" s="253"/>
+      <c r="AM80" s="185"/>
+      <c r="AN80" s="186"/>
+      <c r="AO80" s="185"/>
+      <c r="AP80" s="187"/>
     </row>
   </sheetData>
   <mergeCells count="52">
@@ -13512,6 +13524,7 @@
     <mergeCell ref="AM3:AP3"/>
     <mergeCell ref="C2:D2"/>
     <mergeCell ref="E2:AP2"/>
+    <mergeCell ref="AE4:AH4"/>
     <mergeCell ref="AI4:AL4"/>
     <mergeCell ref="AM4:AP4"/>
     <mergeCell ref="C4:F4"/>
@@ -13519,21 +13532,22 @@
     <mergeCell ref="K4:N4"/>
     <mergeCell ref="O4:R4"/>
     <mergeCell ref="S4:V4"/>
+    <mergeCell ref="A56:A57"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="W4:Z4"/>
     <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="AE4:AH4"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A48:A49"/>
     <mergeCell ref="A67:A68"/>
     <mergeCell ref="A65:A66"/>
     <mergeCell ref="A63:A64"/>
     <mergeCell ref="A60:A61"/>
     <mergeCell ref="A58:A59"/>
-    <mergeCell ref="A56:A57"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A54:A55"/>
+    <mergeCell ref="A52:A53"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A24:A25"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="A44:A45"/>
     <mergeCell ref="A9:A10"/>
@@ -13549,8 +13563,6 @@
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="A42:A43"/>
     <mergeCell ref="A28:A29"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A24:A25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.35" right="0.35" top="0.35" bottom="0.5" header="0.3" footer="0.3"/>
@@ -13574,49 +13586,49 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:59" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="203" t="s">
+      <c r="A1" s="217" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="203"/>
-      <c r="C1" s="203"/>
-      <c r="D1" s="203"/>
-      <c r="E1" s="203"/>
-      <c r="F1" s="203"/>
-      <c r="G1" s="203"/>
-      <c r="H1" s="203"/>
-      <c r="I1" s="203"/>
-      <c r="J1" s="203"/>
-      <c r="K1" s="203"/>
-      <c r="L1" s="203"/>
-      <c r="M1" s="203"/>
-      <c r="N1" s="203"/>
-      <c r="O1" s="203"/>
-      <c r="P1" s="203"/>
-      <c r="Q1" s="203"/>
-      <c r="R1" s="203"/>
-      <c r="S1" s="203"/>
-      <c r="T1" s="203"/>
-      <c r="U1" s="203"/>
-      <c r="V1" s="203"/>
-      <c r="W1" s="203"/>
-      <c r="X1" s="203"/>
-      <c r="Y1" s="203"/>
-      <c r="Z1" s="203"/>
-      <c r="AA1" s="203"/>
-      <c r="AB1" s="203"/>
-      <c r="AC1" s="203"/>
-      <c r="AD1" s="203"/>
-      <c r="AE1" s="203"/>
-      <c r="AF1" s="203"/>
-      <c r="AG1" s="203"/>
-      <c r="AH1" s="203"/>
-      <c r="AI1" s="203"/>
-      <c r="AJ1" s="203"/>
-      <c r="AK1" s="203"/>
-      <c r="AL1" s="203"/>
-      <c r="AM1" s="203"/>
-      <c r="AN1" s="203"/>
-      <c r="AO1" s="203"/>
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="217"/>
+      <c r="N1" s="217"/>
+      <c r="O1" s="217"/>
+      <c r="P1" s="217"/>
+      <c r="Q1" s="217"/>
+      <c r="R1" s="217"/>
+      <c r="S1" s="217"/>
+      <c r="T1" s="217"/>
+      <c r="U1" s="217"/>
+      <c r="V1" s="217"/>
+      <c r="W1" s="217"/>
+      <c r="X1" s="217"/>
+      <c r="Y1" s="217"/>
+      <c r="Z1" s="217"/>
+      <c r="AA1" s="217"/>
+      <c r="AB1" s="217"/>
+      <c r="AC1" s="217"/>
+      <c r="AD1" s="217"/>
+      <c r="AE1" s="217"/>
+      <c r="AF1" s="217"/>
+      <c r="AG1" s="217"/>
+      <c r="AH1" s="217"/>
+      <c r="AI1" s="217"/>
+      <c r="AJ1" s="217"/>
+      <c r="AK1" s="217"/>
+      <c r="AL1" s="217"/>
+      <c r="AM1" s="217"/>
+      <c r="AN1" s="217"/>
+      <c r="AO1" s="217"/>
     </row>
     <row r="2" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
@@ -13627,131 +13639,131 @@
       <c r="A3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="208" t="s">
+      <c r="B3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="C3" s="209"/>
-      <c r="D3" s="209"/>
-      <c r="E3" s="210"/>
-      <c r="F3" s="208" t="s">
+      <c r="C3" s="223"/>
+      <c r="D3" s="223"/>
+      <c r="E3" s="224"/>
+      <c r="F3" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="G3" s="209"/>
-      <c r="H3" s="209"/>
-      <c r="I3" s="210"/>
-      <c r="J3" s="208" t="s">
+      <c r="G3" s="223"/>
+      <c r="H3" s="223"/>
+      <c r="I3" s="224"/>
+      <c r="J3" s="222" t="s">
         <v>96</v>
       </c>
-      <c r="K3" s="209"/>
-      <c r="L3" s="209"/>
-      <c r="M3" s="210"/>
-      <c r="N3" s="208" t="s">
+      <c r="K3" s="223"/>
+      <c r="L3" s="223"/>
+      <c r="M3" s="224"/>
+      <c r="N3" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="O3" s="209"/>
-      <c r="P3" s="209"/>
-      <c r="Q3" s="210"/>
-      <c r="R3" s="208" t="s">
+      <c r="O3" s="223"/>
+      <c r="P3" s="223"/>
+      <c r="Q3" s="224"/>
+      <c r="R3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="S3" s="209"/>
-      <c r="T3" s="209"/>
-      <c r="U3" s="210"/>
-      <c r="V3" s="208" t="s">
+      <c r="S3" s="223"/>
+      <c r="T3" s="223"/>
+      <c r="U3" s="224"/>
+      <c r="V3" s="222" t="s">
         <v>95</v>
       </c>
-      <c r="W3" s="209"/>
-      <c r="X3" s="209"/>
-      <c r="Y3" s="210"/>
-      <c r="Z3" s="208" t="s">
+      <c r="W3" s="223"/>
+      <c r="X3" s="223"/>
+      <c r="Y3" s="224"/>
+      <c r="Z3" s="222" t="s">
         <v>96</v>
       </c>
-      <c r="AA3" s="209"/>
-      <c r="AB3" s="209"/>
-      <c r="AC3" s="210"/>
-      <c r="AD3" s="208" t="s">
+      <c r="AA3" s="223"/>
+      <c r="AB3" s="223"/>
+      <c r="AC3" s="224"/>
+      <c r="AD3" s="222" t="s">
         <v>97</v>
       </c>
-      <c r="AE3" s="209"/>
-      <c r="AF3" s="209"/>
-      <c r="AG3" s="210"/>
-      <c r="AH3" s="208" t="s">
+      <c r="AE3" s="223"/>
+      <c r="AF3" s="223"/>
+      <c r="AG3" s="224"/>
+      <c r="AH3" s="222" t="s">
         <v>98</v>
       </c>
-      <c r="AI3" s="209"/>
-      <c r="AJ3" s="209"/>
-      <c r="AK3" s="210"/>
-      <c r="AL3" s="208" t="s">
+      <c r="AI3" s="223"/>
+      <c r="AJ3" s="223"/>
+      <c r="AK3" s="224"/>
+      <c r="AL3" s="222" t="s">
         <v>94</v>
       </c>
-      <c r="AM3" s="209"/>
-      <c r="AN3" s="209"/>
-      <c r="AO3" s="210"/>
+      <c r="AM3" s="223"/>
+      <c r="AN3" s="223"/>
+      <c r="AO3" s="224"/>
     </row>
     <row r="4" spans="1:59" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="20">
         <v>46139</v>
       </c>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="219" t="s">
         <v>99</v>
       </c>
-      <c r="C4" s="206"/>
-      <c r="D4" s="206"/>
-      <c r="E4" s="207"/>
-      <c r="F4" s="205" t="s">
+      <c r="C4" s="220"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="219" t="s">
         <v>100</v>
       </c>
-      <c r="G4" s="206"/>
-      <c r="H4" s="206"/>
-      <c r="I4" s="207"/>
-      <c r="J4" s="205" t="s">
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="219" t="s">
         <v>101</v>
       </c>
-      <c r="K4" s="206"/>
-      <c r="L4" s="206"/>
-      <c r="M4" s="207"/>
-      <c r="N4" s="205" t="s">
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="221"/>
+      <c r="N4" s="219" t="s">
         <v>102</v>
       </c>
-      <c r="O4" s="206"/>
-      <c r="P4" s="206"/>
-      <c r="Q4" s="207"/>
-      <c r="R4" s="205" t="s">
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="221"/>
+      <c r="R4" s="219" t="s">
         <v>103</v>
       </c>
-      <c r="S4" s="206"/>
-      <c r="T4" s="206"/>
-      <c r="U4" s="207"/>
-      <c r="V4" s="205" t="s">
+      <c r="S4" s="220"/>
+      <c r="T4" s="220"/>
+      <c r="U4" s="221"/>
+      <c r="V4" s="219" t="s">
         <v>104</v>
       </c>
-      <c r="W4" s="206"/>
-      <c r="X4" s="206"/>
-      <c r="Y4" s="207"/>
-      <c r="Z4" s="205" t="s">
+      <c r="W4" s="220"/>
+      <c r="X4" s="220"/>
+      <c r="Y4" s="221"/>
+      <c r="Z4" s="219" t="s">
         <v>105</v>
       </c>
-      <c r="AA4" s="206"/>
-      <c r="AB4" s="206"/>
-      <c r="AC4" s="207"/>
-      <c r="AD4" s="205" t="s">
+      <c r="AA4" s="220"/>
+      <c r="AB4" s="220"/>
+      <c r="AC4" s="221"/>
+      <c r="AD4" s="219" t="s">
         <v>106</v>
       </c>
-      <c r="AE4" s="206"/>
-      <c r="AF4" s="206"/>
-      <c r="AG4" s="207"/>
-      <c r="AH4" s="205" t="s">
+      <c r="AE4" s="220"/>
+      <c r="AF4" s="220"/>
+      <c r="AG4" s="221"/>
+      <c r="AH4" s="219" t="s">
         <v>107</v>
       </c>
-      <c r="AI4" s="206"/>
-      <c r="AJ4" s="206"/>
-      <c r="AK4" s="207"/>
-      <c r="AL4" s="205" t="s">
+      <c r="AI4" s="220"/>
+      <c r="AJ4" s="220"/>
+      <c r="AK4" s="221"/>
+      <c r="AL4" s="219" t="s">
         <v>108</v>
       </c>
-      <c r="AM4" s="206"/>
-      <c r="AN4" s="206"/>
-      <c r="AO4" s="207"/>
+      <c r="AM4" s="220"/>
+      <c r="AN4" s="220"/>
+      <c r="AO4" s="221"/>
     </row>
     <row r="5" spans="1:59" s="38" customFormat="1" ht="33" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="123" t="s">
@@ -15315,38 +15327,38 @@
       </c>
     </row>
     <row r="40" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Z40" s="230" t="s">
+      <c r="Z40" s="244" t="s">
         <v>21</v>
       </c>
-      <c r="AA40" s="231"/>
-      <c r="AB40" s="234" t="s">
+      <c r="AA40" s="245"/>
+      <c r="AB40" s="248" t="s">
         <v>88</v>
       </c>
-      <c r="AC40" s="235"/>
-      <c r="AD40" s="238" t="s">
+      <c r="AC40" s="249"/>
+      <c r="AD40" s="252" t="s">
         <v>22</v>
       </c>
-      <c r="AE40" s="239"/>
-      <c r="AF40" s="242" t="s">
+      <c r="AE40" s="253"/>
+      <c r="AF40" s="256" t="s">
         <v>50</v>
       </c>
-      <c r="AG40" s="243"/>
-      <c r="AH40" s="246" t="s">
+      <c r="AG40" s="257"/>
+      <c r="AH40" s="260" t="s">
         <v>49</v>
       </c>
-      <c r="AI40" s="247"/>
+      <c r="AI40" s="261"/>
     </row>
     <row r="41" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="Z41" s="232"/>
-      <c r="AA41" s="233"/>
-      <c r="AB41" s="236"/>
-      <c r="AC41" s="237"/>
-      <c r="AD41" s="240"/>
-      <c r="AE41" s="241"/>
-      <c r="AF41" s="244"/>
-      <c r="AG41" s="245"/>
-      <c r="AH41" s="248"/>
-      <c r="AI41" s="249"/>
+      <c r="Z41" s="246"/>
+      <c r="AA41" s="247"/>
+      <c r="AB41" s="250"/>
+      <c r="AC41" s="251"/>
+      <c r="AD41" s="254"/>
+      <c r="AE41" s="255"/>
+      <c r="AF41" s="258"/>
+      <c r="AG41" s="259"/>
+      <c r="AH41" s="262"/>
+      <c r="AI41" s="263"/>
     </row>
   </sheetData>
   <mergeCells count="26">
